--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,150 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Mexican Liga MX</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
+    <t>UEFA Nations League</t>
+  </si>
+  <si>
+    <t>Slovenian 2 SNL</t>
+  </si>
+  <si>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>01:10:00</t>
+  </si>
+  <si>
+    <t>03:10:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>19:30:00</t>
+  </si>
+  <si>
+    <t>Leon</t>
+  </si>
+  <si>
+    <t>Deportivo Cali</t>
+  </si>
+  <si>
+    <t>Necaxa</t>
+  </si>
+  <si>
+    <t>MSK Zilina II</t>
+  </si>
+  <si>
+    <t>Armenia</t>
+  </si>
+  <si>
+    <t>Latvia</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Rudar</t>
+  </si>
+  <si>
+    <t>Leganes</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Northern Ireland</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>Sportivo San Lorenzo</t>
+  </si>
+  <si>
+    <t>FC Juarez</t>
+  </si>
+  <si>
+    <t>Aguilas Doradas</t>
+  </si>
+  <si>
+    <t>CF America</t>
+  </si>
+  <si>
+    <t>FK Humenne</t>
+  </si>
+  <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
+    <t>Cyprus</t>
+  </si>
+  <si>
+    <t>Ukraine</t>
+  </si>
+  <si>
+    <t>Dravinja Kostroj</t>
+  </si>
+  <si>
+    <t>CD Castellon</t>
+  </si>
+  <si>
+    <t>Bosnia</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Deportivo Recoleta</t>
+  </si>
+  <si>
+    <t>2026-09-26 01:07:34</t>
   </si>
 </sst>
 </file>
@@ -585,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +972,3636 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2">
+        <v>1.62</v>
+      </c>
+      <c r="G2">
+        <v>1.66</v>
+      </c>
+      <c r="H2">
+        <v>5.5</v>
+      </c>
+      <c r="I2">
+        <v>6.2</v>
+      </c>
+      <c r="J2">
+        <v>4.3</v>
+      </c>
+      <c r="K2">
+        <v>4.8</v>
+      </c>
+      <c r="L2">
+        <v>1.31</v>
+      </c>
+      <c r="M2">
+        <v>1.04</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+      <c r="O2">
+        <v>1.22</v>
+      </c>
+      <c r="P2">
+        <v>2.36</v>
+      </c>
+      <c r="Q2">
+        <v>1.64</v>
+      </c>
+      <c r="R2">
+        <v>1.53</v>
+      </c>
+      <c r="S2">
+        <v>2.58</v>
+      </c>
+      <c r="T2">
+        <v>1.73</v>
+      </c>
+      <c r="U2">
+        <v>2.22</v>
+      </c>
+      <c r="V2">
+        <v>1.19</v>
+      </c>
+      <c r="W2">
+        <v>2.5</v>
+      </c>
+      <c r="X2">
+        <v>24</v>
+      </c>
+      <c r="Y2">
+        <v>25</v>
+      </c>
+      <c r="Z2">
+        <v>50</v>
+      </c>
+      <c r="AA2">
+        <v>150</v>
+      </c>
+      <c r="AB2">
+        <v>11.5</v>
+      </c>
+      <c r="AC2">
+        <v>11</v>
+      </c>
+      <c r="AD2">
+        <v>23</v>
+      </c>
+      <c r="AE2">
+        <v>75</v>
+      </c>
+      <c r="AF2">
+        <v>11.5</v>
+      </c>
+      <c r="AG2">
+        <v>10.5</v>
+      </c>
+      <c r="AH2">
+        <v>19.5</v>
+      </c>
+      <c r="AI2">
+        <v>70</v>
+      </c>
+      <c r="AJ2">
+        <v>17</v>
+      </c>
+      <c r="AK2">
+        <v>17</v>
+      </c>
+      <c r="AL2">
+        <v>30</v>
+      </c>
+      <c r="AM2">
+        <v>95</v>
+      </c>
+      <c r="AN2">
+        <v>7.6</v>
+      </c>
+      <c r="AO2">
+        <v>70</v>
+      </c>
+      <c r="AP2">
+        <v>18.5</v>
+      </c>
+      <c r="AQ2">
+        <v>20</v>
+      </c>
+      <c r="AR2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT2">
+        <v>9.6</v>
+      </c>
+      <c r="AU2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV2">
+        <v>18.5</v>
+      </c>
+      <c r="AW2">
+        <v>8.6</v>
+      </c>
+      <c r="AX2">
+        <v>10</v>
+      </c>
+      <c r="AY2">
+        <v>9</v>
+      </c>
+      <c r="AZ2">
+        <v>16.5</v>
+      </c>
+      <c r="BA2">
+        <v>8.6</v>
+      </c>
+      <c r="BB2">
+        <v>14</v>
+      </c>
+      <c r="BC2">
+        <v>14</v>
+      </c>
+      <c r="BD2">
+        <v>7.2</v>
+      </c>
+      <c r="BE2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF2">
+        <v>6.6</v>
+      </c>
+      <c r="BG2">
+        <v>8.6</v>
+      </c>
+      <c r="BH2">
+        <v>4.3</v>
+      </c>
+      <c r="BI2">
+        <v>3.75</v>
+      </c>
+      <c r="BJ2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>21</v>
+      </c>
+      <c r="BN2">
+        <v>4.6</v>
+      </c>
+      <c r="BO2">
+        <v>4</v>
+      </c>
+      <c r="BP2">
+        <v>10.5</v>
+      </c>
+      <c r="BQ2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR2">
+        <v>23</v>
+      </c>
+      <c r="BS2">
+        <v>16.5</v>
+      </c>
+      <c r="BT2">
+        <v>9.4</v>
+      </c>
+      <c r="BU2">
+        <v>8</v>
+      </c>
+      <c r="BV2">
+        <v>44</v>
+      </c>
+      <c r="BW2">
+        <v>30</v>
+      </c>
+      <c r="BX2">
+        <v>46</v>
+      </c>
+      <c r="BY2">
+        <v>32</v>
+      </c>
+      <c r="BZ2">
+        <v>15.5</v>
+      </c>
+      <c r="CA2">
+        <v>11.5</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3">
+        <v>1.91</v>
+      </c>
+      <c r="G3">
+        <v>1.99</v>
+      </c>
+      <c r="H3">
+        <v>4.8</v>
+      </c>
+      <c r="I3">
+        <v>5.7</v>
+      </c>
+      <c r="J3">
+        <v>3.35</v>
+      </c>
+      <c r="K3">
+        <v>3.6</v>
+      </c>
+      <c r="L3">
+        <v>1.4</v>
+      </c>
+      <c r="M3">
+        <v>1.1</v>
+      </c>
+      <c r="N3">
+        <v>3.05</v>
+      </c>
+      <c r="O3">
+        <v>1.42</v>
+      </c>
+      <c r="P3">
+        <v>1.68</v>
+      </c>
+      <c r="Q3">
+        <v>2.34</v>
+      </c>
+      <c r="R3">
+        <v>1.24</v>
+      </c>
+      <c r="S3">
+        <v>4.3</v>
+      </c>
+      <c r="T3">
+        <v>2</v>
+      </c>
+      <c r="U3">
+        <v>1.79</v>
+      </c>
+      <c r="V3">
+        <v>1.21</v>
+      </c>
+      <c r="W3">
+        <v>2</v>
+      </c>
+      <c r="X3">
+        <v>18</v>
+      </c>
+      <c r="Y3">
+        <v>17</v>
+      </c>
+      <c r="Z3">
+        <v>40</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>8</v>
+      </c>
+      <c r="AC3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>95</v>
+      </c>
+      <c r="AF3">
+        <v>19</v>
+      </c>
+      <c r="AG3">
+        <v>20</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>22</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.99</v>
+      </c>
+      <c r="AQ3">
+        <v>1.97</v>
+      </c>
+      <c r="AR3">
+        <v>2.12</v>
+      </c>
+      <c r="AS3">
+        <v>2.24</v>
+      </c>
+      <c r="AT3">
+        <v>6.6</v>
+      </c>
+      <c r="AU3">
+        <v>6.8</v>
+      </c>
+      <c r="AV3">
+        <v>17</v>
+      </c>
+      <c r="AW3">
+        <v>2.18</v>
+      </c>
+      <c r="AX3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3">
+        <v>2.24</v>
+      </c>
+      <c r="BA3">
+        <v>2.24</v>
+      </c>
+      <c r="BB3">
+        <v>17</v>
+      </c>
+      <c r="BC3">
+        <v>19</v>
+      </c>
+      <c r="BD3">
+        <v>2.24</v>
+      </c>
+      <c r="BE3">
+        <v>2.24</v>
+      </c>
+      <c r="BF3">
+        <v>2.02</v>
+      </c>
+      <c r="BG3">
+        <v>2.24</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4">
+        <v>3.7</v>
+      </c>
+      <c r="G4">
+        <v>4.5</v>
+      </c>
+      <c r="H4">
+        <v>1.89</v>
+      </c>
+      <c r="I4">
+        <v>2.06</v>
+      </c>
+      <c r="J4">
+        <v>3.85</v>
+      </c>
+      <c r="K4">
+        <v>5.1</v>
+      </c>
+      <c r="L4">
+        <v>1.3</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>4.1</v>
+      </c>
+      <c r="O4">
+        <v>1.22</v>
+      </c>
+      <c r="P4">
+        <v>2.16</v>
+      </c>
+      <c r="Q4">
+        <v>1.7</v>
+      </c>
+      <c r="R4">
+        <v>1.44</v>
+      </c>
+      <c r="S4">
+        <v>2.68</v>
+      </c>
+      <c r="T4">
+        <v>1.62</v>
+      </c>
+      <c r="U4">
+        <v>2.26</v>
+      </c>
+      <c r="V4">
+        <v>1.95</v>
+      </c>
+      <c r="W4">
+        <v>1.29</v>
+      </c>
+      <c r="X4">
+        <v>21</v>
+      </c>
+      <c r="Y4">
+        <v>21</v>
+      </c>
+      <c r="Z4">
+        <v>30</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>18.5</v>
+      </c>
+      <c r="AC4">
+        <v>14.5</v>
+      </c>
+      <c r="AD4">
+        <v>18</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>36</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>34</v>
+      </c>
+      <c r="AJ4">
+        <v>90</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>90</v>
+      </c>
+      <c r="AN4">
+        <v>44</v>
+      </c>
+      <c r="AO4">
+        <v>19</v>
+      </c>
+      <c r="AP4">
+        <v>12</v>
+      </c>
+      <c r="AQ4">
+        <v>7.8</v>
+      </c>
+      <c r="AR4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS4">
+        <v>17.5</v>
+      </c>
+      <c r="AT4">
+        <v>11</v>
+      </c>
+      <c r="AU4">
+        <v>6.8</v>
+      </c>
+      <c r="AV4">
+        <v>7.4</v>
+      </c>
+      <c r="AW4">
+        <v>11</v>
+      </c>
+      <c r="AX4">
+        <v>1.77</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
+        <v>11</v>
+      </c>
+      <c r="BA4">
+        <v>1.77</v>
+      </c>
+      <c r="BB4">
+        <v>1.83</v>
+      </c>
+      <c r="BC4">
+        <v>1.87</v>
+      </c>
+      <c r="BD4">
+        <v>1.87</v>
+      </c>
+      <c r="BE4">
+        <v>1.83</v>
+      </c>
+      <c r="BF4">
+        <v>1.78</v>
+      </c>
+      <c r="BG4">
+        <v>7.6</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>3.2</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>6.6</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>5.6</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>4</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5">
+        <v>1.5</v>
+      </c>
+      <c r="G5">
+        <v>1.9</v>
+      </c>
+      <c r="H5">
+        <v>4.2</v>
+      </c>
+      <c r="I5">
+        <v>18</v>
+      </c>
+      <c r="J5">
+        <v>3.6</v>
+      </c>
+      <c r="K5">
+        <v>10.5</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>2.06</v>
+      </c>
+      <c r="Q5">
+        <v>1.5</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6">
+        <v>2.92</v>
+      </c>
+      <c r="G6">
+        <v>3.3</v>
+      </c>
+      <c r="H6">
+        <v>2.48</v>
+      </c>
+      <c r="I6">
+        <v>2.74</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>3.4</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.25</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6">
+        <v>1.03</v>
+      </c>
+      <c r="AR6">
+        <v>1.03</v>
+      </c>
+      <c r="AS6">
+        <v>1.03</v>
+      </c>
+      <c r="AT6">
+        <v>1.03</v>
+      </c>
+      <c r="AU6">
+        <v>1.03</v>
+      </c>
+      <c r="AV6">
+        <v>1.03</v>
+      </c>
+      <c r="AW6">
+        <v>1.03</v>
+      </c>
+      <c r="AX6">
+        <v>1.03</v>
+      </c>
+      <c r="AY6">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6">
+        <v>1.03</v>
+      </c>
+      <c r="BA6">
+        <v>1.03</v>
+      </c>
+      <c r="BB6">
+        <v>1.03</v>
+      </c>
+      <c r="BC6">
+        <v>1.03</v>
+      </c>
+      <c r="BD6">
+        <v>1.03</v>
+      </c>
+      <c r="BE6">
+        <v>1.03</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7">
+        <v>2.26</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>2.64</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1.13</v>
+      </c>
+      <c r="K7">
+        <v>6.6</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.25</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1.01</v>
+      </c>
+      <c r="U7">
+        <v>1.01</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7">
+        <v>1.03</v>
+      </c>
+      <c r="AR7">
+        <v>1.03</v>
+      </c>
+      <c r="AS7">
+        <v>1.03</v>
+      </c>
+      <c r="AT7">
+        <v>1.03</v>
+      </c>
+      <c r="AU7">
+        <v>1.03</v>
+      </c>
+      <c r="AV7">
+        <v>1.03</v>
+      </c>
+      <c r="AW7">
+        <v>1.03</v>
+      </c>
+      <c r="AX7">
+        <v>1.03</v>
+      </c>
+      <c r="AY7">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7">
+        <v>1.03</v>
+      </c>
+      <c r="BA7">
+        <v>1.03</v>
+      </c>
+      <c r="BB7">
+        <v>1.03</v>
+      </c>
+      <c r="BC7">
+        <v>1.03</v>
+      </c>
+      <c r="BD7">
+        <v>1.03</v>
+      </c>
+      <c r="BE7">
+        <v>1.03</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8">
+        <v>2.78</v>
+      </c>
+      <c r="G8">
+        <v>2.98</v>
+      </c>
+      <c r="H8">
+        <v>2.7</v>
+      </c>
+      <c r="I8">
+        <v>2.92</v>
+      </c>
+      <c r="J8">
+        <v>3.35</v>
+      </c>
+      <c r="K8">
+        <v>3.45</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.78</v>
+      </c>
+      <c r="Q8">
+        <v>2.22</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>1.84</v>
+      </c>
+      <c r="U8">
+        <v>2.04</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>12</v>
+      </c>
+      <c r="Y8">
+        <v>10.5</v>
+      </c>
+      <c r="Z8">
+        <v>18.5</v>
+      </c>
+      <c r="AA8">
+        <v>46</v>
+      </c>
+      <c r="AB8">
+        <v>10.5</v>
+      </c>
+      <c r="AC8">
+        <v>7.6</v>
+      </c>
+      <c r="AD8">
+        <v>13</v>
+      </c>
+      <c r="AE8">
+        <v>34</v>
+      </c>
+      <c r="AF8">
+        <v>21</v>
+      </c>
+      <c r="AG8">
+        <v>13</v>
+      </c>
+      <c r="AH8">
+        <v>18.5</v>
+      </c>
+      <c r="AI8">
+        <v>60</v>
+      </c>
+      <c r="AJ8">
+        <v>60</v>
+      </c>
+      <c r="AK8">
+        <v>36</v>
+      </c>
+      <c r="AL8">
+        <v>60</v>
+      </c>
+      <c r="AM8">
+        <v>130</v>
+      </c>
+      <c r="AN8">
+        <v>34</v>
+      </c>
+      <c r="AO8">
+        <v>34</v>
+      </c>
+      <c r="AP8">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8">
+        <v>9</v>
+      </c>
+      <c r="AR8">
+        <v>16</v>
+      </c>
+      <c r="AS8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU8">
+        <v>6.6</v>
+      </c>
+      <c r="AV8">
+        <v>11</v>
+      </c>
+      <c r="AW8">
+        <v>8.6</v>
+      </c>
+      <c r="AX8">
+        <v>15.5</v>
+      </c>
+      <c r="AY8">
+        <v>11.5</v>
+      </c>
+      <c r="AZ8">
+        <v>16</v>
+      </c>
+      <c r="BA8">
+        <v>9.4</v>
+      </c>
+      <c r="BB8">
+        <v>38</v>
+      </c>
+      <c r="BC8">
+        <v>29</v>
+      </c>
+      <c r="BD8">
+        <v>9.6</v>
+      </c>
+      <c r="BE8">
+        <v>10.5</v>
+      </c>
+      <c r="BF8">
+        <v>26</v>
+      </c>
+      <c r="BG8">
+        <v>27</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9">
+        <v>1.01</v>
+      </c>
+      <c r="G9">
+        <v>1000</v>
+      </c>
+      <c r="H9">
+        <v>1.01</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9">
+        <v>1.02</v>
+      </c>
+      <c r="K9">
+        <v>1000</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.01</v>
+      </c>
+      <c r="O9">
+        <v>1.01</v>
+      </c>
+      <c r="P9">
+        <v>1.01</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>1.01</v>
+      </c>
+      <c r="S9">
+        <v>1.01</v>
+      </c>
+      <c r="T9">
+        <v>1.01</v>
+      </c>
+      <c r="U9">
+        <v>1.01</v>
+      </c>
+      <c r="V9">
+        <v>1.01</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9">
+        <v>1.03</v>
+      </c>
+      <c r="AR9">
+        <v>1.03</v>
+      </c>
+      <c r="AS9">
+        <v>1.03</v>
+      </c>
+      <c r="AT9">
+        <v>1.03</v>
+      </c>
+      <c r="AU9">
+        <v>1.03</v>
+      </c>
+      <c r="AV9">
+        <v>1.03</v>
+      </c>
+      <c r="AW9">
+        <v>1.03</v>
+      </c>
+      <c r="AX9">
+        <v>1.03</v>
+      </c>
+      <c r="AY9">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9">
+        <v>1.03</v>
+      </c>
+      <c r="BA9">
+        <v>1.03</v>
+      </c>
+      <c r="BB9">
+        <v>1.03</v>
+      </c>
+      <c r="BC9">
+        <v>1.03</v>
+      </c>
+      <c r="BD9">
+        <v>1.03</v>
+      </c>
+      <c r="BE9">
+        <v>1.03</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>3.4</v>
+      </c>
+      <c r="H10">
+        <v>2.42</v>
+      </c>
+      <c r="I10">
+        <v>2.54</v>
+      </c>
+      <c r="J10">
+        <v>3.4</v>
+      </c>
+      <c r="K10">
+        <v>3.65</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1.8</v>
+      </c>
+      <c r="Q10">
+        <v>1.95</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11">
+        <v>2.22</v>
+      </c>
+      <c r="G11">
+        <v>2.34</v>
+      </c>
+      <c r="H11">
+        <v>3.45</v>
+      </c>
+      <c r="I11">
+        <v>3.7</v>
+      </c>
+      <c r="J11">
+        <v>3.4</v>
+      </c>
+      <c r="K11">
+        <v>3.7</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.08</v>
+      </c>
+      <c r="N11">
+        <v>3.55</v>
+      </c>
+      <c r="O11">
+        <v>1.35</v>
+      </c>
+      <c r="P11">
+        <v>1.87</v>
+      </c>
+      <c r="Q11">
+        <v>2.06</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>1.86</v>
+      </c>
+      <c r="U11">
+        <v>2.1</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>13.5</v>
+      </c>
+      <c r="Y11">
+        <v>13</v>
+      </c>
+      <c r="Z11">
+        <v>26</v>
+      </c>
+      <c r="AA11">
+        <v>80</v>
+      </c>
+      <c r="AB11">
+        <v>9.6</v>
+      </c>
+      <c r="AC11">
+        <v>8</v>
+      </c>
+      <c r="AD11">
+        <v>15.5</v>
+      </c>
+      <c r="AE11">
+        <v>46</v>
+      </c>
+      <c r="AF11">
+        <v>14.5</v>
+      </c>
+      <c r="AG11">
+        <v>11.5</v>
+      </c>
+      <c r="AH11">
+        <v>19</v>
+      </c>
+      <c r="AI11">
+        <v>65</v>
+      </c>
+      <c r="AJ11">
+        <v>32</v>
+      </c>
+      <c r="AK11">
+        <v>26</v>
+      </c>
+      <c r="AL11">
+        <v>42</v>
+      </c>
+      <c r="AM11">
+        <v>120</v>
+      </c>
+      <c r="AN11">
+        <v>20</v>
+      </c>
+      <c r="AO11">
+        <v>50</v>
+      </c>
+      <c r="AP11">
+        <v>11.5</v>
+      </c>
+      <c r="AQ11">
+        <v>11</v>
+      </c>
+      <c r="AR11">
+        <v>21</v>
+      </c>
+      <c r="AS11">
+        <v>10</v>
+      </c>
+      <c r="AT11">
+        <v>8.4</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>13</v>
+      </c>
+      <c r="AW11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX11">
+        <v>12</v>
+      </c>
+      <c r="AY11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11">
+        <v>16</v>
+      </c>
+      <c r="BA11">
+        <v>9.6</v>
+      </c>
+      <c r="BB11">
+        <v>22</v>
+      </c>
+      <c r="BC11">
+        <v>21</v>
+      </c>
+      <c r="BD11">
+        <v>9</v>
+      </c>
+      <c r="BE11">
+        <v>10.5</v>
+      </c>
+      <c r="BF11">
+        <v>16.5</v>
+      </c>
+      <c r="BG11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12">
+        <v>3.8</v>
+      </c>
+      <c r="G12">
+        <v>3.9</v>
+      </c>
+      <c r="H12">
+        <v>1.98</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>4.1</v>
+      </c>
+      <c r="K12">
+        <v>4.2</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1.04</v>
+      </c>
+      <c r="N12">
+        <v>5.9</v>
+      </c>
+      <c r="O12">
+        <v>1.18</v>
+      </c>
+      <c r="P12">
+        <v>2.74</v>
+      </c>
+      <c r="Q12">
+        <v>1.56</v>
+      </c>
+      <c r="R12">
+        <v>1.71</v>
+      </c>
+      <c r="S12">
+        <v>2.34</v>
+      </c>
+      <c r="T12">
+        <v>1.55</v>
+      </c>
+      <c r="U12">
+        <v>2.7</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>28</v>
+      </c>
+      <c r="Y12">
+        <v>15</v>
+      </c>
+      <c r="Z12">
+        <v>18</v>
+      </c>
+      <c r="AA12">
+        <v>27</v>
+      </c>
+      <c r="AB12">
+        <v>26</v>
+      </c>
+      <c r="AC12">
+        <v>12.5</v>
+      </c>
+      <c r="AD12">
+        <v>12.5</v>
+      </c>
+      <c r="AE12">
+        <v>20</v>
+      </c>
+      <c r="AF12">
+        <v>38</v>
+      </c>
+      <c r="AG12">
+        <v>21</v>
+      </c>
+      <c r="AH12">
+        <v>18.5</v>
+      </c>
+      <c r="AI12">
+        <v>32</v>
+      </c>
+      <c r="AJ12">
+        <v>80</v>
+      </c>
+      <c r="AK12">
+        <v>48</v>
+      </c>
+      <c r="AL12">
+        <v>48</v>
+      </c>
+      <c r="AM12">
+        <v>65</v>
+      </c>
+      <c r="AN12">
+        <v>32</v>
+      </c>
+      <c r="AO12">
+        <v>8.4</v>
+      </c>
+      <c r="AP12">
+        <v>22</v>
+      </c>
+      <c r="AQ12">
+        <v>13</v>
+      </c>
+      <c r="AR12">
+        <v>13.5</v>
+      </c>
+      <c r="AS12">
+        <v>5</v>
+      </c>
+      <c r="AT12">
+        <v>19</v>
+      </c>
+      <c r="AU12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW12">
+        <v>14.5</v>
+      </c>
+      <c r="AX12">
+        <v>5.3</v>
+      </c>
+      <c r="AY12">
+        <v>14.5</v>
+      </c>
+      <c r="AZ12">
+        <v>13.5</v>
+      </c>
+      <c r="BA12">
+        <v>5.1</v>
+      </c>
+      <c r="BB12">
+        <v>5.8</v>
+      </c>
+      <c r="BC12">
+        <v>5.5</v>
+      </c>
+      <c r="BD12">
+        <v>5.5</v>
+      </c>
+      <c r="BE12">
+        <v>5.7</v>
+      </c>
+      <c r="BF12">
+        <v>5.2</v>
+      </c>
+      <c r="BG12">
+        <v>7.2</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>3.45</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.01</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>5.6</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.01</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.01</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>4.2</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13">
+        <v>2.8</v>
+      </c>
+      <c r="G13">
+        <v>2.82</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>3.05</v>
+      </c>
+      <c r="J13">
+        <v>3.15</v>
+      </c>
+      <c r="K13">
+        <v>3.2</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1.12</v>
+      </c>
+      <c r="N13">
+        <v>2.72</v>
+      </c>
+      <c r="O13">
+        <v>1.54</v>
+      </c>
+      <c r="P13">
+        <v>1.58</v>
+      </c>
+      <c r="Q13">
+        <v>2.66</v>
+      </c>
+      <c r="R13">
+        <v>1.21</v>
+      </c>
+      <c r="S13">
+        <v>5.4</v>
+      </c>
+      <c r="T13">
+        <v>2.14</v>
+      </c>
+      <c r="U13">
+        <v>1.82</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y13">
+        <v>9</v>
+      </c>
+      <c r="Z13">
+        <v>18.5</v>
+      </c>
+      <c r="AA13">
+        <v>65</v>
+      </c>
+      <c r="AB13">
+        <v>8.6</v>
+      </c>
+      <c r="AC13">
+        <v>7.2</v>
+      </c>
+      <c r="AD13">
+        <v>14.5</v>
+      </c>
+      <c r="AE13">
+        <v>50</v>
+      </c>
+      <c r="AF13">
+        <v>17.5</v>
+      </c>
+      <c r="AG13">
+        <v>14</v>
+      </c>
+      <c r="AH13">
+        <v>24</v>
+      </c>
+      <c r="AI13">
+        <v>70</v>
+      </c>
+      <c r="AJ13">
+        <v>60</v>
+      </c>
+      <c r="AK13">
+        <v>48</v>
+      </c>
+      <c r="AL13">
+        <v>80</v>
+      </c>
+      <c r="AM13">
+        <v>200</v>
+      </c>
+      <c r="AN13">
+        <v>55</v>
+      </c>
+      <c r="AO13">
+        <v>60</v>
+      </c>
+      <c r="AP13">
+        <v>8</v>
+      </c>
+      <c r="AQ13">
+        <v>7.8</v>
+      </c>
+      <c r="AR13">
+        <v>16</v>
+      </c>
+      <c r="AS13">
+        <v>10</v>
+      </c>
+      <c r="AT13">
+        <v>7.6</v>
+      </c>
+      <c r="AU13">
+        <v>6.4</v>
+      </c>
+      <c r="AV13">
+        <v>12</v>
+      </c>
+      <c r="AW13">
+        <v>9.4</v>
+      </c>
+      <c r="AX13">
+        <v>15</v>
+      </c>
+      <c r="AY13">
+        <v>12</v>
+      </c>
+      <c r="AZ13">
+        <v>19</v>
+      </c>
+      <c r="BA13">
+        <v>10</v>
+      </c>
+      <c r="BB13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD13">
+        <v>10</v>
+      </c>
+      <c r="BE13">
+        <v>11</v>
+      </c>
+      <c r="BF13">
+        <v>9.6</v>
+      </c>
+      <c r="BG13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH13">
+        <v>2.88</v>
+      </c>
+      <c r="BI13">
+        <v>2.32</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>7.8</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>4.7</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.01</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.01</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14">
+        <v>1.92</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>3.8</v>
+      </c>
+      <c r="I14">
+        <v>4.2</v>
+      </c>
+      <c r="J14">
+        <v>3.85</v>
+      </c>
+      <c r="K14">
+        <v>4.2</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1.05</v>
+      </c>
+      <c r="N14">
+        <v>4.5</v>
+      </c>
+      <c r="O14">
+        <v>1.25</v>
+      </c>
+      <c r="P14">
+        <v>2.22</v>
+      </c>
+      <c r="Q14">
+        <v>1.75</v>
+      </c>
+      <c r="R14">
+        <v>1.48</v>
+      </c>
+      <c r="S14">
+        <v>2.82</v>
+      </c>
+      <c r="T14">
+        <v>1.66</v>
+      </c>
+      <c r="U14">
+        <v>2.3</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>20</v>
+      </c>
+      <c r="Y14">
+        <v>18</v>
+      </c>
+      <c r="Z14">
+        <v>34</v>
+      </c>
+      <c r="AA14">
+        <v>85</v>
+      </c>
+      <c r="AB14">
+        <v>11.5</v>
+      </c>
+      <c r="AC14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD14">
+        <v>17</v>
+      </c>
+      <c r="AE14">
+        <v>55</v>
+      </c>
+      <c r="AF14">
+        <v>14</v>
+      </c>
+      <c r="AG14">
+        <v>11</v>
+      </c>
+      <c r="AH14">
+        <v>17</v>
+      </c>
+      <c r="AI14">
+        <v>60</v>
+      </c>
+      <c r="AJ14">
+        <v>25</v>
+      </c>
+      <c r="AK14">
+        <v>20</v>
+      </c>
+      <c r="AL14">
+        <v>34</v>
+      </c>
+      <c r="AM14">
+        <v>85</v>
+      </c>
+      <c r="AN14">
+        <v>11</v>
+      </c>
+      <c r="AO14">
+        <v>44</v>
+      </c>
+      <c r="AP14">
+        <v>16.5</v>
+      </c>
+      <c r="AQ14">
+        <v>15.5</v>
+      </c>
+      <c r="AR14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS14">
+        <v>11</v>
+      </c>
+      <c r="AT14">
+        <v>10</v>
+      </c>
+      <c r="AU14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV14">
+        <v>14.5</v>
+      </c>
+      <c r="AW14">
+        <v>32</v>
+      </c>
+      <c r="AX14">
+        <v>12</v>
+      </c>
+      <c r="AY14">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14">
+        <v>15</v>
+      </c>
+      <c r="BA14">
+        <v>36</v>
+      </c>
+      <c r="BB14">
+        <v>19.5</v>
+      </c>
+      <c r="BC14">
+        <v>16.5</v>
+      </c>
+      <c r="BD14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE14">
+        <v>11</v>
+      </c>
+      <c r="BF14">
+        <v>9.6</v>
+      </c>
+      <c r="BG14">
+        <v>9.6</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>3.1</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>6.8</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>3.95</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>9</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>5.6</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15">
+        <v>2.8</v>
+      </c>
+      <c r="G15">
+        <v>2.86</v>
+      </c>
+      <c r="H15">
+        <v>2.72</v>
+      </c>
+      <c r="I15">
+        <v>2.78</v>
+      </c>
+      <c r="J15">
+        <v>3.55</v>
+      </c>
+      <c r="K15">
+        <v>3.6</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1.06</v>
+      </c>
+      <c r="N15">
+        <v>4.4</v>
+      </c>
+      <c r="O15">
+        <v>1.26</v>
+      </c>
+      <c r="P15">
+        <v>2.16</v>
+      </c>
+      <c r="Q15">
+        <v>1.83</v>
+      </c>
+      <c r="R15">
+        <v>1.44</v>
+      </c>
+      <c r="S15">
+        <v>2.98</v>
+      </c>
+      <c r="T15">
+        <v>1.65</v>
+      </c>
+      <c r="U15">
+        <v>2.42</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>21</v>
+      </c>
+      <c r="Y15">
+        <v>13.5</v>
+      </c>
+      <c r="Z15">
+        <v>20</v>
+      </c>
+      <c r="AA15">
+        <v>40</v>
+      </c>
+      <c r="AB15">
+        <v>14</v>
+      </c>
+      <c r="AC15">
+        <v>8.4</v>
+      </c>
+      <c r="AD15">
+        <v>12.5</v>
+      </c>
+      <c r="AE15">
+        <v>28</v>
+      </c>
+      <c r="AF15">
+        <v>21</v>
+      </c>
+      <c r="AG15">
+        <v>13</v>
+      </c>
+      <c r="AH15">
+        <v>16</v>
+      </c>
+      <c r="AI15">
+        <v>38</v>
+      </c>
+      <c r="AJ15">
+        <v>42</v>
+      </c>
+      <c r="AK15">
+        <v>30</v>
+      </c>
+      <c r="AL15">
+        <v>40</v>
+      </c>
+      <c r="AM15">
+        <v>75</v>
+      </c>
+      <c r="AN15">
+        <v>22</v>
+      </c>
+      <c r="AO15">
+        <v>21</v>
+      </c>
+      <c r="AP15">
+        <v>14.5</v>
+      </c>
+      <c r="AQ15">
+        <v>12</v>
+      </c>
+      <c r="AR15">
+        <v>16.5</v>
+      </c>
+      <c r="AS15">
+        <v>30</v>
+      </c>
+      <c r="AT15">
+        <v>12</v>
+      </c>
+      <c r="AU15">
+        <v>7.2</v>
+      </c>
+      <c r="AV15">
+        <v>11</v>
+      </c>
+      <c r="AW15">
+        <v>22</v>
+      </c>
+      <c r="AX15">
+        <v>17</v>
+      </c>
+      <c r="AY15">
+        <v>11</v>
+      </c>
+      <c r="AZ15">
+        <v>13.5</v>
+      </c>
+      <c r="BA15">
+        <v>30</v>
+      </c>
+      <c r="BB15">
+        <v>8.4</v>
+      </c>
+      <c r="BC15">
+        <v>23</v>
+      </c>
+      <c r="BD15">
+        <v>30</v>
+      </c>
+      <c r="BE15">
+        <v>9.4</v>
+      </c>
+      <c r="BF15">
+        <v>18</v>
+      </c>
+      <c r="BG15">
+        <v>18</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>3</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>6.2</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>4.8</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>4.6</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16">
+        <v>2.9</v>
+      </c>
+      <c r="G16">
+        <v>3.6</v>
+      </c>
+      <c r="H16">
+        <v>2.36</v>
+      </c>
+      <c r="I16">
+        <v>2.78</v>
+      </c>
+      <c r="J16">
+        <v>3.25</v>
+      </c>
+      <c r="K16">
+        <v>4.4</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.89</v>
+      </c>
+      <c r="Q16">
+        <v>1.87</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
@@ -397,7 +397,7 @@
     <t>Deportivo Recoleta</t>
   </si>
   <si>
-    <t>2026-09-26 01:07:34</t>
+    <t>2026-09-26 03:27:52</t>
   </si>
 </sst>
 </file>
@@ -997,7 +997,7 @@
         <v>1.66</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I2">
         <v>6.2</v>
@@ -1030,10 +1030,10 @@
         <v>1.53</v>
       </c>
       <c r="S2">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T2">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U2">
         <v>2.22</v>
@@ -1078,7 +1078,7 @@
         <v>19.5</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
         <v>17</v>
@@ -1090,10 +1090,10 @@
         <v>30</v>
       </c>
       <c r="AM2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO2">
         <v>70</v>
@@ -1105,13 +1105,13 @@
         <v>20</v>
       </c>
       <c r="AR2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2">
         <v>9.199999999999999</v>
@@ -1120,7 +1120,7 @@
         <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1132,7 +1132,7 @@
         <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
         <v>14</v>
@@ -1141,28 +1141,28 @@
         <v>14</v>
       </c>
       <c r="BD2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2">
         <v>6.6</v>
       </c>
       <c r="BG2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI2">
         <v>3.75</v>
       </c>
       <c r="BJ2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1171,7 +1171,7 @@
         <v>21</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
         <v>4</v>
@@ -1180,7 +1180,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR2">
         <v>23</v>
@@ -1192,7 +1192,7 @@
         <v>9.4</v>
       </c>
       <c r="BU2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV2">
         <v>44</v>
@@ -1233,7 +1233,7 @@
         <v>113</v>
       </c>
       <c r="F3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G3">
         <v>1.99</v>
@@ -1242,7 +1242,7 @@
         <v>4.8</v>
       </c>
       <c r="I3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J3">
         <v>3.35</v>
@@ -1257,7 +1257,7 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
         <v>1.42</v>
@@ -1266,7 +1266,7 @@
         <v>1.68</v>
       </c>
       <c r="Q3">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R3">
         <v>1.24</v>
@@ -1278,7 +1278,7 @@
         <v>2</v>
       </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
         <v>1.21</v>
@@ -1293,7 +1293,7 @@
         <v>17</v>
       </c>
       <c r="Z3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1311,10 +1311,10 @@
         <v>95</v>
       </c>
       <c r="AF3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH3">
         <v>1000</v>
@@ -1341,16 +1341,16 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AQ3">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AR3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AS3">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
@@ -1362,19 +1362,19 @@
         <v>17</v>
       </c>
       <c r="AW3">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AX3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY3">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BA3">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BB3">
         <v>17</v>
@@ -1383,16 +1383,16 @@
         <v>19</v>
       </c>
       <c r="BD3">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BE3">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BF3">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="BG3">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1475,43 +1475,43 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H4">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="I4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J4">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>1.3</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
         <v>4.1</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
         <v>2.16</v>
       </c>
       <c r="Q4">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="R4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S4">
         <v>2.68</v>
@@ -1520,22 +1520,22 @@
         <v>1.62</v>
       </c>
       <c r="U4">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V4">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="W4">
         <v>1.29</v>
       </c>
       <c r="X4">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
         <v>21</v>
       </c>
       <c r="Z4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -1604,34 +1604,34 @@
         <v>7.4</v>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX4">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AY4">
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BA4">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="BB4">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="BC4">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="BD4">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="BE4">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="BF4">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="BG4">
         <v>7.6</v>
@@ -1682,7 +1682,7 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BX4">
         <v>1000</v>
@@ -2034,16 +2034,16 @@
         <v>1000</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF6">
         <v>1000</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI6">
         <v>1000</v>
@@ -2067,58 +2067,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY6">
         <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH6">
         <v>0</v>
@@ -2204,19 +2204,19 @@
         <v>2.26</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H7">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J7">
-        <v>1.13</v>
+        <v>2.54</v>
       </c>
       <c r="K7">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="BB7">
         <v>1.03</v>
@@ -2351,16 +2351,16 @@
         <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="BE7">
         <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH7">
         <v>0</v>
@@ -2443,13 +2443,13 @@
         <v>118</v>
       </c>
       <c r="F8">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G8">
         <v>2.98</v>
       </c>
       <c r="H8">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I8">
         <v>2.92</v>
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U8">
         <v>2.04</v>
@@ -2566,7 +2566,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV8">
         <v>11</v>
@@ -2685,22 +2685,22 @@
         <v>119</v>
       </c>
       <c r="F9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J9">
         <v>1.02</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2930,7 +2930,7 @@
         <v>3</v>
       </c>
       <c r="G10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H10">
         <v>2.42</v>
@@ -2957,10 +2957,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="Q10">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3169,10 +3169,10 @@
         <v>121</v>
       </c>
       <c r="F11">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H11">
         <v>3.45</v>
@@ -3199,7 +3199,7 @@
         <v>1.35</v>
       </c>
       <c r="P11">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q11">
         <v>2.06</v>
@@ -3211,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="U11">
         <v>2.1</v>
@@ -3411,10 +3411,10 @@
         <v>122</v>
       </c>
       <c r="F12">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G12">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H12">
         <v>1.98</v>
@@ -3426,7 +3426,7 @@
         <v>4.1</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3435,7 +3435,7 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>1.18</v>
@@ -3447,10 +3447,10 @@
         <v>1.56</v>
       </c>
       <c r="R12">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="S12">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T12">
         <v>1.55</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y12">
         <v>15</v>
@@ -3483,16 +3483,16 @@
         <v>12.5</v>
       </c>
       <c r="AD12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE12">
         <v>20</v>
       </c>
       <c r="AF12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH12">
         <v>18.5</v>
@@ -3528,7 +3528,7 @@
         <v>13.5</v>
       </c>
       <c r="AS12">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AT12">
         <v>19</v>
@@ -3552,13 +3552,13 @@
         <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB12">
         <v>5.8</v>
       </c>
       <c r="BC12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD12">
         <v>5.5</v>
@@ -3570,7 +3570,7 @@
         <v>5.2</v>
       </c>
       <c r="BG12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3653,13 +3653,13 @@
         <v>123</v>
       </c>
       <c r="F13">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G13">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I13">
         <v>3.05</v>
@@ -3680,10 +3680,10 @@
         <v>2.72</v>
       </c>
       <c r="O13">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P13">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q13">
         <v>2.66</v>
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -3716,10 +3716,10 @@
         <v>18.5</v>
       </c>
       <c r="AA13">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13">
         <v>7.2</v>
@@ -3761,7 +3761,7 @@
         <v>60</v>
       </c>
       <c r="AP13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ13">
         <v>7.8</v>
@@ -3770,7 +3770,7 @@
         <v>16</v>
       </c>
       <c r="AS13">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AT13">
         <v>7.6</v>
@@ -3779,10 +3779,10 @@
         <v>6.4</v>
       </c>
       <c r="AV13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX13">
         <v>15</v>
@@ -3794,37 +3794,37 @@
         <v>19</v>
       </c>
       <c r="BA13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD13">
         <v>10</v>
       </c>
       <c r="BE13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF13">
+        <v>9.4</v>
+      </c>
+      <c r="BG13">
         <v>9.6</v>
       </c>
-      <c r="BG13">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH13">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BI13">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -3836,7 +3836,7 @@
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP13">
         <v>1000</v>
@@ -3901,7 +3901,7 @@
         <v>2</v>
       </c>
       <c r="H14">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I14">
         <v>4.2</v>
@@ -3925,19 +3925,19 @@
         <v>1.25</v>
       </c>
       <c r="P14">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q14">
         <v>1.75</v>
       </c>
       <c r="R14">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S14">
         <v>2.82</v>
       </c>
       <c r="T14">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U14">
         <v>2.3</v>
@@ -3973,7 +3973,7 @@
         <v>55</v>
       </c>
       <c r="AF14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -3985,22 +3985,22 @@
         <v>60</v>
       </c>
       <c r="AJ14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK14">
         <v>20</v>
       </c>
       <c r="AL14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM14">
         <v>85</v>
       </c>
       <c r="AN14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AP14">
         <v>16.5</v>
@@ -4009,13 +4009,13 @@
         <v>15.5</v>
       </c>
       <c r="AR14">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14">
         <v>8.199999999999999</v>
@@ -4042,31 +4042,31 @@
         <v>19.5</v>
       </c>
       <c r="BC14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD14">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG14">
         <v>9.6</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI14">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK14">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BL14">
         <v>1000</v>
@@ -4075,46 +4075,46 @@
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO14">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ14">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU14">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="CB14" t="s">
         <v>127</v>
@@ -4137,10 +4137,10 @@
         <v>125</v>
       </c>
       <c r="F15">
+        <v>2.78</v>
+      </c>
+      <c r="G15">
         <v>2.8</v>
-      </c>
-      <c r="G15">
-        <v>2.86</v>
       </c>
       <c r="H15">
         <v>2.72</v>
@@ -4176,13 +4176,13 @@
         <v>1.44</v>
       </c>
       <c r="S15">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U15">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -4281,7 +4281,7 @@
         <v>30</v>
       </c>
       <c r="BB15">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="BC15">
         <v>23</v>
@@ -4299,58 +4299,58 @@
         <v>18</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK15">
+        <v>6.6</v>
+      </c>
+      <c r="BL15">
+        <v>100</v>
+      </c>
+      <c r="BM15">
+        <v>65</v>
+      </c>
+      <c r="BN15">
         <v>6.2</v>
       </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.01</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
       <c r="BO15">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU15">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BZ15">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
@@ -397,7 +397,7 @@
     <t>Deportivo Recoleta</t>
   </si>
   <si>
-    <t>2026-09-26 03:27:52</t>
+    <t>2026-09-26 05:47:07</t>
   </si>
 </sst>
 </file>
@@ -991,22 +991,22 @@
         <v>112</v>
       </c>
       <c r="F2">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="G2">
         <v>1.66</v>
       </c>
       <c r="H2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J2">
         <v>4.3</v>
       </c>
       <c r="K2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L2">
         <v>1.31</v>
@@ -1018,25 +1018,25 @@
         <v>5</v>
       </c>
       <c r="O2">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P2">
         <v>2.36</v>
       </c>
       <c r="Q2">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="R2">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S2">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T2">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
         <v>1.19</v>
@@ -1051,7 +1051,7 @@
         <v>25</v>
       </c>
       <c r="Z2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA2">
         <v>150</v>
@@ -1081,10 +1081,10 @@
         <v>65</v>
       </c>
       <c r="AJ2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL2">
         <v>30</v>
@@ -1093,34 +1093,34 @@
         <v>90</v>
       </c>
       <c r="AN2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO2">
         <v>70</v>
       </c>
       <c r="AP2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AQ2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AS2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT2">
         <v>9.800000000000001</v>
       </c>
       <c r="AU2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1129,34 +1129,34 @@
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BG2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2">
         <v>4.2</v>
       </c>
       <c r="BI2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ2">
         <v>9.6</v>
@@ -1174,22 +1174,22 @@
         <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP2">
         <v>10.5</v>
       </c>
       <c r="BQ2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BR2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS2">
         <v>16.5</v>
       </c>
       <c r="BT2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU2">
         <v>8.199999999999999</v>
@@ -1207,7 +1207,7 @@
         <v>32</v>
       </c>
       <c r="BZ2">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA2">
         <v>11.5</v>
@@ -1257,7 +1257,7 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O3">
         <v>1.42</v>
@@ -1266,7 +1266,7 @@
         <v>1.68</v>
       </c>
       <c r="Q3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R3">
         <v>1.24</v>
@@ -1475,22 +1475,22 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="G4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H4">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="I4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J4">
         <v>3.55</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L4">
         <v>1.3</v>
@@ -1502,16 +1502,16 @@
         <v>4.1</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
         <v>2.16</v>
       </c>
       <c r="Q4">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="R4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S4">
         <v>2.68</v>
@@ -1523,7 +1523,7 @@
         <v>2.2</v>
       </c>
       <c r="V4">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W4">
         <v>1.29</v>
@@ -1544,7 +1544,7 @@
         <v>18.5</v>
       </c>
       <c r="AC4">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD4">
         <v>18</v>
@@ -1559,7 +1559,7 @@
         <v>1000</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI4">
         <v>34</v>
@@ -1607,7 +1607,7 @@
         <v>11.5</v>
       </c>
       <c r="AX4">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -1616,22 +1616,22 @@
         <v>10.5</v>
       </c>
       <c r="BA4">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="BB4">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="BC4">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="BD4">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="BE4">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="BF4">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="BG4">
         <v>7.6</v>
@@ -1959,7 +1959,7 @@
         <v>116</v>
       </c>
       <c r="F6">
-        <v>2.92</v>
+        <v>1.41</v>
       </c>
       <c r="G6">
         <v>3.3</v>
@@ -1968,10 +1968,10 @@
         <v>2.48</v>
       </c>
       <c r="I6">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>1.43</v>
       </c>
       <c r="K6">
         <v>3.4</v>
@@ -2013,31 +2013,31 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE6">
         <v>65</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG6">
         <v>26</v>
@@ -2049,10 +2049,10 @@
         <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL6">
         <v>1000</v>
@@ -2061,64 +2061,64 @@
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP6">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="AQ6">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="AR6">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AS6">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="AT6">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="AU6">
-        <v>1.08</v>
+        <v>1.59</v>
       </c>
       <c r="AV6">
-        <v>1.08</v>
+        <v>1.63</v>
       </c>
       <c r="AW6">
-        <v>1.06</v>
+        <v>1.7</v>
       </c>
       <c r="AX6">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="AZ6">
-        <v>1.05</v>
+        <v>1.68</v>
       </c>
       <c r="BA6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB6">
-        <v>1.08</v>
+        <v>1.71</v>
       </c>
       <c r="BC6">
-        <v>1.08</v>
+        <v>1.69</v>
       </c>
       <c r="BD6">
-        <v>1.08</v>
+        <v>19</v>
       </c>
       <c r="BE6">
-        <v>1.08</v>
+        <v>1.74</v>
       </c>
       <c r="BF6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH6">
         <v>0</v>
@@ -2201,16 +2201,16 @@
         <v>117</v>
       </c>
       <c r="F7">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="G7">
         <v>3.15</v>
       </c>
       <c r="H7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J7">
         <v>2.54</v>
@@ -2255,46 +2255,46 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI7">
         <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL7">
         <v>1000</v>
@@ -2303,64 +2303,64 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="BA7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="BD7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="BF7">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH7">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>34</v>
       </c>
       <c r="AF8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG8">
         <v>13</v>
@@ -2533,7 +2533,7 @@
         <v>60</v>
       </c>
       <c r="AJ8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK8">
         <v>36</v>
@@ -2560,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="AS8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT8">
         <v>9.199999999999999</v>
@@ -2572,7 +2572,7 @@
         <v>11</v>
       </c>
       <c r="AW8">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX8">
         <v>15.5</v>
@@ -2584,7 +2584,7 @@
         <v>16</v>
       </c>
       <c r="BA8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB8">
         <v>38</v>
@@ -2593,13 +2593,13 @@
         <v>29</v>
       </c>
       <c r="BD8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF8">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="BG8">
         <v>27</v>
@@ -2685,19 +2685,19 @@
         <v>119</v>
       </c>
       <c r="F9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G9">
         <v>110</v>
       </c>
       <c r="H9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I9">
         <v>110</v>
       </c>
       <c r="J9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K9">
         <v>910</v>
@@ -2733,10 +2733,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3169,10 +3169,10 @@
         <v>121</v>
       </c>
       <c r="F11">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G11">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H11">
         <v>3.45</v>
@@ -3193,13 +3193,13 @@
         <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O11">
         <v>1.35</v>
       </c>
       <c r="P11">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q11">
         <v>2.06</v>
@@ -3274,7 +3274,7 @@
         <v>20</v>
       </c>
       <c r="AO11">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP11">
         <v>11.5</v>
@@ -3310,7 +3310,7 @@
         <v>16</v>
       </c>
       <c r="BA11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB11">
         <v>22</v>
@@ -3414,13 +3414,13 @@
         <v>3.85</v>
       </c>
       <c r="G12">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H12">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J12">
         <v>4.1</v>
@@ -3516,10 +3516,10 @@
         <v>32</v>
       </c>
       <c r="AO12">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AP12">
-        <v>22</v>
+        <v>4.9</v>
       </c>
       <c r="AQ12">
         <v>13</v>
@@ -3543,7 +3543,7 @@
         <v>14.5</v>
       </c>
       <c r="AX12">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AY12">
         <v>14.5</v>
@@ -3552,22 +3552,22 @@
         <v>13.5</v>
       </c>
       <c r="BA12">
+        <v>4.9</v>
+      </c>
+      <c r="BB12">
+        <v>5.4</v>
+      </c>
+      <c r="BC12">
         <v>5.2</v>
       </c>
-      <c r="BB12">
-        <v>5.8</v>
-      </c>
-      <c r="BC12">
-        <v>5.6</v>
-      </c>
       <c r="BD12">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BE12">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BF12">
-        <v>5.2</v>
+        <v>19</v>
       </c>
       <c r="BG12">
         <v>7.4</v>
@@ -3653,7 +3653,7 @@
         <v>123</v>
       </c>
       <c r="F13">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G13">
         <v>2.84</v>
@@ -3680,16 +3680,16 @@
         <v>2.72</v>
       </c>
       <c r="O13">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P13">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q13">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R13">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S13">
         <v>5.4</v>
@@ -3767,7 +3767,7 @@
         <v>7.8</v>
       </c>
       <c r="AR13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS13">
         <v>9.4</v>
@@ -3895,7 +3895,7 @@
         <v>124</v>
       </c>
       <c r="F14">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -3940,7 +3940,7 @@
         <v>1.67</v>
       </c>
       <c r="U14">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         <v>20</v>
       </c>
       <c r="AL14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM14">
         <v>85</v>
       </c>
       <c r="AN14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO14">
         <v>48</v>
@@ -4009,10 +4009,10 @@
         <v>15.5</v>
       </c>
       <c r="AR14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT14">
         <v>9.800000000000001</v>
@@ -4045,22 +4045,22 @@
         <v>17</v>
       </c>
       <c r="BD14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF14">
         <v>9.800000000000001</v>
       </c>
       <c r="BG14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH14">
         <v>3.9</v>
       </c>
       <c r="BI14">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ14">
         <v>10.5</v>
@@ -4078,7 +4078,7 @@
         <v>5</v>
       </c>
       <c r="BO14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP14">
         <v>15.5</v>
@@ -4090,7 +4090,7 @@
         <v>28</v>
       </c>
       <c r="BS14">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BT14">
         <v>7.6</v>
@@ -4105,7 +4105,7 @@
         <v>22</v>
       </c>
       <c r="BX14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY14">
         <v>27</v>
@@ -4114,7 +4114,7 @@
         <v>22</v>
       </c>
       <c r="CA14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CB14" t="s">
         <v>127</v>
@@ -4143,10 +4143,10 @@
         <v>2.8</v>
       </c>
       <c r="H15">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I15">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J15">
         <v>3.55</v>
@@ -4179,7 +4179,7 @@
         <v>3</v>
       </c>
       <c r="T15">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U15">
         <v>2.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
@@ -397,7 +397,7 @@
     <t>Deportivo Recoleta</t>
   </si>
   <si>
-    <t>2026-09-26 05:47:07</t>
+    <t>2026-09-26 08:06:11</t>
   </si>
 </sst>
 </file>
@@ -997,7 +997,7 @@
         <v>1.66</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
         <v>6.4</v>
@@ -1009,7 +1009,7 @@
         <v>4.9</v>
       </c>
       <c r="L2">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="M2">
         <v>1.04</v>
@@ -1021,16 +1021,16 @@
         <v>1.21</v>
       </c>
       <c r="P2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q2">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R2">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="S2">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T2">
         <v>1.73</v>
@@ -1039,7 +1039,7 @@
         <v>2.2</v>
       </c>
       <c r="V2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
         <v>2.5</v>
@@ -1153,64 +1153,64 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH2">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="BP2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="BT2">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BV2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>127</v>
@@ -1266,7 +1266,7 @@
         <v>1.68</v>
       </c>
       <c r="Q3">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R3">
         <v>1.24</v>
@@ -1281,7 +1281,7 @@
         <v>1.8</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
         <v>2</v>
@@ -1365,7 +1365,7 @@
         <v>2.1</v>
       </c>
       <c r="AX3">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AY3">
         <v>9.199999999999999</v>
@@ -1475,10 +1475,10 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="G4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H4">
         <v>1.86</v>
@@ -1487,10 +1487,10 @@
         <v>2.06</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>1.3</v>
@@ -1520,10 +1520,10 @@
         <v>1.62</v>
       </c>
       <c r="U4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V4">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W4">
         <v>1.29</v>
@@ -1577,7 +1577,7 @@
         <v>90</v>
       </c>
       <c r="AN4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO4">
         <v>19</v>
@@ -1598,7 +1598,7 @@
         <v>11</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
         <v>7.4</v>
@@ -1959,19 +1959,19 @@
         <v>116</v>
       </c>
       <c r="F6">
-        <v>1.41</v>
+        <v>2.74</v>
       </c>
       <c r="G6">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="H6">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="J6">
-        <v>1.43</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
         <v>3.4</v>
@@ -1989,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -2013,106 +2013,106 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="Y6">
+        <v>10</v>
+      </c>
+      <c r="Z6">
+        <v>19.5</v>
+      </c>
+      <c r="AA6">
+        <v>60</v>
+      </c>
+      <c r="AB6">
+        <v>10</v>
+      </c>
+      <c r="AC6">
+        <v>7.6</v>
+      </c>
+      <c r="AD6">
+        <v>15</v>
+      </c>
+      <c r="AE6">
+        <v>44</v>
+      </c>
+      <c r="AF6">
+        <v>19.5</v>
+      </c>
+      <c r="AG6">
+        <v>15</v>
+      </c>
+      <c r="AH6">
         <v>21</v>
       </c>
-      <c r="Z6">
-        <v>42</v>
-      </c>
-      <c r="AA6">
-        <v>80</v>
-      </c>
-      <c r="AB6">
-        <v>21</v>
-      </c>
-      <c r="AC6">
-        <v>18.5</v>
-      </c>
-      <c r="AD6">
-        <v>26</v>
-      </c>
-      <c r="AE6">
+      <c r="AI6">
         <v>65</v>
       </c>
-      <c r="AF6">
-        <v>42</v>
-      </c>
-      <c r="AG6">
-        <v>26</v>
-      </c>
-      <c r="AH6">
-        <v>48</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
       <c r="AJ6">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AK6">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN6">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AO6">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AP6">
-        <v>1.61</v>
+        <v>4.4</v>
       </c>
       <c r="AQ6">
-        <v>1.61</v>
+        <v>4.2</v>
       </c>
       <c r="AR6">
-        <v>1.67</v>
+        <v>5.3</v>
       </c>
       <c r="AS6">
-        <v>1.7</v>
+        <v>16.5</v>
       </c>
       <c r="AT6">
-        <v>1.61</v>
+        <v>4.2</v>
       </c>
       <c r="AU6">
-        <v>1.59</v>
+        <v>3.75</v>
       </c>
       <c r="AV6">
-        <v>1.63</v>
+        <v>4.9</v>
       </c>
       <c r="AW6">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX6">
-        <v>1.67</v>
+        <v>5.3</v>
       </c>
       <c r="AY6">
-        <v>1.63</v>
+        <v>4.9</v>
       </c>
       <c r="AZ6">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="BA6">
         <v>19</v>
       </c>
       <c r="BB6">
-        <v>1.71</v>
+        <v>19</v>
       </c>
       <c r="BC6">
-        <v>1.69</v>
+        <v>6.2</v>
       </c>
       <c r="BD6">
         <v>19</v>
       </c>
       <c r="BE6">
-        <v>1.74</v>
+        <v>7</v>
       </c>
       <c r="BF6">
         <v>15.5</v>
@@ -2201,160 +2201,160 @@
         <v>117</v>
       </c>
       <c r="F7">
-        <v>1.84</v>
+        <v>2.66</v>
       </c>
       <c r="G7">
+        <v>2.8</v>
+      </c>
+      <c r="H7">
+        <v>2.98</v>
+      </c>
+      <c r="I7">
+        <v>3.1</v>
+      </c>
+      <c r="J7">
         <v>3.15</v>
       </c>
-      <c r="H7">
-        <v>2.68</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>2.54</v>
-      </c>
       <c r="K7">
+        <v>3.4</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.72</v>
+      </c>
+      <c r="Q7">
+        <v>2.28</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1.93</v>
+      </c>
+      <c r="U7">
+        <v>1.98</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>12</v>
+      </c>
+      <c r="Y7">
+        <v>11</v>
+      </c>
+      <c r="Z7">
+        <v>20</v>
+      </c>
+      <c r="AA7">
+        <v>55</v>
+      </c>
+      <c r="AB7">
+        <v>10.5</v>
+      </c>
+      <c r="AC7">
+        <v>7.8</v>
+      </c>
+      <c r="AD7">
+        <v>14</v>
+      </c>
+      <c r="AE7">
+        <v>40</v>
+      </c>
+      <c r="AF7">
+        <v>18</v>
+      </c>
+      <c r="AG7">
+        <v>13</v>
+      </c>
+      <c r="AH7">
+        <v>19.5</v>
+      </c>
+      <c r="AI7">
+        <v>65</v>
+      </c>
+      <c r="AJ7">
+        <v>48</v>
+      </c>
+      <c r="AK7">
+        <v>36</v>
+      </c>
+      <c r="AL7">
+        <v>60</v>
+      </c>
+      <c r="AM7">
+        <v>140</v>
+      </c>
+      <c r="AN7">
+        <v>36</v>
+      </c>
+      <c r="AO7">
+        <v>40</v>
+      </c>
+      <c r="AP7">
+        <v>5</v>
+      </c>
+      <c r="AQ7">
         <v>4.8</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>1.25</v>
-      </c>
-      <c r="Q7">
-        <v>1.01</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>1.01</v>
-      </c>
-      <c r="U7">
-        <v>1.01</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>21</v>
-      </c>
-      <c r="Y7">
-        <v>21</v>
-      </c>
-      <c r="Z7">
-        <v>42</v>
-      </c>
-      <c r="AA7">
-        <v>85</v>
-      </c>
-      <c r="AB7">
-        <v>21</v>
-      </c>
-      <c r="AC7">
-        <v>18</v>
-      </c>
-      <c r="AD7">
-        <v>28</v>
-      </c>
-      <c r="AE7">
-        <v>65</v>
-      </c>
-      <c r="AF7">
-        <v>34</v>
-      </c>
-      <c r="AG7">
-        <v>26</v>
-      </c>
-      <c r="AH7">
-        <v>48</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>80</v>
-      </c>
-      <c r="AK7">
-        <v>60</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>60</v>
-      </c>
-      <c r="AO7">
-        <v>65</v>
-      </c>
-      <c r="AP7">
-        <v>1.63</v>
-      </c>
-      <c r="AQ7">
-        <v>1.63</v>
-      </c>
       <c r="AR7">
-        <v>1.69</v>
+        <v>6</v>
       </c>
       <c r="AS7">
-        <v>1.73</v>
+        <v>7.6</v>
       </c>
       <c r="AT7">
-        <v>1.63</v>
+        <v>4.7</v>
       </c>
       <c r="AU7">
-        <v>1.61</v>
+        <v>4.1</v>
       </c>
       <c r="AV7">
-        <v>1.66</v>
+        <v>5.4</v>
       </c>
       <c r="AW7">
-        <v>1.72</v>
+        <v>7.2</v>
       </c>
       <c r="AX7">
-        <v>1.68</v>
+        <v>5.9</v>
       </c>
       <c r="AY7">
-        <v>1.65</v>
+        <v>5.2</v>
       </c>
       <c r="AZ7">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="BA7">
         <v>20</v>
       </c>
       <c r="BB7">
-        <v>1.73</v>
+        <v>7.4</v>
       </c>
       <c r="BC7">
-        <v>1.71</v>
+        <v>7</v>
       </c>
       <c r="BD7">
         <v>20</v>
       </c>
       <c r="BE7">
-        <v>1.76</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7">
         <v>16.5</v>
@@ -2446,13 +2446,13 @@
         <v>2.76</v>
       </c>
       <c r="G8">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H8">
         <v>2.72</v>
       </c>
       <c r="I8">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J8">
         <v>3.35</v>
@@ -2957,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="Q10">
         <v>1.92</v>
@@ -3169,16 +3169,16 @@
         <v>121</v>
       </c>
       <c r="F11">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G11">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H11">
         <v>3.45</v>
       </c>
       <c r="I11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J11">
         <v>3.4</v>
@@ -3202,7 +3202,7 @@
         <v>1.88</v>
       </c>
       <c r="Q11">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U11">
         <v>2.1</v>
@@ -3307,13 +3307,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA11">
         <v>9.800000000000001</v>
       </c>
       <c r="BB11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC11">
         <v>21</v>
@@ -3411,22 +3411,22 @@
         <v>122</v>
       </c>
       <c r="F12">
+        <v>3.8</v>
+      </c>
+      <c r="G12">
         <v>3.85</v>
       </c>
-      <c r="G12">
-        <v>3.9</v>
-      </c>
       <c r="H12">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="I12">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="J12">
         <v>4.1</v>
       </c>
       <c r="K12">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3435,13 +3435,13 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O12">
         <v>1.18</v>
       </c>
       <c r="P12">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q12">
         <v>1.56</v>
@@ -3471,43 +3471,43 @@
         <v>15</v>
       </c>
       <c r="Z12">
+        <v>16</v>
+      </c>
+      <c r="AA12">
+        <v>23</v>
+      </c>
+      <c r="AB12">
+        <v>21</v>
+      </c>
+      <c r="AC12">
+        <v>10.5</v>
+      </c>
+      <c r="AD12">
+        <v>11.5</v>
+      </c>
+      <c r="AE12">
         <v>18</v>
       </c>
-      <c r="AA12">
-        <v>27</v>
-      </c>
-      <c r="AB12">
-        <v>26</v>
-      </c>
-      <c r="AC12">
-        <v>12.5</v>
-      </c>
-      <c r="AD12">
-        <v>12</v>
-      </c>
-      <c r="AE12">
-        <v>20</v>
-      </c>
       <c r="AF12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG12">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AH12">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ12">
         <v>80</v>
       </c>
       <c r="AK12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL12">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM12">
         <v>65</v>
@@ -3516,10 +3516,10 @@
         <v>32</v>
       </c>
       <c r="AO12">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AP12">
-        <v>4.9</v>
+        <v>23</v>
       </c>
       <c r="AQ12">
         <v>13</v>
@@ -3528,7 +3528,7 @@
         <v>13.5</v>
       </c>
       <c r="AS12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT12">
         <v>19</v>
@@ -3543,28 +3543,28 @@
         <v>14.5</v>
       </c>
       <c r="AX12">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AY12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ12">
         <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BB12">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="BC12">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD12">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12">
         <v>19</v>
@@ -3582,7 +3582,7 @@
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL12">
         <v>1000</v>
@@ -3653,16 +3653,16 @@
         <v>123</v>
       </c>
       <c r="F13">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="G13">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="H13">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="I13">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J13">
         <v>3.15</v>
@@ -3710,31 +3710,31 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z13">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA13">
         <v>60</v>
       </c>
       <c r="AB13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>7.2</v>
       </c>
       <c r="AD13">
+        <v>14</v>
+      </c>
+      <c r="AE13">
+        <v>48</v>
+      </c>
+      <c r="AF13">
+        <v>18.5</v>
+      </c>
+      <c r="AG13">
         <v>14.5</v>
-      </c>
-      <c r="AE13">
-        <v>50</v>
-      </c>
-      <c r="AF13">
-        <v>17.5</v>
-      </c>
-      <c r="AG13">
-        <v>14</v>
       </c>
       <c r="AH13">
         <v>24</v>
@@ -3746,7 +3746,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL13">
         <v>80</v>
@@ -3758,7 +3758,7 @@
         <v>55</v>
       </c>
       <c r="AO13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP13">
         <v>7.8</v>
@@ -3767,7 +3767,7 @@
         <v>7.8</v>
       </c>
       <c r="AR13">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS13">
         <v>9.4</v>
@@ -3779,10 +3779,10 @@
         <v>6.4</v>
       </c>
       <c r="AV13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX13">
         <v>15</v>
@@ -3794,25 +3794,25 @@
         <v>19</v>
       </c>
       <c r="BA13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB13">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC13">
         <v>9</v>
       </c>
       <c r="BD13">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BE13">
         <v>10.5</v>
       </c>
       <c r="BF13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG13">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH13">
         <v>2.9</v>
@@ -3854,7 +3854,7 @@
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV13">
         <v>1000</v>
@@ -3895,10 +3895,10 @@
         <v>124</v>
       </c>
       <c r="F14">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="H14">
         <v>3.85</v>
@@ -3910,7 +3910,7 @@
         <v>3.85</v>
       </c>
       <c r="K14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>55</v>
       </c>
       <c r="AF14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -3982,13 +3982,13 @@
         <v>17</v>
       </c>
       <c r="AI14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL14">
         <v>34</v>
@@ -3997,7 +3997,7 @@
         <v>85</v>
       </c>
       <c r="AN14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO14">
         <v>48</v>
@@ -4009,10 +4009,10 @@
         <v>15.5</v>
       </c>
       <c r="AR14">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AS14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT14">
         <v>9.800000000000001</v>
@@ -4045,16 +4045,16 @@
         <v>17</v>
       </c>
       <c r="BD14">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BE14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF14">
         <v>9.800000000000001</v>
       </c>
       <c r="BG14">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH14">
         <v>3.9</v>
@@ -4137,16 +4137,16 @@
         <v>125</v>
       </c>
       <c r="F15">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G15">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="H15">
+        <v>2.72</v>
+      </c>
+      <c r="I15">
         <v>2.76</v>
-      </c>
-      <c r="I15">
-        <v>2.8</v>
       </c>
       <c r="J15">
         <v>3.55</v>
@@ -4164,16 +4164,16 @@
         <v>4.4</v>
       </c>
       <c r="O15">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P15">
         <v>2.16</v>
       </c>
       <c r="Q15">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R15">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S15">
         <v>3</v>
@@ -4182,7 +4182,7 @@
         <v>1.65</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Y15">
         <v>13.5</v>
@@ -4290,7 +4290,7 @@
         <v>30</v>
       </c>
       <c r="BE15">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF15">
         <v>18</v>
@@ -4299,16 +4299,16 @@
         <v>18</v>
       </c>
       <c r="BH15">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI15">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="BJ15">
         <v>9.4</v>
       </c>
       <c r="BK15">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL15">
         <v>100</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
@@ -397,7 +397,7 @@
     <t>Deportivo Recoleta</t>
   </si>
   <si>
-    <t>2026-09-26 08:06:11</t>
+    <t>2026-09-26 10:24:44</t>
   </si>
 </sst>
 </file>
@@ -997,7 +997,7 @@
         <v>1.66</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
         <v>6.4</v>
@@ -1009,13 +1009,13 @@
         <v>4.9</v>
       </c>
       <c r="L2">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M2">
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O2">
         <v>1.21</v>
@@ -1024,13 +1024,13 @@
         <v>2.38</v>
       </c>
       <c r="Q2">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="R2">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S2">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="T2">
         <v>1.73</v>
@@ -1233,16 +1233,16 @@
         <v>113</v>
       </c>
       <c r="F3">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G3">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H3">
         <v>4.8</v>
       </c>
       <c r="I3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J3">
         <v>3.35</v>
@@ -1263,7 +1263,7 @@
         <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
         <v>2.32</v>
@@ -1284,7 +1284,7 @@
         <v>1.2</v>
       </c>
       <c r="W3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X3">
         <v>18</v>
@@ -1365,7 +1365,7 @@
         <v>2.1</v>
       </c>
       <c r="AX3">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AY3">
         <v>9.199999999999999</v>
@@ -1475,16 +1475,16 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="G4">
         <v>4.4</v>
       </c>
       <c r="H4">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="I4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J4">
         <v>3.85</v>
@@ -1499,7 +1499,7 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O4">
         <v>1.22</v>
@@ -1523,7 +1523,7 @@
         <v>2.22</v>
       </c>
       <c r="V4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="W4">
         <v>1.29</v>
@@ -1577,7 +1577,7 @@
         <v>90</v>
       </c>
       <c r="AN4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO4">
         <v>19</v>
@@ -1598,7 +1598,7 @@
         <v>11</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
         <v>7.4</v>
@@ -1959,16 +1959,16 @@
         <v>116</v>
       </c>
       <c r="F6">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="G6">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="H6">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="I6">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="J6">
         <v>3.35</v>
@@ -1992,7 +1992,7 @@
         <v>1.6</v>
       </c>
       <c r="Q6">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         <v>4.9</v>
       </c>
       <c r="AW6">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="AX6">
         <v>5.3</v>
@@ -2106,7 +2106,7 @@
         <v>19</v>
       </c>
       <c r="BC6">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="BD6">
         <v>19</v>
@@ -2201,22 +2201,22 @@
         <v>117</v>
       </c>
       <c r="F7">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="G7">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H7">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="I7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2231,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2243,10 +2243,10 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2255,10 +2255,10 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z7">
         <v>20</v>
@@ -2267,13 +2267,13 @@
         <v>55</v>
       </c>
       <c r="AB7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE7">
         <v>40</v>
@@ -2309,52 +2309,52 @@
         <v>40</v>
       </c>
       <c r="AP7">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ7">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AR7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS7">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AT7">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AU7">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AV7">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AW7">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX7">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AY7">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA7">
         <v>20</v>
       </c>
       <c r="BB7">
-        <v>7.4</v>
+        <v>17.5</v>
       </c>
       <c r="BC7">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BD7">
         <v>20</v>
       </c>
       <c r="BE7">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF7">
         <v>16.5</v>
@@ -2446,13 +2446,13 @@
         <v>2.76</v>
       </c>
       <c r="G8">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H8">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I8">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J8">
         <v>3.35</v>
@@ -2476,7 +2476,7 @@
         <v>1.78</v>
       </c>
       <c r="Q8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>60</v>
       </c>
       <c r="AJ8">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK8">
         <v>36</v>
@@ -2560,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="AS8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT8">
         <v>9.199999999999999</v>
@@ -2572,7 +2572,7 @@
         <v>11</v>
       </c>
       <c r="AW8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX8">
         <v>15.5</v>
@@ -2593,13 +2593,13 @@
         <v>29</v>
       </c>
       <c r="BD8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG8">
         <v>27</v>
@@ -2685,19 +2685,19 @@
         <v>119</v>
       </c>
       <c r="F9">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="G9">
         <v>110</v>
       </c>
       <c r="H9">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="I9">
         <v>110</v>
       </c>
       <c r="J9">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K9">
         <v>910</v>
@@ -2733,10 +2733,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2927,7 +2927,7 @@
         <v>120</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G10">
         <v>3.35</v>
@@ -2936,7 +2936,7 @@
         <v>2.42</v>
       </c>
       <c r="I10">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="J10">
         <v>3.4</v>
@@ -2957,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="Q10">
         <v>1.92</v>
@@ -3172,7 +3172,7 @@
         <v>2.24</v>
       </c>
       <c r="G11">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H11">
         <v>3.45</v>
@@ -3196,13 +3196,13 @@
         <v>3.6</v>
       </c>
       <c r="O11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P11">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q11">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3411,10 +3411,10 @@
         <v>122</v>
       </c>
       <c r="F12">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G12">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H12">
         <v>1.99</v>
@@ -3438,7 +3438,7 @@
         <v>5.9</v>
       </c>
       <c r="O12">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P12">
         <v>2.72</v>
@@ -3507,7 +3507,7 @@
         <v>46</v>
       </c>
       <c r="AL12">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM12">
         <v>65</v>
@@ -3519,7 +3519,7 @@
         <v>8.6</v>
       </c>
       <c r="AP12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ12">
         <v>13</v>
@@ -3531,7 +3531,7 @@
         <v>20</v>
       </c>
       <c r="AT12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU12">
         <v>9.199999999999999</v>
@@ -3543,7 +3543,7 @@
         <v>14.5</v>
       </c>
       <c r="AX12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY12">
         <v>14</v>
@@ -3552,19 +3552,19 @@
         <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC12">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD12">
         <v>8.199999999999999</v>
       </c>
       <c r="BE12">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF12">
         <v>19</v>
@@ -3653,16 +3653,16 @@
         <v>123</v>
       </c>
       <c r="F13">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="G13">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H13">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J13">
         <v>3.15</v>
@@ -3677,16 +3677,16 @@
         <v>1.12</v>
       </c>
       <c r="N13">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O13">
         <v>1.54</v>
       </c>
       <c r="P13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q13">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R13">
         <v>1.2</v>
@@ -3695,7 +3695,7 @@
         <v>5.4</v>
       </c>
       <c r="T13">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U13">
         <v>1.82</v>
@@ -3707,34 +3707,34 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y13">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA13">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC13">
         <v>7.2</v>
       </c>
       <c r="AD13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF13">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG13">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH13">
         <v>24</v>
@@ -3743,34 +3743,34 @@
         <v>70</v>
       </c>
       <c r="AJ13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK13">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL13">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM13">
         <v>200</v>
       </c>
       <c r="AN13">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO13">
         <v>55</v>
       </c>
       <c r="AP13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR13">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AS13">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT13">
         <v>7.6</v>
@@ -3782,10 +3782,10 @@
         <v>12</v>
       </c>
       <c r="AW13">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY13">
         <v>12</v>
@@ -3794,25 +3794,25 @@
         <v>19</v>
       </c>
       <c r="BA13">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB13">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="BC13">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD13">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE13">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF13">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BG13">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH13">
         <v>2.9</v>
@@ -3895,16 +3895,16 @@
         <v>124</v>
       </c>
       <c r="F14">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G14">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H14">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J14">
         <v>3.85</v>
@@ -3940,7 +3940,7 @@
         <v>1.67</v>
       </c>
       <c r="U14">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -4000,28 +4000,28 @@
         <v>11.5</v>
       </c>
       <c r="AO14">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ14">
         <v>15.5</v>
       </c>
       <c r="AR14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS14">
+        <v>10.5</v>
+      </c>
+      <c r="AT14">
         <v>10</v>
-      </c>
-      <c r="AT14">
-        <v>9.800000000000001</v>
       </c>
       <c r="AU14">
         <v>8.199999999999999</v>
       </c>
       <c r="AV14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW14">
         <v>32</v>
@@ -4045,10 +4045,10 @@
         <v>17</v>
       </c>
       <c r="BD14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF14">
         <v>9.800000000000001</v>
@@ -4137,16 +4137,16 @@
         <v>125</v>
       </c>
       <c r="F15">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G15">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H15">
         <v>2.72</v>
       </c>
       <c r="I15">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J15">
         <v>3.55</v>
@@ -4173,10 +4173,10 @@
         <v>1.84</v>
       </c>
       <c r="R15">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S15">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T15">
         <v>1.65</v>
@@ -4308,7 +4308,7 @@
         <v>9.4</v>
       </c>
       <c r="BK15">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL15">
         <v>100</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
@@ -397,7 +397,7 @@
     <t>Deportivo Recoleta</t>
   </si>
   <si>
-    <t>2026-09-26 10:24:44</t>
+    <t>2026-09-26 12:42:48</t>
   </si>
 </sst>
 </file>
@@ -994,13 +994,13 @@
         <v>1.58</v>
       </c>
       <c r="G2">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H2">
         <v>5.8</v>
       </c>
       <c r="I2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
         <v>4.3</v>
@@ -1009,31 +1009,31 @@
         <v>4.9</v>
       </c>
       <c r="L2">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M2">
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O2">
         <v>1.21</v>
       </c>
       <c r="P2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q2">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R2">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S2">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U2">
         <v>2.2</v>
@@ -1042,7 +1042,7 @@
         <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X2">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>11</v>
       </c>
       <c r="AD2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
         <v>75</v>
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="AQ2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR2">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS2">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AT2">
         <v>9.800000000000001</v>
@@ -1120,10 +1120,10 @@
         <v>20</v>
       </c>
       <c r="AW2">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AX2">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AY2">
         <v>9</v>
@@ -1132,7 +1132,7 @@
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB2">
         <v>13.5</v>
@@ -1141,76 +1141,76 @@
         <v>13.5</v>
       </c>
       <c r="BD2">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BF2">
         <v>6</v>
       </c>
       <c r="BG2">
+        <v>6.8</v>
+      </c>
+      <c r="BH2">
+        <v>4.2</v>
+      </c>
+      <c r="BI2">
+        <v>3.8</v>
+      </c>
+      <c r="BJ2">
         <v>9.800000000000001</v>
       </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>3.45</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
       <c r="BK2">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BO2">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ2">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS2">
+        <v>18</v>
+      </c>
+      <c r="BT2">
+        <v>9.6</v>
+      </c>
+      <c r="BU2">
+        <v>8.4</v>
+      </c>
+      <c r="BV2">
+        <v>48</v>
+      </c>
+      <c r="BW2">
+        <v>32</v>
+      </c>
+      <c r="BX2">
+        <v>48</v>
+      </c>
+      <c r="BY2">
+        <v>34</v>
+      </c>
+      <c r="BZ2">
+        <v>14.5</v>
+      </c>
+      <c r="CA2">
         <v>12</v>
-      </c>
-      <c r="BT2">
-        <v>1000</v>
-      </c>
-      <c r="BU2">
-        <v>6.8</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>1.01</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>1.01</v>
-      </c>
-      <c r="BZ2">
-        <v>1000</v>
-      </c>
-      <c r="CA2">
-        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>127</v>
@@ -1233,13 +1233,13 @@
         <v>113</v>
       </c>
       <c r="F3">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G3">
         <v>1.97</v>
       </c>
       <c r="H3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <v>5.9</v>
@@ -1263,7 +1263,7 @@
         <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q3">
         <v>2.32</v>
@@ -1314,7 +1314,7 @@
         <v>18</v>
       </c>
       <c r="AG3">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
         <v>1000</v>
@@ -1341,16 +1341,16 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AQ3">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AR3">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="AS3">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
@@ -1362,7 +1362,7 @@
         <v>17</v>
       </c>
       <c r="AW3">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AX3">
         <v>9</v>
@@ -1371,10 +1371,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="BA3">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="BB3">
         <v>17</v>
@@ -1383,16 +1383,16 @@
         <v>19</v>
       </c>
       <c r="BD3">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="BE3">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="BF3">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="BG3">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1475,22 +1475,22 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G4">
         <v>4.4</v>
       </c>
       <c r="H4">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="I4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J4">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L4">
         <v>1.3</v>
@@ -1499,34 +1499,34 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="Q4">
         <v>1.7</v>
       </c>
       <c r="R4">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S4">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T4">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U4">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="V4">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="W4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1541,16 +1541,16 @@
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC4">
         <v>9.6</v>
       </c>
       <c r="AD4">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF4">
         <v>36</v>
@@ -1592,22 +1592,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS4">
-        <v>17.5</v>
+        <v>2.4</v>
       </c>
       <c r="AT4">
         <v>11</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW4">
         <v>11.5</v>
       </c>
       <c r="AX4">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -1616,22 +1616,22 @@
         <v>10.5</v>
       </c>
       <c r="BA4">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="BB4">
-        <v>1.97</v>
+        <v>2.34</v>
       </c>
       <c r="BC4">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="BD4">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="BE4">
-        <v>1.97</v>
+        <v>2.34</v>
       </c>
       <c r="BF4">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="BG4">
         <v>7.6</v>
@@ -1726,7 +1726,7 @@
         <v>4.2</v>
       </c>
       <c r="I5">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J5">
         <v>3.6</v>
@@ -1735,16 +1735,16 @@
         <v>10.5</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5">
         <v>2.06</v>
@@ -1753,190 +1753,190 @@
         <v>1.5</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
         <v>127</v>
@@ -1959,19 +1959,19 @@
         <v>116</v>
       </c>
       <c r="F6">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G6">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H6">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I6">
         <v>2.86</v>
       </c>
       <c r="J6">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K6">
         <v>3.4</v>
@@ -1989,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q6">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U6">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -2016,31 +2016,31 @@
         <v>11</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Z6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AC6">
         <v>7.6</v>
       </c>
       <c r="AD6">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF6">
         <v>19.5</v>
       </c>
       <c r="AG6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH6">
         <v>21</v>
@@ -2064,40 +2064,40 @@
         <v>46</v>
       </c>
       <c r="AO6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP6">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ6">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS6">
         <v>16.5</v>
       </c>
       <c r="AT6">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AU6">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="AV6">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AW6">
         <v>16.5</v>
       </c>
       <c r="AX6">
-        <v>5.3</v>
+        <v>15.5</v>
       </c>
       <c r="AY6">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="AZ6">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA6">
         <v>19</v>
@@ -2112,7 +2112,7 @@
         <v>19</v>
       </c>
       <c r="BE6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF6">
         <v>15.5</v>
@@ -2204,19 +2204,19 @@
         <v>2.74</v>
       </c>
       <c r="G7">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="H7">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2243,10 +2243,10 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U7">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2309,37 +2309,37 @@
         <v>40</v>
       </c>
       <c r="AP7">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ7">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AR7">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AS7">
         <v>9</v>
       </c>
       <c r="AT7">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU7">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV7">
         <v>11</v>
       </c>
       <c r="AW7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX7">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="AY7">
         <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BA7">
         <v>20</v>
@@ -2348,7 +2348,7 @@
         <v>17.5</v>
       </c>
       <c r="BC7">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="BD7">
         <v>20</v>
@@ -2449,7 +2449,7 @@
         <v>2.96</v>
       </c>
       <c r="H8">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I8">
         <v>2.88</v>
@@ -2930,19 +2930,19 @@
         <v>3.1</v>
       </c>
       <c r="G10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H10">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I10">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q10">
         <v>1.92</v>
@@ -3175,7 +3175,7 @@
         <v>2.34</v>
       </c>
       <c r="H11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I11">
         <v>3.65</v>
@@ -3184,7 +3184,7 @@
         <v>3.4</v>
       </c>
       <c r="K11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>120</v>
       </c>
       <c r="AN11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO11">
         <v>48</v>
@@ -3286,7 +3286,7 @@
         <v>21</v>
       </c>
       <c r="AS11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT11">
         <v>8.4</v>
@@ -3298,7 +3298,7 @@
         <v>13</v>
       </c>
       <c r="AW11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX11">
         <v>12</v>
@@ -3307,10 +3307,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB11">
         <v>20</v>
@@ -3319,16 +3319,16 @@
         <v>21</v>
       </c>
       <c r="BD11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF11">
         <v>16.5</v>
       </c>
       <c r="BG11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH11">
         <v>0</v>
@@ -3411,16 +3411,16 @@
         <v>122</v>
       </c>
       <c r="F12">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G12">
         <v>3.9</v>
       </c>
       <c r="H12">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I12">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J12">
         <v>4.1</v>
@@ -3438,7 +3438,7 @@
         <v>5.9</v>
       </c>
       <c r="O12">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P12">
         <v>2.72</v>
@@ -3513,7 +3513,7 @@
         <v>65</v>
       </c>
       <c r="AN12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO12">
         <v>8.6</v>
@@ -3543,7 +3543,7 @@
         <v>14.5</v>
       </c>
       <c r="AX12">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY12">
         <v>14</v>
@@ -3552,19 +3552,19 @@
         <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB12">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE12">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF12">
         <v>19</v>
@@ -3713,7 +3713,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA13">
         <v>65</v>
@@ -3895,10 +3895,10 @@
         <v>124</v>
       </c>
       <c r="F14">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G14">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H14">
         <v>3.8</v>
@@ -3982,7 +3982,7 @@
         <v>17</v>
       </c>
       <c r="AI14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ14">
         <v>25</v>
@@ -3991,7 +3991,7 @@
         <v>21</v>
       </c>
       <c r="AL14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM14">
         <v>85</v>
@@ -4018,7 +4018,7 @@
         <v>10</v>
       </c>
       <c r="AU14">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV14">
         <v>14</v>
@@ -4137,16 +4137,16 @@
         <v>125</v>
       </c>
       <c r="F15">
+        <v>2.8</v>
+      </c>
+      <c r="G15">
         <v>2.82</v>
       </c>
-      <c r="G15">
-        <v>2.84</v>
-      </c>
       <c r="H15">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I15">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J15">
         <v>3.55</v>
@@ -4176,7 +4176,7 @@
         <v>1.45</v>
       </c>
       <c r="S15">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T15">
         <v>1.65</v>
@@ -4227,7 +4227,7 @@
         <v>38</v>
       </c>
       <c r="AJ15">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AK15">
         <v>30</v>
@@ -4290,7 +4290,7 @@
         <v>30</v>
       </c>
       <c r="BE15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF15">
         <v>18</v>
@@ -4305,13 +4305,13 @@
         <v>3.3</v>
       </c>
       <c r="BJ15">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK15">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM15">
         <v>65</v>
@@ -4326,7 +4326,7 @@
         <v>21</v>
       </c>
       <c r="BQ15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BR15">
         <v>32</v>
@@ -4344,7 +4344,7 @@
         <v>20</v>
       </c>
       <c r="BW15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX15">
         <v>30</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="188">
   <si>
     <t>League</t>
   </si>
@@ -463,6 +463,9 @@
     <t>America MG</t>
   </si>
   <si>
+    <t>Quindio</t>
+  </si>
+  <si>
     <t>Wanderers (Uru)</t>
   </si>
   <si>
@@ -568,10 +571,13 @@
     <t>Juventude</t>
   </si>
   <si>
+    <t>Bogota</t>
+  </si>
+  <si>
     <t>Albion FC</t>
   </si>
   <si>
-    <t>2026-09-27 18:45:44</t>
+    <t>2026-09-27 20:57:44</t>
   </si>
 </sst>
 </file>
@@ -903,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB36"/>
+  <dimension ref="A1:CB37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1162,25 +1168,25 @@
         <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F2">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="G2">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
         <v>8.6</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K2">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L2">
         <v>1.34</v>
@@ -1189,61 +1195,61 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q2">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S2">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T2">
         <v>2</v>
       </c>
       <c r="U2">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V2">
         <v>1.13</v>
       </c>
       <c r="W2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X2">
         <v>21</v>
       </c>
       <c r="Y2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AA2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC2">
         <v>11.5</v>
       </c>
       <c r="AD2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE2">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AF2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1252,43 +1258,43 @@
         <v>27</v>
       </c>
       <c r="AI2">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
         <v>12</v>
       </c>
       <c r="AK2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM2">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO2">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2">
         <v>23</v>
       </c>
       <c r="AR2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS2">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="AT2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV2">
         <v>26</v>
@@ -1300,16 +1306,16 @@
         <v>7.8</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC2">
         <v>13.5</v>
@@ -1318,31 +1324,31 @@
         <v>30</v>
       </c>
       <c r="BE2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="BF2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG2">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="BH2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI2">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>130</v>
       </c>
       <c r="BN2">
         <v>3.9</v>
@@ -1351,43 +1357,43 @@
         <v>3.55</v>
       </c>
       <c r="BP2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BQ2">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
         <v>25</v>
       </c>
       <c r="BS2">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
         <v>12.5</v>
       </c>
       <c r="BU2">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="BZ2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1404,133 +1410,133 @@
         <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F3">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="H3">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="I3">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O3">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P3">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q3">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T3">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="V3">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="W3">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z3">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA3">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB3">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AC3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AD3">
         <v>10</v>
       </c>
       <c r="AE3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF3">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AG3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AH3">
         <v>25</v>
       </c>
       <c r="AI3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ3">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AK3">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AL3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM3">
         <v>160</v>
       </c>
       <c r="AN3">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AO3">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ3">
         <v>7</v>
       </c>
       <c r="AR3">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AT3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AV3">
         <v>9.199999999999999</v>
@@ -1539,61 +1545,61 @@
         <v>16</v>
       </c>
       <c r="AX3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AY3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB3">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="BC3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BD3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BE3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BH3">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BI3">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.7</v>
+        <v>130</v>
       </c>
       <c r="BN3">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BO3">
-        <v>7.6</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
         <v>5.4</v>
@@ -1602,34 +1608,34 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT3">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BU3">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BV3">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BW3">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="CA3">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="CB3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1646,16 +1652,16 @@
         <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F4">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G4">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H4">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I4">
         <v>2.84</v>
@@ -1670,16 +1676,16 @@
         <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O4">
         <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q4">
         <v>1.79</v>
@@ -1691,43 +1697,43 @@
         <v>3</v>
       </c>
       <c r="T4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V4">
         <v>1.54</v>
       </c>
       <c r="W4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y4">
         <v>13</v>
       </c>
       <c r="Z4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB4">
         <v>13</v>
       </c>
       <c r="AC4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD4">
         <v>13</v>
       </c>
       <c r="AE4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG4">
         <v>12.5</v>
@@ -1736,43 +1742,43 @@
         <v>17</v>
       </c>
       <c r="AI4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ4">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL4">
         <v>38</v>
       </c>
       <c r="AM4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
         <v>17</v>
       </c>
       <c r="AS4">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AT4">
         <v>11</v>
       </c>
       <c r="AU4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV4">
         <v>11</v>
@@ -1781,7 +1787,7 @@
         <v>24</v>
       </c>
       <c r="AX4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY4">
         <v>10.5</v>
@@ -1790,7 +1796,7 @@
         <v>14.5</v>
       </c>
       <c r="BA4">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="BB4">
         <v>32</v>
@@ -1802,76 +1808,76 @@
         <v>25</v>
       </c>
       <c r="BE4">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="BF4">
         <v>17</v>
       </c>
       <c r="BG4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH4">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BI4">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BN4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO4">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP4">
         <v>23</v>
       </c>
       <c r="BQ4">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="BR4">
         <v>36</v>
       </c>
       <c r="BS4">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BT4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU4">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV4">
         <v>24</v>
       </c>
       <c r="BW4">
-        <v>15</v>
+        <v>4.6</v>
       </c>
       <c r="BX4">
         <v>36</v>
       </c>
       <c r="BY4">
-        <v>22</v>
+        <v>4.9</v>
       </c>
       <c r="BZ4">
         <v>26</v>
       </c>
       <c r="CA4">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1888,16 +1894,16 @@
         <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F5">
+        <v>1.57</v>
+      </c>
+      <c r="G5">
         <v>1.61</v>
       </c>
-      <c r="G5">
-        <v>1.62</v>
-      </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -1906,7 +1912,7 @@
         <v>4.3</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.35</v>
@@ -1921,10 +1927,10 @@
         <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R5">
         <v>1.48</v>
@@ -1933,16 +1939,16 @@
         <v>3</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V5">
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="X5">
         <v>19</v>
@@ -1954,31 +1960,31 @@
         <v>60</v>
       </c>
       <c r="AA5">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD5">
+        <v>25</v>
+      </c>
+      <c r="AE5">
+        <v>95</v>
+      </c>
+      <c r="AF5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG5">
         <v>9.6</v>
-      </c>
-      <c r="AC5">
-        <v>10</v>
-      </c>
-      <c r="AD5">
-        <v>24</v>
-      </c>
-      <c r="AE5">
-        <v>90</v>
-      </c>
-      <c r="AF5">
-        <v>10</v>
-      </c>
-      <c r="AG5">
-        <v>10</v>
       </c>
       <c r="AH5">
         <v>21</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
         <v>15.5</v>
@@ -1987,43 +1993,43 @@
         <v>16.5</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN5">
         <v>8</v>
       </c>
       <c r="AO5">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP5">
         <v>17</v>
       </c>
       <c r="AQ5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR5">
         <v>50</v>
       </c>
       <c r="AS5">
-        <v>70</v>
+        <v>16.5</v>
       </c>
       <c r="AT5">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5">
         <v>21</v>
       </c>
       <c r="AW5">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY5">
         <v>9</v>
@@ -2032,25 +2038,25 @@
         <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC5">
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE5">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="BF5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG5">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="BH5">
         <v>3.85</v>
@@ -2068,7 +2074,7 @@
         <v>120</v>
       </c>
       <c r="BM5">
-        <v>15.5</v>
+        <v>90</v>
       </c>
       <c r="BN5">
         <v>4.2</v>
@@ -2080,7 +2086,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR5">
         <v>23</v>
@@ -2092,7 +2098,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV5">
         <v>55</v>
@@ -2113,7 +2119,7 @@
         <v>8.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2130,22 +2136,22 @@
         <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F6">
+        <v>1.78</v>
+      </c>
+      <c r="G6">
         <v>1.82</v>
       </c>
-      <c r="G6">
-        <v>1.84</v>
-      </c>
       <c r="H6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I6">
         <v>5.7</v>
       </c>
       <c r="J6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
         <v>3.8</v>
@@ -2157,16 +2163,16 @@
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O6">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q6">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R6">
         <v>1.29</v>
@@ -2175,28 +2181,28 @@
         <v>4.2</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V6">
         <v>1.21</v>
       </c>
       <c r="W6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X6">
         <v>11.5</v>
       </c>
       <c r="Y6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
         <v>44</v>
       </c>
       <c r="AA6">
-        <v>180</v>
+        <v>630</v>
       </c>
       <c r="AB6">
         <v>7.4</v>
@@ -2205,13 +2211,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE6">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG6">
         <v>10.5</v>
@@ -2223,19 +2229,19 @@
         <v>110</v>
       </c>
       <c r="AJ6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK6">
         <v>22</v>
       </c>
       <c r="AL6">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM6">
         <v>170</v>
       </c>
       <c r="AN6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO6">
         <v>190</v>
@@ -2250,10 +2256,10 @@
         <v>36</v>
       </c>
       <c r="AS6">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="AT6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU6">
         <v>7.4</v>
@@ -2262,7 +2268,7 @@
         <v>19.5</v>
       </c>
       <c r="AW6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX6">
         <v>8.800000000000001</v>
@@ -2274,10 +2280,10 @@
         <v>21</v>
       </c>
       <c r="BA6">
-        <v>55</v>
+        <v>15.5</v>
       </c>
       <c r="BB6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC6">
         <v>19.5</v>
@@ -2292,70 +2298,70 @@
         <v>13</v>
       </c>
       <c r="BG6">
-        <v>75</v>
+        <v>15.5</v>
       </c>
       <c r="BH6">
         <v>3.5</v>
       </c>
       <c r="BI6">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6">
         <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="BN6">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO6">
         <v>3.8</v>
       </c>
       <c r="BP6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ6">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BR6">
         <v>36</v>
       </c>
       <c r="BS6">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BT6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU6">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="BV6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BW6">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BX6">
         <v>75</v>
       </c>
       <c r="BY6">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BZ6">
         <v>32</v>
       </c>
       <c r="CA6">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2372,25 +2378,25 @@
         <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F7">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>2.04</v>
+      </c>
+      <c r="I7">
+        <v>2.06</v>
+      </c>
+      <c r="J7">
         <v>3.85</v>
       </c>
-      <c r="H7">
-        <v>2.08</v>
-      </c>
-      <c r="I7">
-        <v>2.1</v>
-      </c>
-      <c r="J7">
-        <v>3.8</v>
-      </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L7">
         <v>1.35</v>
@@ -2417,16 +2423,16 @@
         <v>2.88</v>
       </c>
       <c r="T7">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U7">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V7">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="W7">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X7">
         <v>20</v>
@@ -2435,7 +2441,7 @@
         <v>11.5</v>
       </c>
       <c r="Z7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA7">
         <v>25</v>
@@ -2444,7 +2450,7 @@
         <v>18</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>11</v>
@@ -2453,10 +2459,10 @@
         <v>20</v>
       </c>
       <c r="AF7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH7">
         <v>16</v>
@@ -2465,19 +2471,19 @@
         <v>30</v>
       </c>
       <c r="AJ7">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM7">
         <v>75</v>
       </c>
       <c r="AN7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO7">
         <v>12</v>
@@ -2489,22 +2495,22 @@
         <v>10.5</v>
       </c>
       <c r="AR7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT7">
         <v>15.5</v>
       </c>
       <c r="AU7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX7">
         <v>26</v>
@@ -2519,7 +2525,7 @@
         <v>26</v>
       </c>
       <c r="BB7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BC7">
         <v>36</v>
@@ -2528,7 +2534,7 @@
         <v>38</v>
       </c>
       <c r="BE7">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="BF7">
         <v>29</v>
@@ -2540,7 +2546,7 @@
         <v>3.85</v>
       </c>
       <c r="BI7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ7">
         <v>9</v>
@@ -2552,7 +2558,7 @@
         <v>95</v>
       </c>
       <c r="BM7">
-        <v>14.5</v>
+        <v>75</v>
       </c>
       <c r="BN7">
         <v>7.2</v>
@@ -2564,13 +2570,13 @@
         <v>28</v>
       </c>
       <c r="BQ7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR7">
         <v>36</v>
       </c>
       <c r="BS7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT7">
         <v>5</v>
@@ -2582,7 +2588,7 @@
         <v>14</v>
       </c>
       <c r="BW7">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BX7">
         <v>26</v>
@@ -2591,13 +2597,13 @@
         <v>10.5</v>
       </c>
       <c r="BZ7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA7">
         <v>9.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2614,19 +2620,19 @@
         <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F8">
         <v>1.1</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H8">
         <v>1.1</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8">
         <v>1.1</v>
@@ -2656,7 +2662,7 @@
         <v>1.08</v>
       </c>
       <c r="S8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2665,10 +2671,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2839,7 +2845,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2856,25 +2862,25 @@
         <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F9">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G9">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H9">
         <v>3.5</v>
       </c>
       <c r="I9">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2883,13 +2889,13 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O9">
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q9">
         <v>1.61</v>
@@ -2910,7 +2916,7 @@
         <v>1.3</v>
       </c>
       <c r="W9">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="X9">
         <v>23</v>
@@ -2967,7 +2973,7 @@
         <v>44</v>
       </c>
       <c r="AP9">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="AQ9">
         <v>4.3</v>
@@ -2979,7 +2985,7 @@
         <v>5.1</v>
       </c>
       <c r="AT9">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU9">
         <v>7.4</v>
@@ -3006,7 +3012,7 @@
         <v>4.5</v>
       </c>
       <c r="BC9">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="BD9">
         <v>4.7</v>
@@ -3081,7 +3087,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3098,67 +3104,67 @@
         <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F10">
         <v>2.7</v>
       </c>
       <c r="G10">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H10">
         <v>3.05</v>
       </c>
       <c r="I10">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K10">
         <v>3.3</v>
       </c>
       <c r="L10">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P10">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Q10">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R10">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T10">
         <v>2.02</v>
       </c>
       <c r="U10">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V10">
         <v>1.47</v>
       </c>
       <c r="W10">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z10">
         <v>19</v>
@@ -3167,25 +3173,25 @@
         <v>55</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10">
         <v>7.2</v>
       </c>
       <c r="AD10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE10">
         <v>42</v>
       </c>
       <c r="AF10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG10">
         <v>13</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI10">
         <v>65</v>
@@ -3200,28 +3206,28 @@
         <v>60</v>
       </c>
       <c r="AM10">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO10">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ10">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS10">
         <v>46</v>
       </c>
       <c r="AT10">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU10">
         <v>6.6</v>
@@ -3239,46 +3245,46 @@
         <v>11.5</v>
       </c>
       <c r="AZ10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA10">
         <v>50</v>
       </c>
       <c r="BB10">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BC10">
         <v>30</v>
       </c>
       <c r="BD10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE10">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF10">
         <v>32</v>
       </c>
       <c r="BG10">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH10">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BI10">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BN10">
         <v>5.6</v>
@@ -3287,16 +3293,16 @@
         <v>4.9</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR10">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT10">
         <v>6</v>
@@ -3308,22 +3314,22 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3340,10 +3346,10 @@
         <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F11">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G11">
         <v>3.1</v>
@@ -3352,7 +3358,7 @@
         <v>2.7</v>
       </c>
       <c r="I11">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J11">
         <v>3.25</v>
@@ -3361,49 +3367,49 @@
         <v>3.3</v>
       </c>
       <c r="L11">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M11">
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P11">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q11">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T11">
         <v>1.99</v>
       </c>
       <c r="U11">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V11">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W11">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA11">
         <v>48</v>
@@ -3415,10 +3421,10 @@
         <v>7.2</v>
       </c>
       <c r="AD11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF11">
         <v>19</v>
@@ -3430,31 +3436,31 @@
         <v>20</v>
       </c>
       <c r="AI11">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK11">
+        <v>40</v>
+      </c>
+      <c r="AL11">
+        <v>60</v>
+      </c>
+      <c r="AM11">
+        <v>130</v>
+      </c>
+      <c r="AN11">
         <v>44</v>
-      </c>
-      <c r="AL11">
-        <v>65</v>
-      </c>
-      <c r="AM11">
-        <v>160</v>
-      </c>
-      <c r="AN11">
-        <v>48</v>
       </c>
       <c r="AO11">
         <v>34</v>
       </c>
       <c r="AP11">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR11">
         <v>14</v>
@@ -3475,7 +3481,7 @@
         <v>30</v>
       </c>
       <c r="AX11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY11">
         <v>12.5</v>
@@ -3487,40 +3493,40 @@
         <v>46</v>
       </c>
       <c r="BB11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BC11">
+        <v>12</v>
+      </c>
+      <c r="BD11">
+        <v>48</v>
+      </c>
+      <c r="BE11">
+        <v>15</v>
+      </c>
+      <c r="BF11">
         <v>36</v>
-      </c>
-      <c r="BD11">
-        <v>50</v>
-      </c>
-      <c r="BE11">
-        <v>14.5</v>
-      </c>
-      <c r="BF11">
-        <v>38</v>
       </c>
       <c r="BG11">
         <v>30</v>
       </c>
       <c r="BH11">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BI11">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="BJ11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN11">
         <v>6.8</v>
@@ -3529,7 +3535,7 @@
         <v>5.4</v>
       </c>
       <c r="BP11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ11">
         <v>6.8</v>
@@ -3538,16 +3544,16 @@
         <v>50</v>
       </c>
       <c r="BS11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT11">
         <v>5.7</v>
       </c>
       <c r="BU11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW11">
         <v>6.4</v>
@@ -3556,16 +3562,16 @@
         <v>46</v>
       </c>
       <c r="BY11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CA11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3582,22 +3588,22 @@
         <v>125</v>
       </c>
       <c r="E12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F12">
+        <v>2.84</v>
+      </c>
+      <c r="G12">
         <v>2.86</v>
       </c>
-      <c r="G12">
-        <v>2.9</v>
-      </c>
       <c r="H12">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I12">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K12">
         <v>3.4</v>
@@ -3609,16 +3615,16 @@
         <v>1.09</v>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O12">
         <v>1.4</v>
       </c>
       <c r="P12">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q12">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R12">
         <v>1.3</v>
@@ -3633,10 +3639,10 @@
         <v>2.04</v>
       </c>
       <c r="V12">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X12">
         <v>12</v>
@@ -3660,16 +3666,16 @@
         <v>13</v>
       </c>
       <c r="AE12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF12">
         <v>18</v>
       </c>
       <c r="AG12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH12">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI12">
         <v>50</v>
@@ -3684,7 +3690,7 @@
         <v>50</v>
       </c>
       <c r="AM12">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AN12">
         <v>34</v>
@@ -3735,10 +3741,10 @@
         <v>30</v>
       </c>
       <c r="BD12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE12">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF12">
         <v>29</v>
@@ -3762,7 +3768,7 @@
         <v>170</v>
       </c>
       <c r="BM12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN12">
         <v>5.8</v>
@@ -3771,7 +3777,7 @@
         <v>5.2</v>
       </c>
       <c r="BP12">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BQ12">
         <v>8.199999999999999</v>
@@ -3780,7 +3786,7 @@
         <v>46</v>
       </c>
       <c r="BS12">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT12">
         <v>5.8</v>
@@ -3792,22 +3798,22 @@
         <v>28</v>
       </c>
       <c r="BW12">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX12">
         <v>46</v>
       </c>
       <c r="BY12">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ12">
         <v>40</v>
       </c>
       <c r="CA12">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3824,7 +3830,7 @@
         <v>126</v>
       </c>
       <c r="E13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F13">
         <v>1.1</v>
@@ -3836,7 +3842,7 @@
         <v>1.1</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J13">
         <v>1.1</v>
@@ -3875,10 +3881,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4049,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4066,7 +4072,7 @@
         <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F14">
         <v>1.1</v>
@@ -4078,7 +4084,7 @@
         <v>1.1</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J14">
         <v>1.1</v>
@@ -4117,10 +4123,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4291,7 +4297,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4308,13 +4314,13 @@
         <v>128</v>
       </c>
       <c r="E15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F15">
         <v>1.1</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H15">
         <v>1.1</v>
@@ -4338,13 +4344,13 @@
         <v>1.1</v>
       </c>
       <c r="O15">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P15">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Q15">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="R15">
         <v>1.08</v>
@@ -4359,10 +4365,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4533,7 +4539,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4550,22 +4556,22 @@
         <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F16">
-        <v>1.26</v>
+        <v>1.59</v>
       </c>
       <c r="G16">
         <v>970</v>
       </c>
       <c r="H16">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I16">
         <v>970</v>
       </c>
       <c r="J16">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="K16">
         <v>910</v>
@@ -4601,10 +4607,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W16">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4775,7 +4781,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4792,7 +4798,7 @@
         <v>130</v>
       </c>
       <c r="E17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F17">
         <v>1.1</v>
@@ -4819,16 +4825,16 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="O17">
         <v>1.32</v>
       </c>
       <c r="P17">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Q17">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R17">
         <v>1.08</v>
@@ -4843,10 +4849,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5017,7 +5023,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5034,7 +5040,7 @@
         <v>131</v>
       </c>
       <c r="E18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F18">
         <v>1.1</v>
@@ -5046,7 +5052,7 @@
         <v>1.1</v>
       </c>
       <c r="I18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J18">
         <v>1.1</v>
@@ -5085,10 +5091,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5259,7 +5265,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5276,19 +5282,19 @@
         <v>132</v>
       </c>
       <c r="E19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F19">
         <v>1.1</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H19">
         <v>1.1</v>
       </c>
       <c r="I19">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="J19">
         <v>1.1</v>
@@ -5327,10 +5333,10 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5501,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5518,19 +5524,19 @@
         <v>133</v>
       </c>
       <c r="E20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F20">
         <v>1.1</v>
       </c>
       <c r="G20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H20">
         <v>1.1</v>
       </c>
       <c r="I20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J20">
         <v>1.1</v>
@@ -5569,10 +5575,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5743,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5760,19 +5766,19 @@
         <v>134</v>
       </c>
       <c r="E21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F21">
         <v>1.1</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H21">
         <v>1.1</v>
       </c>
       <c r="I21">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J21">
         <v>1.1</v>
@@ -5811,10 +5817,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5985,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6002,28 +6008,28 @@
         <v>135</v>
       </c>
       <c r="E22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F22">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G22">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H22">
         <v>2.36</v>
       </c>
       <c r="I22">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J22">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K22">
         <v>3.55</v>
       </c>
       <c r="L22">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M22">
         <v>1.07</v>
@@ -6038,13 +6044,13 @@
         <v>1.98</v>
       </c>
       <c r="Q22">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R22">
         <v>1.37</v>
       </c>
       <c r="S22">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T22">
         <v>1.76</v>
@@ -6053,22 +6059,22 @@
         <v>2.22</v>
       </c>
       <c r="V22">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W22">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X22">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y22">
         <v>11</v>
       </c>
       <c r="Z22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA22">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB22">
         <v>13.5</v>
@@ -6077,55 +6083,55 @@
         <v>7.8</v>
       </c>
       <c r="AD22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE22">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG22">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH22">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ22">
         <v>65</v>
       </c>
       <c r="AK22">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL22">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM22">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN22">
         <v>36</v>
       </c>
       <c r="AO22">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP22">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ22">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS22">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AT22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU22">
         <v>7.2</v>
@@ -6137,37 +6143,37 @@
         <v>22</v>
       </c>
       <c r="AX22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY22">
         <v>12.5</v>
       </c>
       <c r="AZ22">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA22">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="BB22">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BC22">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BD22">
-        <v>26</v>
+        <v>12.5</v>
       </c>
       <c r="BE22">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="BF22">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BG22">
         <v>16.5</v>
       </c>
       <c r="BH22">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI22">
         <v>3.15</v>
@@ -6212,7 +6218,7 @@
         <v>18</v>
       </c>
       <c r="BW22">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX22">
         <v>32</v>
@@ -6227,7 +6233,7 @@
         <v>9</v>
       </c>
       <c r="CB22" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6244,16 +6250,16 @@
         <v>136</v>
       </c>
       <c r="E23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F23">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G23">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H23">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I23">
         <v>2.82</v>
@@ -6262,7 +6268,7 @@
         <v>3.6</v>
       </c>
       <c r="K23">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L23">
         <v>1.36</v>
@@ -6277,10 +6283,10 @@
         <v>1.25</v>
       </c>
       <c r="P23">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q23">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R23">
         <v>1.48</v>
@@ -6289,10 +6295,10 @@
         <v>2.92</v>
       </c>
       <c r="T23">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U23">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V23">
         <v>1.54</v>
@@ -6307,19 +6313,19 @@
         <v>14.5</v>
       </c>
       <c r="Z23">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA23">
         <v>42</v>
       </c>
       <c r="AB23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC23">
         <v>8.199999999999999</v>
       </c>
       <c r="AD23">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE23">
         <v>27</v>
@@ -6352,19 +6358,19 @@
         <v>19</v>
       </c>
       <c r="AO23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP23">
         <v>16</v>
       </c>
       <c r="AQ23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR23">
         <v>18.5</v>
       </c>
       <c r="AS23">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT23">
         <v>12.5</v>
@@ -6373,7 +6379,7 @@
         <v>7.8</v>
       </c>
       <c r="AV23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW23">
         <v>25</v>
@@ -6397,34 +6403,34 @@
         <v>25</v>
       </c>
       <c r="BD23">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE23">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH23">
         <v>3.8</v>
       </c>
       <c r="BI23">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ23">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK23">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM23">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="BN23">
         <v>5.9</v>
@@ -6433,13 +6439,13 @@
         <v>5.3</v>
       </c>
       <c r="BP23">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BR23">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS23">
         <v>20</v>
@@ -6460,7 +6466,7 @@
         <v>30</v>
       </c>
       <c r="BY23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -6469,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6486,7 +6492,7 @@
         <v>137</v>
       </c>
       <c r="E24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F24">
         <v>2.3</v>
@@ -6507,13 +6513,13 @@
         <v>3.55</v>
       </c>
       <c r="L24">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M24">
         <v>1.08</v>
       </c>
       <c r="N24">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O24">
         <v>1.37</v>
@@ -6531,7 +6537,7 @@
         <v>3.9</v>
       </c>
       <c r="T24">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U24">
         <v>2.08</v>
@@ -6564,7 +6570,7 @@
         <v>15</v>
       </c>
       <c r="AE24">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF24">
         <v>14</v>
@@ -6597,7 +6603,7 @@
         <v>48</v>
       </c>
       <c r="AP24">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ24">
         <v>11.5</v>
@@ -6627,7 +6633,7 @@
         <v>10</v>
       </c>
       <c r="AZ24">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA24">
         <v>46</v>
@@ -6684,7 +6690,7 @@
         <v>34</v>
       </c>
       <c r="BS24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BT24">
         <v>6.8</v>
@@ -6696,22 +6702,22 @@
         <v>32</v>
       </c>
       <c r="BW24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BX24">
         <v>44</v>
       </c>
       <c r="BY24">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BZ24">
         <v>32</v>
       </c>
       <c r="CA24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CB24" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6728,13 +6734,13 @@
         <v>138</v>
       </c>
       <c r="E25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F25">
+        <v>3.9</v>
+      </c>
+      <c r="G25">
         <v>3.95</v>
-      </c>
-      <c r="G25">
-        <v>4</v>
       </c>
       <c r="H25">
         <v>1.98</v>
@@ -6743,10 +6749,10 @@
         <v>1.99</v>
       </c>
       <c r="J25">
+        <v>4</v>
+      </c>
+      <c r="K25">
         <v>4.1</v>
-      </c>
-      <c r="K25">
-        <v>4.2</v>
       </c>
       <c r="L25">
         <v>1.29</v>
@@ -6761,7 +6767,7 @@
         <v>1.17</v>
       </c>
       <c r="P25">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q25">
         <v>1.55</v>
@@ -6770,13 +6776,13 @@
         <v>1.69</v>
       </c>
       <c r="S25">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T25">
         <v>1.53</v>
       </c>
       <c r="U25">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="V25">
         <v>2</v>
@@ -6785,7 +6791,7 @@
         <v>1.33</v>
       </c>
       <c r="X25">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y25">
         <v>14.5</v>
@@ -6836,7 +6842,7 @@
         <v>26</v>
       </c>
       <c r="AO25">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP25">
         <v>24</v>
@@ -6845,7 +6851,7 @@
         <v>13.5</v>
       </c>
       <c r="AR25">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS25">
         <v>21</v>
@@ -6854,13 +6860,13 @@
         <v>21</v>
       </c>
       <c r="AU25">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV25">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW25">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX25">
         <v>32</v>
@@ -6884,7 +6890,7 @@
         <v>34</v>
       </c>
       <c r="BE25">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF25">
         <v>23</v>
@@ -6893,7 +6899,7 @@
         <v>8</v>
       </c>
       <c r="BH25">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI25">
         <v>4.1</v>
@@ -6935,7 +6941,7 @@
         <v>4.7</v>
       </c>
       <c r="BV25">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW25">
         <v>11</v>
@@ -6953,7 +6959,7 @@
         <v>10</v>
       </c>
       <c r="CB25" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6970,19 +6976,19 @@
         <v>139</v>
       </c>
       <c r="E26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F26">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G26">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
         <v>3.05</v>
-      </c>
-      <c r="I26">
-        <v>3.1</v>
       </c>
       <c r="J26">
         <v>3.1</v>
@@ -7015,31 +7021,31 @@
         <v>5.4</v>
       </c>
       <c r="T26">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U26">
         <v>1.83</v>
       </c>
       <c r="V26">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W26">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X26">
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA26">
         <v>55</v>
       </c>
       <c r="AB26">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC26">
         <v>7</v>
@@ -7048,7 +7054,7 @@
         <v>14.5</v>
       </c>
       <c r="AE26">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF26">
         <v>16.5</v>
@@ -7063,7 +7069,7 @@
         <v>75</v>
       </c>
       <c r="AJ26">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK26">
         <v>40</v>
@@ -7081,16 +7087,16 @@
         <v>65</v>
       </c>
       <c r="AP26">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ26">
         <v>8.6</v>
       </c>
       <c r="AR26">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS26">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AT26">
         <v>8</v>
@@ -7123,19 +7129,19 @@
         <v>34</v>
       </c>
       <c r="BD26">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE26">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BF26">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG26">
         <v>46</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="BI26">
         <v>2.34</v>
@@ -7144,58 +7150,58 @@
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BT26">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="CB26" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7212,34 +7218,34 @@
         <v>140</v>
       </c>
       <c r="E27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F27">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G27">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H27">
         <v>3.5</v>
       </c>
       <c r="I27">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J27">
         <v>3.7</v>
       </c>
       <c r="K27">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L27">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M27">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N27">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O27">
         <v>1.26</v>
@@ -7254,16 +7260,16 @@
         <v>1.47</v>
       </c>
       <c r="S27">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T27">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U27">
         <v>2.42</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W27">
         <v>1.8</v>
@@ -7284,7 +7290,7 @@
         <v>12</v>
       </c>
       <c r="AC27">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27">
         <v>14</v>
@@ -7308,13 +7314,13 @@
         <v>27</v>
       </c>
       <c r="AK27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM27">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN27">
         <v>14</v>
@@ -7338,7 +7344,7 @@
         <v>11</v>
       </c>
       <c r="AU27">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV27">
         <v>13</v>
@@ -7359,7 +7365,7 @@
         <v>38</v>
       </c>
       <c r="BB27">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC27">
         <v>19</v>
@@ -7371,7 +7377,7 @@
         <v>50</v>
       </c>
       <c r="BF27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG27">
         <v>28</v>
@@ -7398,37 +7404,37 @@
         <v>5.2</v>
       </c>
       <c r="BO27">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP27">
         <v>15</v>
       </c>
       <c r="BQ27">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BR27">
         <v>25</v>
       </c>
       <c r="BS27">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BT27">
         <v>7</v>
       </c>
       <c r="BU27">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV27">
         <v>26</v>
       </c>
       <c r="BW27">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BX27">
         <v>34</v>
       </c>
       <c r="BY27">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BZ27">
         <v>19.5</v>
@@ -7437,7 +7443,7 @@
         <v>14.5</v>
       </c>
       <c r="CB27" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7454,16 +7460,16 @@
         <v>141</v>
       </c>
       <c r="E28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F28">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H28">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I28">
         <v>4.5</v>
@@ -7487,22 +7493,22 @@
         <v>1.32</v>
       </c>
       <c r="P28">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q28">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R28">
         <v>1.32</v>
       </c>
       <c r="S28">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T28">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U28">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V28">
         <v>1.28</v>
@@ -7511,10 +7517,10 @@
         <v>2</v>
       </c>
       <c r="X28">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y28">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z28">
         <v>36</v>
@@ -7523,154 +7529,154 @@
         <v>110</v>
       </c>
       <c r="AB28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD28">
+        <v>18.5</v>
+      </c>
+      <c r="AE28">
+        <v>65</v>
+      </c>
+      <c r="AF28">
+        <v>12.5</v>
+      </c>
+      <c r="AG28">
+        <v>11</v>
+      </c>
+      <c r="AH28">
+        <v>21</v>
+      </c>
+      <c r="AI28">
+        <v>70</v>
+      </c>
+      <c r="AJ28">
+        <v>24</v>
+      </c>
+      <c r="AK28">
+        <v>23</v>
+      </c>
+      <c r="AL28">
+        <v>40</v>
+      </c>
+      <c r="AM28">
+        <v>120</v>
+      </c>
+      <c r="AN28">
+        <v>15.5</v>
+      </c>
+      <c r="AO28">
+        <v>75</v>
+      </c>
+      <c r="AP28">
+        <v>11.5</v>
+      </c>
+      <c r="AQ28">
+        <v>13</v>
+      </c>
+      <c r="AR28">
+        <v>28</v>
+      </c>
+      <c r="AS28">
+        <v>80</v>
+      </c>
+      <c r="AT28">
+        <v>7.6</v>
+      </c>
+      <c r="AU28">
+        <v>7.4</v>
+      </c>
+      <c r="AV28">
+        <v>15</v>
+      </c>
+      <c r="AW28">
+        <v>46</v>
+      </c>
+      <c r="AX28">
         <v>10</v>
       </c>
-      <c r="AC28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD28">
-        <v>20</v>
-      </c>
-      <c r="AE28">
-        <v>70</v>
-      </c>
-      <c r="AF28">
-        <v>14</v>
-      </c>
-      <c r="AG28">
+      <c r="AY28">
+        <v>9</v>
+      </c>
+      <c r="AZ28">
+        <v>16.5</v>
+      </c>
+      <c r="BA28">
+        <v>50</v>
+      </c>
+      <c r="BB28">
+        <v>19.5</v>
+      </c>
+      <c r="BC28">
+        <v>18</v>
+      </c>
+      <c r="BD28">
+        <v>30</v>
+      </c>
+      <c r="BE28">
+        <v>85</v>
+      </c>
+      <c r="BF28">
         <v>12</v>
-      </c>
-      <c r="AH28">
-        <v>24</v>
-      </c>
-      <c r="AI28">
-        <v>80</v>
-      </c>
-      <c r="AJ28">
-        <v>27</v>
-      </c>
-      <c r="AK28">
-        <v>25</v>
-      </c>
-      <c r="AL28">
-        <v>46</v>
-      </c>
-      <c r="AM28">
-        <v>130</v>
-      </c>
-      <c r="AN28">
-        <v>19</v>
-      </c>
-      <c r="AO28">
-        <v>80</v>
-      </c>
-      <c r="AP28">
-        <v>9.6</v>
-      </c>
-      <c r="AQ28">
-        <v>12</v>
-      </c>
-      <c r="AR28">
-        <v>24</v>
-      </c>
-      <c r="AS28">
-        <v>44</v>
-      </c>
-      <c r="AT28">
-        <v>6.8</v>
-      </c>
-      <c r="AU28">
-        <v>6.4</v>
-      </c>
-      <c r="AV28">
-        <v>13.5</v>
-      </c>
-      <c r="AW28">
-        <v>40</v>
-      </c>
-      <c r="AX28">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY28">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ28">
-        <v>14.5</v>
-      </c>
-      <c r="BA28">
-        <v>34</v>
-      </c>
-      <c r="BB28">
-        <v>17.5</v>
-      </c>
-      <c r="BC28">
-        <v>16</v>
-      </c>
-      <c r="BD28">
-        <v>28</v>
-      </c>
-      <c r="BE28">
-        <v>42</v>
-      </c>
-      <c r="BF28">
-        <v>11</v>
       </c>
       <c r="BG28">
         <v>40</v>
       </c>
       <c r="BH28">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL28">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM28">
         <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ28">
         <v>0</v>
@@ -7679,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7696,40 +7702,40 @@
         <v>142</v>
       </c>
       <c r="E29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F29">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G29">
         <v>3.1</v>
       </c>
       <c r="H29">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I29">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J29">
         <v>3.35</v>
       </c>
       <c r="K29">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L29">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M29">
         <v>1.07</v>
       </c>
       <c r="N29">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O29">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P29">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="Q29">
         <v>1.91</v>
@@ -7738,16 +7744,16 @@
         <v>1.36</v>
       </c>
       <c r="S29">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T29">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U29">
         <v>2.16</v>
       </c>
       <c r="V29">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W29">
         <v>1.47</v>
@@ -7828,7 +7834,7 @@
         <v>10</v>
       </c>
       <c r="AW29">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="AX29">
         <v>18</v>
@@ -7840,13 +7846,13 @@
         <v>14.5</v>
       </c>
       <c r="BA29">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB29">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC29">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD29">
         <v>7.2</v>
@@ -7864,19 +7870,19 @@
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BJ29">
         <v>13</v>
       </c>
       <c r="BK29">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BN29">
         <v>8.6</v>
@@ -7885,16 +7891,16 @@
         <v>4.2</v>
       </c>
       <c r="BP29">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ29">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BR29">
         <v>46</v>
       </c>
       <c r="BS29">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="BT29">
         <v>7.4</v>
@@ -7903,25 +7909,25 @@
         <v>4.1</v>
       </c>
       <c r="BV29">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW29">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BX29">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY29">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="BZ29">
         <v>36</v>
       </c>
       <c r="CA29">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CB29" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7938,22 +7944,22 @@
         <v>143</v>
       </c>
       <c r="E30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F30">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="G30">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="H30">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="I30">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K30">
         <v>3.25</v>
@@ -7965,94 +7971,94 @@
         <v>1.12</v>
       </c>
       <c r="N30">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="O30">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P30">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q30">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R30">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S30">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T30">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U30">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V30">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="X30">
         <v>9.4</v>
       </c>
       <c r="Y30">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z30">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA30">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC30">
         <v>7.4</v>
       </c>
       <c r="AD30">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AE30">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AF30">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG30">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH30">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI30">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ30">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AK30">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AL30">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AM30">
         <v>190</v>
       </c>
       <c r="AN30">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AO30">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP30">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR30">
         <v>1.01</v>
@@ -8061,43 +8067,43 @@
         <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU30">
         <v>6.4</v>
       </c>
       <c r="AV30">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW30">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AY30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ30">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA30">
         <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
         <v>1.01</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BE30">
         <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
         <v>1.01</v>
@@ -8163,7 +8169,7 @@
         <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8180,25 +8186,25 @@
         <v>144</v>
       </c>
       <c r="E31" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F31">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G31">
-        <v>110</v>
+        <v>2.32</v>
       </c>
       <c r="H31">
-        <v>1.28</v>
+        <v>3.75</v>
       </c>
       <c r="I31">
-        <v>110</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J31">
-        <v>1.15</v>
+        <v>3.2</v>
       </c>
       <c r="K31">
-        <v>110</v>
+        <v>4.9</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8231,10 +8237,10 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="W31">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8294,37 +8300,37 @@
         <v>1.01</v>
       </c>
       <c r="AQ31">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="AR31">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS31">
+        <v>1.01</v>
+      </c>
+      <c r="AT31">
+        <v>1.01</v>
+      </c>
+      <c r="AU31">
+        <v>1.01</v>
+      </c>
+      <c r="AV31">
+        <v>1.01</v>
+      </c>
+      <c r="AW31">
         <v>24</v>
       </c>
-      <c r="AT31">
-        <v>1.01</v>
-      </c>
-      <c r="AU31">
-        <v>1.01</v>
-      </c>
-      <c r="AV31">
-        <v>12</v>
-      </c>
-      <c r="AW31">
-        <v>1.01</v>
-      </c>
       <c r="AX31">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="AY31">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ31">
-        <v>16</v>
+        <v>1.98</v>
       </c>
       <c r="BA31">
-        <v>32</v>
+        <v>2.1</v>
       </c>
       <c r="BB31">
         <v>1.01</v>
@@ -8336,7 +8342,7 @@
         <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>19.5</v>
+        <v>1.98</v>
       </c>
       <c r="BF31">
         <v>1.01</v>
@@ -8405,7 +8411,7 @@
         <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8422,37 +8428,37 @@
         <v>145</v>
       </c>
       <c r="E32" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F32">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G32">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H32">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I32">
         <v>8.199999999999999</v>
       </c>
       <c r="J32">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K32">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M32">
         <v>1.07</v>
       </c>
       <c r="N32">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O32">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P32">
         <v>1.84</v>
@@ -8461,7 +8467,7 @@
         <v>2.02</v>
       </c>
       <c r="R32">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S32">
         <v>3.7</v>
@@ -8470,46 +8476,46 @@
         <v>1.89</v>
       </c>
       <c r="U32">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V32">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W32">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="X32">
         <v>16.5</v>
       </c>
       <c r="Y32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z32">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA32">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AB32">
         <v>7.4</v>
       </c>
       <c r="AC32">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD32">
         <v>34</v>
       </c>
       <c r="AE32">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF32">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG32">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH32">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AI32">
         <v>140</v>
@@ -8524,13 +8530,13 @@
         <v>55</v>
       </c>
       <c r="AM32">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN32">
         <v>12</v>
       </c>
       <c r="AO32">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AP32">
         <v>11.5</v>
@@ -8539,10 +8545,10 @@
         <v>17.5</v>
       </c>
       <c r="AR32">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS32">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT32">
         <v>6.4</v>
@@ -8551,10 +8557,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV32">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="AW32">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AX32">
         <v>7.6</v>
@@ -8563,28 +8569,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ32">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="BA32">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BB32">
         <v>12.5</v>
       </c>
       <c r="BC32">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD32">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BE32">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF32">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG32">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8647,7 +8653,7 @@
         <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8664,19 +8670,19 @@
         <v>146</v>
       </c>
       <c r="E33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F33">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G33">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H33">
         <v>2.46</v>
       </c>
       <c r="I33">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J33">
         <v>3.35</v>
@@ -8691,19 +8697,19 @@
         <v>1.07</v>
       </c>
       <c r="N33">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O33">
         <v>1.34</v>
       </c>
       <c r="P33">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q33">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S33">
         <v>3.55</v>
@@ -8715,7 +8721,7 @@
         <v>2.14</v>
       </c>
       <c r="V33">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
         <v>1.45</v>
@@ -8790,7 +8796,7 @@
         <v>10.5</v>
       </c>
       <c r="AU33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV33">
         <v>10.5</v>
@@ -8808,13 +8814,13 @@
         <v>15</v>
       </c>
       <c r="BA33">
+        <v>5</v>
+      </c>
+      <c r="BB33">
+        <v>5.1</v>
+      </c>
+      <c r="BC33">
         <v>4.9</v>
-      </c>
-      <c r="BB33">
-        <v>5</v>
-      </c>
-      <c r="BC33">
-        <v>4.8</v>
       </c>
       <c r="BD33">
         <v>5</v>
@@ -8832,37 +8838,37 @@
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="BJ33">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK33">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="BN33">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BO33">
         <v>4.5</v>
       </c>
       <c r="BP33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ33">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="BR33">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS33">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BT33">
         <v>7.8</v>
@@ -8874,22 +8880,22 @@
         <v>26</v>
       </c>
       <c r="BW33">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="BX33">
         <v>48</v>
       </c>
       <c r="BY33">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BZ33">
         <v>40</v>
       </c>
       <c r="CA33">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="CB33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8906,46 +8912,46 @@
         <v>147</v>
       </c>
       <c r="E34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F34">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G34">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="H34">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="I34">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J34">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="K34">
-        <v>5.9</v>
+        <v>110</v>
       </c>
       <c r="L34">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N34">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O34">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P34">
         <v>1.52</v>
       </c>
       <c r="Q34">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="R34">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S34">
         <v>3.2</v>
@@ -8957,10 +8963,10 @@
         <v>1.01</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W34">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -9131,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9148,22 +9154,22 @@
         <v>148</v>
       </c>
       <c r="E35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F35">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G35">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H35">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I35">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J35">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K35">
         <v>3.45</v>
@@ -9181,10 +9187,10 @@
         <v>1.43</v>
       </c>
       <c r="P35">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q35">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R35">
         <v>1.26</v>
@@ -9193,10 +9199,10 @@
         <v>4.4</v>
       </c>
       <c r="T35">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U35">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V35">
         <v>1.79</v>
@@ -9205,13 +9211,13 @@
         <v>1.32</v>
       </c>
       <c r="X35">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y35">
         <v>8.199999999999999</v>
       </c>
       <c r="Z35">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA35">
         <v>30</v>
@@ -9220,7 +9226,7 @@
         <v>12.5</v>
       </c>
       <c r="AC35">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD35">
         <v>11.5</v>
@@ -9229,7 +9235,7 @@
         <v>28</v>
       </c>
       <c r="AF35">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG35">
         <v>17.5</v>
@@ -9244,10 +9250,10 @@
         <v>110</v>
       </c>
       <c r="AK35">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AL35">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM35">
         <v>170</v>
@@ -9262,13 +9268,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ35">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR35">
         <v>11.5</v>
       </c>
       <c r="AS35">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT35">
         <v>10.5</v>
@@ -9280,34 +9286,34 @@
         <v>10</v>
       </c>
       <c r="AW35">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX35">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="AY35">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ35">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA35">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BB35">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BC35">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD35">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BE35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF35">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BG35">
         <v>19.5</v>
@@ -9316,69 +9322,69 @@
         <v>1000</v>
       </c>
       <c r="BI35">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BJ35">
         <v>1000</v>
       </c>
       <c r="BK35">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BN35">
         <v>1000</v>
       </c>
       <c r="BO35">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BP35">
         <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BT35">
         <v>1000</v>
       </c>
       <c r="BU35">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="CB35" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B36" t="s">
         <v>96</v>
@@ -9390,232 +9396,474 @@
         <v>149</v>
       </c>
       <c r="E36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F36">
-        <v>2.42</v>
+        <v>1.7</v>
       </c>
       <c r="G36">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="H36">
+        <v>4.2</v>
+      </c>
+      <c r="I36">
+        <v>7.4</v>
+      </c>
+      <c r="J36">
+        <v>3.15</v>
+      </c>
+      <c r="K36">
+        <v>3.75</v>
+      </c>
+      <c r="L36">
+        <v>1.01</v>
+      </c>
+      <c r="M36">
+        <v>1.01</v>
+      </c>
+      <c r="N36">
+        <v>2.28</v>
+      </c>
+      <c r="O36">
+        <v>1.23</v>
+      </c>
+      <c r="P36">
+        <v>1.47</v>
+      </c>
+      <c r="Q36">
+        <v>2.14</v>
+      </c>
+      <c r="R36">
+        <v>1.16</v>
+      </c>
+      <c r="S36">
+        <v>2.46</v>
+      </c>
+      <c r="T36">
+        <v>2.02</v>
+      </c>
+      <c r="U36">
+        <v>1.01</v>
+      </c>
+      <c r="V36">
+        <v>1.15</v>
+      </c>
+      <c r="W36">
+        <v>1.89</v>
+      </c>
+      <c r="X36">
+        <v>1000</v>
+      </c>
+      <c r="Y36">
+        <v>1000</v>
+      </c>
+      <c r="Z36">
+        <v>1000</v>
+      </c>
+      <c r="AA36">
+        <v>1000</v>
+      </c>
+      <c r="AB36">
+        <v>1000</v>
+      </c>
+      <c r="AC36">
+        <v>1000</v>
+      </c>
+      <c r="AD36">
+        <v>1000</v>
+      </c>
+      <c r="AE36">
+        <v>1000</v>
+      </c>
+      <c r="AF36">
+        <v>1000</v>
+      </c>
+      <c r="AG36">
+        <v>1000</v>
+      </c>
+      <c r="AH36">
+        <v>1000</v>
+      </c>
+      <c r="AI36">
+        <v>1000</v>
+      </c>
+      <c r="AJ36">
+        <v>1000</v>
+      </c>
+      <c r="AK36">
+        <v>1000</v>
+      </c>
+      <c r="AL36">
+        <v>1000</v>
+      </c>
+      <c r="AM36">
+        <v>1000</v>
+      </c>
+      <c r="AN36">
+        <v>1000</v>
+      </c>
+      <c r="AO36">
+        <v>1000</v>
+      </c>
+      <c r="AP36">
+        <v>1.01</v>
+      </c>
+      <c r="AQ36">
+        <v>1.01</v>
+      </c>
+      <c r="AR36">
+        <v>1.01</v>
+      </c>
+      <c r="AS36">
+        <v>1.01</v>
+      </c>
+      <c r="AT36">
+        <v>1.01</v>
+      </c>
+      <c r="AU36">
+        <v>1.01</v>
+      </c>
+      <c r="AV36">
+        <v>1.01</v>
+      </c>
+      <c r="AW36">
+        <v>1.01</v>
+      </c>
+      <c r="AX36">
+        <v>1.01</v>
+      </c>
+      <c r="AY36">
+        <v>1.01</v>
+      </c>
+      <c r="AZ36">
+        <v>1.01</v>
+      </c>
+      <c r="BA36">
+        <v>1.01</v>
+      </c>
+      <c r="BB36">
+        <v>1.01</v>
+      </c>
+      <c r="BC36">
+        <v>1.01</v>
+      </c>
+      <c r="BD36">
+        <v>1.01</v>
+      </c>
+      <c r="BE36">
+        <v>1.01</v>
+      </c>
+      <c r="BF36">
+        <v>1.01</v>
+      </c>
+      <c r="BG36">
+        <v>1.01</v>
+      </c>
+      <c r="BH36">
+        <v>1000</v>
+      </c>
+      <c r="BI36">
+        <v>1.01</v>
+      </c>
+      <c r="BJ36">
+        <v>1000</v>
+      </c>
+      <c r="BK36">
+        <v>1.01</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>1.01</v>
+      </c>
+      <c r="BN36">
+        <v>1000</v>
+      </c>
+      <c r="BO36">
+        <v>1.01</v>
+      </c>
+      <c r="BP36">
+        <v>1000</v>
+      </c>
+      <c r="BQ36">
+        <v>1.01</v>
+      </c>
+      <c r="BR36">
+        <v>1000</v>
+      </c>
+      <c r="BS36">
+        <v>1.01</v>
+      </c>
+      <c r="BT36">
+        <v>1000</v>
+      </c>
+      <c r="BU36">
+        <v>1.01</v>
+      </c>
+      <c r="BV36">
+        <v>1000</v>
+      </c>
+      <c r="BW36">
+        <v>1.01</v>
+      </c>
+      <c r="BX36">
+        <v>1000</v>
+      </c>
+      <c r="BY36">
+        <v>1.01</v>
+      </c>
+      <c r="BZ36">
+        <v>0</v>
+      </c>
+      <c r="CA36">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" t="s">
+        <v>150</v>
+      </c>
+      <c r="E37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F37">
+        <v>2.38</v>
+      </c>
+      <c r="G37">
+        <v>2.46</v>
+      </c>
+      <c r="H37">
         <v>3.45</v>
       </c>
-      <c r="I36">
+      <c r="I37">
         <v>3.65</v>
       </c>
-      <c r="J36">
+      <c r="J37">
         <v>3.2</v>
       </c>
-      <c r="K36">
+      <c r="K37">
         <v>3.3</v>
       </c>
-      <c r="L36">
-        <v>1.45</v>
-      </c>
-      <c r="M36">
+      <c r="L37">
+        <v>1.46</v>
+      </c>
+      <c r="M37">
         <v>1.09</v>
       </c>
-      <c r="N36">
-        <v>3.45</v>
-      </c>
-      <c r="O36">
+      <c r="N37">
+        <v>3.35</v>
+      </c>
+      <c r="O37">
         <v>1.38</v>
       </c>
-      <c r="P36">
-        <v>1.79</v>
-      </c>
-      <c r="Q36">
+      <c r="P37">
+        <v>1.81</v>
+      </c>
+      <c r="Q37">
         <v>2.16</v>
       </c>
-      <c r="R36">
+      <c r="R37">
         <v>1.31</v>
       </c>
-      <c r="S36">
+      <c r="S37">
         <v>3.95</v>
       </c>
-      <c r="T36">
-        <v>1.85</v>
-      </c>
-      <c r="U36">
+      <c r="T37">
+        <v>1.86</v>
+      </c>
+      <c r="U37">
         <v>2.08</v>
       </c>
-      <c r="V36">
+      <c r="V37">
         <v>1.38</v>
       </c>
-      <c r="W36">
-        <v>1.67</v>
-      </c>
-      <c r="X36">
+      <c r="W37">
+        <v>1.68</v>
+      </c>
+      <c r="X37">
         <v>12</v>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <v>12.5</v>
       </c>
-      <c r="Z36">
-        <v>22</v>
-      </c>
-      <c r="AA36">
+      <c r="Z37">
+        <v>24</v>
+      </c>
+      <c r="AA37">
         <v>65</v>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <v>9.6</v>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <v>7.2</v>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <v>15</v>
       </c>
-      <c r="AE36">
+      <c r="AE37">
         <v>46</v>
       </c>
-      <c r="AF36">
+      <c r="AF37">
+        <v>14.5</v>
+      </c>
+      <c r="AG37">
+        <v>12</v>
+      </c>
+      <c r="AH37">
+        <v>18</v>
+      </c>
+      <c r="AI37">
+        <v>60</v>
+      </c>
+      <c r="AJ37">
+        <v>34</v>
+      </c>
+      <c r="AK37">
+        <v>28</v>
+      </c>
+      <c r="AL37">
+        <v>46</v>
+      </c>
+      <c r="AM37">
+        <v>120</v>
+      </c>
+      <c r="AN37">
+        <v>24</v>
+      </c>
+      <c r="AO37">
+        <v>50</v>
+      </c>
+      <c r="AP37">
+        <v>10.5</v>
+      </c>
+      <c r="AQ37">
+        <v>11</v>
+      </c>
+      <c r="AR37">
+        <v>21</v>
+      </c>
+      <c r="AS37">
+        <v>50</v>
+      </c>
+      <c r="AT37">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU37">
+        <v>6.4</v>
+      </c>
+      <c r="AV37">
+        <v>13</v>
+      </c>
+      <c r="AW37">
+        <v>36</v>
+      </c>
+      <c r="AX37">
+        <v>13.5</v>
+      </c>
+      <c r="AY37">
+        <v>10.5</v>
+      </c>
+      <c r="AZ37">
         <v>15.5</v>
       </c>
-      <c r="AG36">
-        <v>12</v>
-      </c>
-      <c r="AH36">
-        <v>18</v>
-      </c>
-      <c r="AI36">
-        <v>60</v>
-      </c>
-      <c r="AJ36">
+      <c r="BA37">
+        <v>38</v>
+      </c>
+      <c r="BB37">
+        <v>29</v>
+      </c>
+      <c r="BC37">
+        <v>24</v>
+      </c>
+      <c r="BD37">
+        <v>38</v>
+      </c>
+      <c r="BE37">
+        <v>38</v>
+      </c>
+      <c r="BF37">
+        <v>21</v>
+      </c>
+      <c r="BG37">
+        <v>36</v>
+      </c>
+      <c r="BH37">
+        <v>3.15</v>
+      </c>
+      <c r="BI37">
+        <v>2.88</v>
+      </c>
+      <c r="BJ37">
+        <v>10.5</v>
+      </c>
+      <c r="BK37">
+        <v>5.8</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>11.5</v>
+      </c>
+      <c r="BN37">
+        <v>5.4</v>
+      </c>
+      <c r="BO37">
+        <v>4.5</v>
+      </c>
+      <c r="BP37">
+        <v>19</v>
+      </c>
+      <c r="BQ37">
+        <v>13.5</v>
+      </c>
+      <c r="BR37">
+        <v>36</v>
+      </c>
+      <c r="BS37">
+        <v>9.4</v>
+      </c>
+      <c r="BT37">
+        <v>6.6</v>
+      </c>
+      <c r="BU37">
+        <v>5.6</v>
+      </c>
+      <c r="BV37">
+        <v>29</v>
+      </c>
+      <c r="BW37">
+        <v>9</v>
+      </c>
+      <c r="BX37">
+        <v>44</v>
+      </c>
+      <c r="BY37">
+        <v>10</v>
+      </c>
+      <c r="BZ37">
         <v>34</v>
       </c>
-      <c r="AK36">
-        <v>29</v>
-      </c>
-      <c r="AL36">
-        <v>46</v>
-      </c>
-      <c r="AM36">
-        <v>120</v>
-      </c>
-      <c r="AN36">
-        <v>25</v>
-      </c>
-      <c r="AO36">
-        <v>50</v>
-      </c>
-      <c r="AP36">
-        <v>10.5</v>
-      </c>
-      <c r="AQ36">
-        <v>11</v>
-      </c>
-      <c r="AR36">
-        <v>21</v>
-      </c>
-      <c r="AS36">
-        <v>50</v>
-      </c>
-      <c r="AT36">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU36">
-        <v>6.4</v>
-      </c>
-      <c r="AV36">
-        <v>13</v>
-      </c>
-      <c r="AW36">
-        <v>36</v>
-      </c>
-      <c r="AX36">
-        <v>13.5</v>
-      </c>
-      <c r="AY36">
-        <v>10.5</v>
-      </c>
-      <c r="AZ36">
-        <v>15.5</v>
-      </c>
-      <c r="BA36">
-        <v>38</v>
-      </c>
-      <c r="BB36">
-        <v>29</v>
-      </c>
-      <c r="BC36">
-        <v>24</v>
-      </c>
-      <c r="BD36">
-        <v>38</v>
-      </c>
-      <c r="BE36">
-        <v>38</v>
-      </c>
-      <c r="BF36">
-        <v>21</v>
-      </c>
-      <c r="BG36">
-        <v>32</v>
-      </c>
-      <c r="BH36">
-        <v>3.2</v>
-      </c>
-      <c r="BI36">
-        <v>2.88</v>
-      </c>
-      <c r="BJ36">
-        <v>10.5</v>
-      </c>
-      <c r="BK36">
-        <v>7.4</v>
-      </c>
-      <c r="BL36">
-        <v>1000</v>
-      </c>
-      <c r="BM36">
-        <v>11</v>
-      </c>
-      <c r="BN36">
-        <v>5.4</v>
-      </c>
-      <c r="BO36">
-        <v>4.5</v>
-      </c>
-      <c r="BP36">
-        <v>19</v>
-      </c>
-      <c r="BQ36">
-        <v>13.5</v>
-      </c>
-      <c r="BR36">
-        <v>36</v>
-      </c>
-      <c r="BS36">
-        <v>9</v>
-      </c>
-      <c r="BT36">
-        <v>6.6</v>
-      </c>
-      <c r="BU36">
-        <v>5.6</v>
-      </c>
-      <c r="BV36">
-        <v>29</v>
-      </c>
-      <c r="BW36">
-        <v>8.6</v>
-      </c>
-      <c r="BX36">
-        <v>44</v>
-      </c>
-      <c r="BY36">
-        <v>9.6</v>
-      </c>
-      <c r="BZ36">
-        <v>34</v>
-      </c>
-      <c r="CA36">
-        <v>9</v>
-      </c>
-      <c r="CB36" t="s">
-        <v>185</v>
+      <c r="CA37">
+        <v>9.4</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
@@ -523,7 +523,7 @@
     <t>Albion FC</t>
   </si>
   <si>
-    <t>2026-09-28 03:29:40</t>
+    <t>2026-09-28 05:41:51</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1117,7 @@
         <v>139</v>
       </c>
       <c r="F2">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G2">
         <v>1.99</v>
@@ -1132,52 +1132,52 @@
         <v>3.6</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
         <v>1.39</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P2">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U2">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
         <v>1.22</v>
       </c>
       <c r="W2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y2">
         <v>18</v>
       </c>
       <c r="Z2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
         <v>120</v>
@@ -1195,22 +1195,22 @@
         <v>70</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
         <v>75</v>
       </c>
       <c r="AJ2">
+        <v>22</v>
+      </c>
+      <c r="AK2">
         <v>21</v>
-      </c>
-      <c r="AK2">
-        <v>20</v>
       </c>
       <c r="AL2">
         <v>36</v>
@@ -1225,118 +1225,118 @@
         <v>75</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>3.65</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH2">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
         <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>169</v>
@@ -1359,136 +1359,136 @@
         <v>140</v>
       </c>
       <c r="F3">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="G3">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="H3">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="I3">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K3">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
         <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="Q3">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="R3">
         <v>1.48</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="T3">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="U3">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="X3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y3">
+        <v>21</v>
+      </c>
+      <c r="Z3">
+        <v>38</v>
+      </c>
+      <c r="AA3">
+        <v>130</v>
+      </c>
+      <c r="AB3">
+        <v>13</v>
+      </c>
+      <c r="AC3">
+        <v>10.5</v>
+      </c>
+      <c r="AD3">
+        <v>18</v>
+      </c>
+      <c r="AE3">
+        <v>60</v>
+      </c>
+      <c r="AF3">
+        <v>15.5</v>
+      </c>
+      <c r="AG3">
+        <v>12</v>
+      </c>
+      <c r="AH3">
         <v>19</v>
       </c>
-      <c r="Z3">
+      <c r="AI3">
+        <v>60</v>
+      </c>
+      <c r="AJ3">
+        <v>26</v>
+      </c>
+      <c r="AK3">
+        <v>22</v>
+      </c>
+      <c r="AL3">
         <v>34</v>
       </c>
-      <c r="AA3">
-        <v>75</v>
-      </c>
-      <c r="AB3">
-        <v>14</v>
-      </c>
-      <c r="AC3">
-        <v>11</v>
-      </c>
-      <c r="AD3">
-        <v>17.5</v>
-      </c>
-      <c r="AE3">
-        <v>46</v>
-      </c>
-      <c r="AF3">
-        <v>17</v>
-      </c>
-      <c r="AG3">
-        <v>13</v>
-      </c>
-      <c r="AH3">
-        <v>19.5</v>
-      </c>
-      <c r="AI3">
-        <v>48</v>
-      </c>
-      <c r="AJ3">
-        <v>29</v>
-      </c>
-      <c r="AK3">
-        <v>24</v>
-      </c>
-      <c r="AL3">
-        <v>36</v>
-      </c>
       <c r="AM3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN3">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AO3">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AP3">
         <v>16</v>
       </c>
       <c r="AQ3">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR3">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AS3">
-        <v>4.7</v>
+        <v>46</v>
       </c>
       <c r="AT3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AW3">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="AX3">
         <v>11</v>
@@ -1497,88 +1497,88 @@
         <v>8.4</v>
       </c>
       <c r="AZ3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="BB3">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BC3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BD3">
+        <v>22</v>
+      </c>
+      <c r="BE3">
+        <v>55</v>
+      </c>
+      <c r="BF3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG3">
+        <v>26</v>
+      </c>
+      <c r="BH3">
         <v>4.4</v>
       </c>
-      <c r="BE3">
-        <v>4.8</v>
-      </c>
-      <c r="BF3">
-        <v>8.6</v>
-      </c>
-      <c r="BG3">
-        <v>19.5</v>
-      </c>
-      <c r="BH3">
-        <v>4.5</v>
-      </c>
       <c r="BI3">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BN3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
         <v>4</v>
       </c>
       <c r="BP3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3">
+        <v>3.55</v>
+      </c>
+      <c r="BR3">
+        <v>27</v>
+      </c>
+      <c r="BS3">
         <v>4</v>
-      </c>
-      <c r="BR3">
-        <v>28</v>
-      </c>
-      <c r="BS3">
-        <v>4.5</v>
       </c>
       <c r="BT3">
         <v>8.4</v>
       </c>
       <c r="BU3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV3">
         <v>34</v>
       </c>
       <c r="BW3">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
+        <v>4.2</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
         <v>4.7</v>
-      </c>
-      <c r="BZ3">
-        <v>22</v>
-      </c>
-      <c r="CA3">
-        <v>4.3</v>
       </c>
       <c r="CB3" t="s">
         <v>169</v>
@@ -1607,46 +1607,46 @@
         <v>2.18</v>
       </c>
       <c r="H4">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>110</v>
       </c>
       <c r="L4">
         <v>1.44</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
         <v>3.05</v>
       </c>
       <c r="O4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S4">
-        <v>3.7</v>
+        <v>2.14</v>
       </c>
       <c r="T4">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
         <v>1.25</v>
@@ -1655,61 +1655,61 @@
         <v>1.86</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AQ4">
         <v>1.01</v>
@@ -1730,7 +1730,7 @@
         <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX4">
         <v>1.01</v>
@@ -1763,58 +1763,58 @@
         <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
         <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
         <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1843,19 +1843,19 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G5">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="H5">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I5">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
         <v>3.95</v>
@@ -1864,91 +1864,91 @@
         <v>1.44</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S5">
         <v>3.6</v>
       </c>
       <c r="T5">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="X5">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
         <v>1.01</v>
@@ -2005,64 +2005,64 @@
         <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
         <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
         <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
         <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
         <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
         <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
         <v>169</v>
@@ -2085,34 +2085,34 @@
         <v>143</v>
       </c>
       <c r="F6">
-        <v>1.12</v>
+        <v>3.85</v>
       </c>
       <c r="G6">
         <v>110</v>
       </c>
       <c r="H6">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="I6">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>1.12</v>
       </c>
       <c r="K6">
-        <v>5.3</v>
+        <v>930</v>
       </c>
       <c r="L6">
         <v>1.33</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
         <v>4.1</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P6">
         <v>2.12</v>
@@ -2124,19 +2124,19 @@
         <v>1.43</v>
       </c>
       <c r="S6">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T6">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="W6">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2247,61 +2247,61 @@
         <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
         <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
         <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
         <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2330,64 +2330,64 @@
         <v>2.84</v>
       </c>
       <c r="G7">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H7">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I7">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J7">
         <v>3.3</v>
       </c>
       <c r="K7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L7">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O7">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S7">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T7">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U7">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W7">
         <v>1.53</v>
       </c>
       <c r="X7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA7">
         <v>46</v>
@@ -2399,10 +2399,10 @@
         <v>7.2</v>
       </c>
       <c r="AD7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF7">
         <v>18</v>
@@ -2411,13 +2411,13 @@
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK7">
         <v>34</v>
@@ -2426,10 +2426,10 @@
         <v>48</v>
       </c>
       <c r="AM7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO7">
         <v>34</v>
@@ -2438,10 +2438,10 @@
         <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS7">
         <v>40</v>
@@ -2465,88 +2465,88 @@
         <v>11.5</v>
       </c>
       <c r="AZ7">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB7">
         <v>40</v>
       </c>
       <c r="BC7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BG7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH7">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BI7">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>6.8</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
         <v>10</v>
       </c>
-      <c r="BK7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL7">
-        <v>140</v>
-      </c>
-      <c r="BM7">
-        <v>14.5</v>
-      </c>
       <c r="BN7">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BO7">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP7">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR7">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="BT7">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BU7">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9.6</v>
+        <v>3.1</v>
       </c>
       <c r="BX7">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="BZ7">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="CB7" t="s">
         <v>169</v>
@@ -2575,67 +2575,67 @@
         <v>3.25</v>
       </c>
       <c r="H8">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="I8">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L8">
         <v>1.51</v>
       </c>
       <c r="M8">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Q8">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T8">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="U8">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W8">
         <v>1.44</v>
       </c>
       <c r="X8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z8">
         <v>15.5</v>
       </c>
       <c r="AA8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC8">
         <v>7.2</v>
@@ -2650,19 +2650,19 @@
         <v>21</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ8">
         <v>55</v>
       </c>
       <c r="AK8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL8">
         <v>60</v>
@@ -2671,34 +2671,34 @@
         <v>120</v>
       </c>
       <c r="AN8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO8">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR8">
         <v>14</v>
       </c>
       <c r="AS8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV8">
         <v>11</v>
       </c>
       <c r="AW8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX8">
         <v>19</v>
@@ -2707,13 +2707,13 @@
         <v>12.5</v>
       </c>
       <c r="AZ8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB8">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC8">
         <v>36</v>
@@ -2728,67 +2728,67 @@
         <v>36</v>
       </c>
       <c r="BG8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BH8">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BI8">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="BJ8">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
         <v>7.6</v>
       </c>
       <c r="BL8">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>11</v>
+        <v>2.82</v>
       </c>
       <c r="BN8">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP8">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>8.199999999999999</v>
+        <v>2.82</v>
       </c>
       <c r="BR8">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>9.199999999999999</v>
+        <v>2.82</v>
       </c>
       <c r="BT8">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BV8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>7.6</v>
+        <v>2.8</v>
       </c>
       <c r="BX8">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>9</v>
+        <v>2.82</v>
       </c>
       <c r="BZ8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>8.800000000000001</v>
+        <v>2.82</v>
       </c>
       <c r="CB8" t="s">
         <v>169</v>
@@ -2811,16 +2811,16 @@
         <v>146</v>
       </c>
       <c r="F9">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G9">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H9">
         <v>3</v>
       </c>
       <c r="I9">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J9">
         <v>3.15</v>
@@ -2829,16 +2829,16 @@
         <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M9">
         <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P9">
         <v>1.63</v>
@@ -2853,13 +2853,13 @@
         <v>5.2</v>
       </c>
       <c r="T9">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U9">
         <v>1.88</v>
       </c>
       <c r="V9">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W9">
         <v>1.55</v>
@@ -2871,7 +2871,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA9">
         <v>55</v>
@@ -2883,13 +2883,13 @@
         <v>7.2</v>
       </c>
       <c r="AD9">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE9">
         <v>44</v>
       </c>
       <c r="AF9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG9">
         <v>13</v>
@@ -2907,16 +2907,16 @@
         <v>38</v>
       </c>
       <c r="AL9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AM9">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN9">
+        <v>46</v>
+      </c>
+      <c r="AO9">
         <v>55</v>
-      </c>
-      <c r="AO9">
-        <v>50</v>
       </c>
       <c r="AP9">
         <v>8.800000000000001</v>
@@ -2925,7 +2925,7 @@
         <v>8.6</v>
       </c>
       <c r="AR9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS9">
         <v>46</v>
@@ -2979,34 +2979,34 @@
         <v>2.6</v>
       </c>
       <c r="BJ9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK9">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="BN9">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO9">
         <v>5</v>
       </c>
       <c r="BP9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ9">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS9">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BT9">
         <v>5.9</v>
@@ -3015,22 +3015,22 @@
         <v>5.3</v>
       </c>
       <c r="BV9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW9">
+        <v>10.5</v>
+      </c>
+      <c r="BX9">
+        <v>48</v>
+      </c>
+      <c r="BY9">
         <v>12</v>
       </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>15</v>
-      </c>
       <c r="BZ9">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="CA9">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="CB9" t="s">
         <v>169</v>
@@ -3053,22 +3053,22 @@
         <v>147</v>
       </c>
       <c r="F10">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G10">
         <v>1.85</v>
       </c>
       <c r="H10">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I10">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L10">
         <v>1.3</v>
@@ -3077,37 +3077,37 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O10">
         <v>1.19</v>
       </c>
       <c r="P10">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q10">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R10">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S10">
         <v>2.46</v>
       </c>
       <c r="T10">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="U10">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W10">
         <v>2.16</v>
       </c>
       <c r="X10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y10">
         <v>26</v>
@@ -3116,10 +3116,10 @@
         <v>48</v>
       </c>
       <c r="AA10">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC10">
         <v>12</v>
@@ -3128,148 +3128,148 @@
         <v>23</v>
       </c>
       <c r="AE10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF10">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AG10">
         <v>12</v>
       </c>
       <c r="AH10">
+        <v>20</v>
+      </c>
+      <c r="AI10">
+        <v>60</v>
+      </c>
+      <c r="AJ10">
         <v>21</v>
-      </c>
-      <c r="AI10">
-        <v>65</v>
-      </c>
-      <c r="AJ10">
-        <v>19</v>
       </c>
       <c r="AK10">
         <v>18.5</v>
       </c>
       <c r="AL10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM10">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO10">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH10">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
         <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
         <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
         <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
         <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
         <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
         <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
         <v>1.01</v>
@@ -3295,40 +3295,40 @@
         <v>148</v>
       </c>
       <c r="F11">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G11">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="H11">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J11">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="K11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L11">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M11">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N11">
         <v>2.48</v>
       </c>
       <c r="O11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P11">
         <v>1.5</v>
       </c>
       <c r="Q11">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R11">
         <v>1.18</v>
@@ -3337,7 +3337,7 @@
         <v>5.3</v>
       </c>
       <c r="T11">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U11">
         <v>1.72</v>
@@ -3346,7 +3346,7 @@
         <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X11">
         <v>9.6</v>
@@ -3361,13 +3361,13 @@
         <v>110</v>
       </c>
       <c r="AB11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC11">
         <v>7.6</v>
       </c>
       <c r="AD11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE11">
         <v>70</v>
@@ -3379,7 +3379,7 @@
         <v>13</v>
       </c>
       <c r="AH11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI11">
         <v>110</v>
@@ -3403,7 +3403,7 @@
         <v>120</v>
       </c>
       <c r="AP11">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11">
         <v>8.800000000000001</v>
@@ -3427,7 +3427,7 @@
         <v>50</v>
       </c>
       <c r="AX11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY11">
         <v>8.199999999999999</v>
@@ -3537,13 +3537,13 @@
         <v>149</v>
       </c>
       <c r="F12">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G12">
         <v>2.16</v>
       </c>
       <c r="H12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I12">
         <v>5.6</v>
@@ -3552,10 +3552,10 @@
         <v>3.15</v>
       </c>
       <c r="K12">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L12">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="M12">
         <v>1.13</v>
@@ -3570,7 +3570,7 @@
         <v>1.51</v>
       </c>
       <c r="Q12">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R12">
         <v>1.18</v>
@@ -3579,13 +3579,13 @@
         <v>6</v>
       </c>
       <c r="T12">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U12">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
         <v>1.86</v>
@@ -3621,7 +3621,7 @@
         <v>13</v>
       </c>
       <c r="AH12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI12">
         <v>170</v>
@@ -3645,64 +3645,64 @@
         <v>250</v>
       </c>
       <c r="AP12">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ12">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR12">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS12">
-        <v>100</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AU12">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AV12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW12">
-        <v>70</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12">
+        <v>5.8</v>
+      </c>
+      <c r="AY12">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY12">
-        <v>9.6</v>
-      </c>
       <c r="AZ12">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA12">
-        <v>95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB12">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC12">
-        <v>20</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD12">
-        <v>50</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE12">
-        <v>200</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG12">
-        <v>130</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BI12">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="BJ12">
         <v>15.5</v>
@@ -3711,46 +3711,46 @@
         <v>9.4</v>
       </c>
       <c r="BL12">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="BM12">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BN12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO12">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ12">
-        <v>12.5</v>
+        <v>4.8</v>
       </c>
       <c r="BR12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS12">
-        <v>32</v>
+        <v>5.7</v>
       </c>
       <c r="BT12">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU12">
         <v>6.4</v>
       </c>
       <c r="BV12">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BW12">
-        <v>42</v>
+        <v>5.8</v>
       </c>
       <c r="BX12">
         <v>110</v>
       </c>
       <c r="BY12">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3782,13 +3782,13 @@
         <v>2.92</v>
       </c>
       <c r="G13">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="H13">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I13">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J13">
         <v>2.68</v>
@@ -3806,19 +3806,19 @@
         <v>2.1</v>
       </c>
       <c r="O13">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P13">
         <v>1.35</v>
       </c>
       <c r="Q13">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="S13">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>2.26</v>
@@ -3827,10 +3827,10 @@
         <v>1.62</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W13">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X13">
         <v>8.199999999999999</v>
@@ -3887,7 +3887,7 @@
         <v>100</v>
       </c>
       <c r="AP13">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ13">
         <v>5.6</v>
@@ -3941,16 +3941,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BH13">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BI13">
         <v>2.02</v>
       </c>
       <c r="BJ13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BK13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL13">
         <v>340</v>
@@ -3959,7 +3959,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN13">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BO13">
         <v>4.5</v>
@@ -3971,16 +3971,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BR13">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BS13">
         <v>8.800000000000001</v>
       </c>
       <c r="BT13">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BU13">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV13">
         <v>38</v>
@@ -4021,67 +4021,67 @@
         <v>151</v>
       </c>
       <c r="F14">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="G14">
         <v>2.44</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J14">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="K14">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L14">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="M14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O14">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="P14">
         <v>1.34</v>
       </c>
       <c r="Q14">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R14">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="S14">
         <v>1.01</v>
       </c>
       <c r="T14">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="U14">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V14">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W14">
         <v>1.69</v>
       </c>
       <c r="X14">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="Y14">
         <v>11</v>
       </c>
       <c r="Z14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA14">
         <v>160</v>
@@ -4090,7 +4090,7 @@
         <v>6.2</v>
       </c>
       <c r="AC14">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD14">
         <v>25</v>
@@ -4099,7 +4099,7 @@
         <v>120</v>
       </c>
       <c r="AF14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG14">
         <v>14</v>
@@ -4114,7 +4114,7 @@
         <v>38</v>
       </c>
       <c r="AK14">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AL14">
         <v>100</v>
@@ -4129,58 +4129,58 @@
         <v>230</v>
       </c>
       <c r="AP14">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AQ14">
+        <v>4.8</v>
+      </c>
+      <c r="AR14">
+        <v>7</v>
+      </c>
+      <c r="AS14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT14">
+        <v>5.1</v>
+      </c>
+      <c r="AU14">
+        <v>4.5</v>
+      </c>
+      <c r="AV14">
+        <v>6.4</v>
+      </c>
+      <c r="AW14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX14">
+        <v>5.2</v>
+      </c>
+      <c r="AY14">
+        <v>5.4</v>
+      </c>
+      <c r="AZ14">
+        <v>7</v>
+      </c>
+      <c r="BA14">
+        <v>8.4</v>
+      </c>
+      <c r="BB14">
+        <v>7</v>
+      </c>
+      <c r="BC14">
         <v>7.2</v>
       </c>
-      <c r="AR14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT14">
-        <v>5</v>
-      </c>
-      <c r="AU14">
-        <v>6.2</v>
-      </c>
-      <c r="AV14">
-        <v>16</v>
-      </c>
-      <c r="AW14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX14">
-        <v>9.4</v>
-      </c>
-      <c r="AY14">
-        <v>10</v>
-      </c>
-      <c r="AZ14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC14">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BD14">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BE14">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF14">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BG14">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH14">
         <v>2.58</v>
@@ -4189,52 +4189,52 @@
         <v>2.02</v>
       </c>
       <c r="BJ14">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK14">
-        <v>10</v>
+        <v>1.02</v>
       </c>
       <c r="BL14">
         <v>400</v>
       </c>
       <c r="BM14">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO14">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BQ14">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
         <v>70</v>
       </c>
       <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
         <v>8.800000000000001</v>
       </c>
-      <c r="BT14">
-        <v>8.6</v>
-      </c>
       <c r="BU14">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
         <v>65</v>
       </c>
       <c r="BW14">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
         <v>110</v>
       </c>
       <c r="BY14">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4263,166 +4263,166 @@
         <v>152</v>
       </c>
       <c r="F15">
-        <v>1.12</v>
+        <v>2.64</v>
       </c>
       <c r="G15">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="H15">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="I15">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J15">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K15">
         <v>4.1</v>
       </c>
       <c r="L15">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M15">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N15">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="O15">
         <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q15">
         <v>2</v>
       </c>
       <c r="R15">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S15">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="T15">
         <v>1.01</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V15">
         <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK15">
+        <v>50</v>
+      </c>
+      <c r="AL15">
+        <v>75</v>
+      </c>
+      <c r="AM15">
+        <v>130</v>
+      </c>
+      <c r="AN15">
+        <v>40</v>
+      </c>
+      <c r="AO15">
         <v>42</v>
       </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC15">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH15">
         <v>3.6</v>
@@ -4434,55 +4434,55 @@
         <v>11</v>
       </c>
       <c r="BK15">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
         <v>150</v>
       </c>
       <c r="BM15">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
         <v>6.6</v>
       </c>
       <c r="BO15">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
         <v>26</v>
       </c>
       <c r="BQ15">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
         <v>42</v>
       </c>
       <c r="BS15">
-        <v>8.800000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="BT15">
         <v>6.6</v>
       </c>
       <c r="BU15">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
         <v>26</v>
       </c>
       <c r="BW15">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
         <v>42</v>
       </c>
       <c r="BY15">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
         <v>36</v>
       </c>
       <c r="CA15">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
         <v>169</v>
@@ -4508,7 +4508,7 @@
         <v>3.35</v>
       </c>
       <c r="G16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H16">
         <v>2.34</v>
@@ -4517,7 +4517,7 @@
         <v>2.38</v>
       </c>
       <c r="J16">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K16">
         <v>3.55</v>
@@ -4529,37 +4529,37 @@
         <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O16">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P16">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q16">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R16">
         <v>1.38</v>
       </c>
       <c r="S16">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T16">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U16">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V16">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W16">
         <v>1.4</v>
       </c>
       <c r="X16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y16">
         <v>11</v>
@@ -4577,13 +4577,13 @@
         <v>7.8</v>
       </c>
       <c r="AD16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE16">
         <v>25</v>
       </c>
       <c r="AF16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG16">
         <v>14.5</v>
@@ -4655,76 +4655,76 @@
         <v>32</v>
       </c>
       <c r="BD16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE16">
         <v>38</v>
       </c>
       <c r="BF16">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BG16">
         <v>16.5</v>
       </c>
       <c r="BH16">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BI16">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BJ16">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BK16">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BL16">
         <v>130</v>
       </c>
       <c r="BM16">
+        <v>7</v>
+      </c>
+      <c r="BN16">
+        <v>7.4</v>
+      </c>
+      <c r="BO16">
+        <v>5.6</v>
+      </c>
+      <c r="BP16">
+        <v>30</v>
+      </c>
+      <c r="BQ16">
+        <v>6.4</v>
+      </c>
+      <c r="BR16">
+        <v>42</v>
+      </c>
+      <c r="BS16">
+        <v>6.2</v>
+      </c>
+      <c r="BT16">
+        <v>5.5</v>
+      </c>
+      <c r="BU16">
+        <v>4.5</v>
+      </c>
+      <c r="BV16">
+        <v>19.5</v>
+      </c>
+      <c r="BW16">
         <v>12</v>
       </c>
-      <c r="BN16">
+      <c r="BX16">
+        <v>34</v>
+      </c>
+      <c r="BY16">
         <v>6.6</v>
       </c>
-      <c r="BO16">
-        <v>5.9</v>
-      </c>
-      <c r="BP16">
-        <v>27</v>
-      </c>
-      <c r="BQ16">
-        <v>9</v>
-      </c>
-      <c r="BR16">
-        <v>38</v>
-      </c>
-      <c r="BS16">
-        <v>10</v>
-      </c>
-      <c r="BT16">
-        <v>5.3</v>
-      </c>
-      <c r="BU16">
-        <v>4.7</v>
-      </c>
-      <c r="BV16">
-        <v>18</v>
-      </c>
-      <c r="BW16">
-        <v>8</v>
-      </c>
-      <c r="BX16">
-        <v>32</v>
-      </c>
-      <c r="BY16">
-        <v>9.4</v>
-      </c>
       <c r="BZ16">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="CA16">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="s">
         <v>169</v>
@@ -4765,19 +4765,19 @@
         <v>3.65</v>
       </c>
       <c r="L17">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P17">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q17">
         <v>1.76</v>
@@ -4786,37 +4786,37 @@
         <v>1.5</v>
       </c>
       <c r="S17">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T17">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U17">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V17">
         <v>1.58</v>
       </c>
       <c r="W17">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X17">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y17">
         <v>13.5</v>
       </c>
       <c r="Z17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA17">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC17">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD17">
         <v>12</v>
@@ -4828,7 +4828,7 @@
         <v>20</v>
       </c>
       <c r="AG17">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH17">
         <v>14.5</v>
@@ -4852,22 +4852,22 @@
         <v>21</v>
       </c>
       <c r="AO17">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP17">
         <v>17</v>
       </c>
       <c r="AQ17">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU17">
         <v>7.8</v>
@@ -4876,10 +4876,10 @@
         <v>11</v>
       </c>
       <c r="AW17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX17">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY17">
         <v>11.5</v>
@@ -4888,7 +4888,7 @@
         <v>13.5</v>
       </c>
       <c r="BA17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB17">
         <v>38</v>
@@ -4900,19 +4900,19 @@
         <v>32</v>
       </c>
       <c r="BE17">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BG17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BH17">
         <v>3.9</v>
       </c>
       <c r="BI17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ17">
         <v>8.800000000000001</v>
@@ -4924,16 +4924,16 @@
         <v>90</v>
       </c>
       <c r="BM17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO17">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ17">
         <v>17</v>
@@ -4945,7 +4945,7 @@
         <v>10</v>
       </c>
       <c r="BT17">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU17">
         <v>5.3</v>
@@ -4989,16 +4989,16 @@
         <v>155</v>
       </c>
       <c r="F18">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G18">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="H18">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="I18">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J18">
         <v>3.45</v>
@@ -5019,7 +5019,7 @@
         <v>1.37</v>
       </c>
       <c r="P18">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q18">
         <v>2.14</v>
@@ -5028,31 +5028,31 @@
         <v>1.32</v>
       </c>
       <c r="S18">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T18">
         <v>1.86</v>
       </c>
       <c r="U18">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W18">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="X18">
         <v>12.5</v>
       </c>
       <c r="Y18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z18">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA18">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB18">
         <v>9.4</v>
@@ -5061,19 +5061,19 @@
         <v>7.6</v>
       </c>
       <c r="AD18">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE18">
         <v>44</v>
       </c>
       <c r="AF18">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG18">
         <v>11.5</v>
       </c>
       <c r="AH18">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI18">
         <v>55</v>
@@ -5082,7 +5082,7 @@
         <v>34</v>
       </c>
       <c r="AK18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL18">
         <v>42</v>
@@ -5091,22 +5091,22 @@
         <v>110</v>
       </c>
       <c r="AN18">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO18">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP18">
         <v>11.5</v>
       </c>
       <c r="AQ18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT18">
         <v>8.6</v>
@@ -5115,19 +5115,19 @@
         <v>7</v>
       </c>
       <c r="AV18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW18">
         <v>38</v>
       </c>
       <c r="AX18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA18">
         <v>46</v>
@@ -5142,19 +5142,19 @@
         <v>36</v>
       </c>
       <c r="BE18">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="BF18">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH18">
         <v>3.2</v>
       </c>
       <c r="BI18">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ18">
         <v>9.800000000000001</v>
@@ -5166,49 +5166,49 @@
         <v>140</v>
       </c>
       <c r="BM18">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="BN18">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP18">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BQ18">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BR18">
         <v>34</v>
       </c>
       <c r="BS18">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="BT18">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU18">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV18">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BW18">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="BX18">
         <v>44</v>
       </c>
       <c r="BY18">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="BZ18">
         <v>32</v>
       </c>
       <c r="CA18">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="CB18" t="s">
         <v>169</v>
@@ -5231,16 +5231,16 @@
         <v>156</v>
       </c>
       <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19">
         <v>4.1</v>
       </c>
-      <c r="G19">
-        <v>4.2</v>
-      </c>
       <c r="H19">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I19">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="J19">
         <v>4.1</v>
@@ -5255,64 +5255,64 @@
         <v>1.04</v>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="O19">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P19">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="Q19">
+        <v>1.61</v>
+      </c>
+      <c r="R19">
+        <v>1.64</v>
+      </c>
+      <c r="S19">
+        <v>2.52</v>
+      </c>
+      <c r="T19">
         <v>1.59</v>
       </c>
-      <c r="R19">
-        <v>1.66</v>
-      </c>
-      <c r="S19">
-        <v>2.46</v>
-      </c>
-      <c r="T19">
-        <v>1.56</v>
-      </c>
       <c r="U19">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V19">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W19">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X19">
         <v>24</v>
       </c>
       <c r="Y19">
+        <v>13</v>
+      </c>
+      <c r="Z19">
         <v>14</v>
-      </c>
-      <c r="Z19">
-        <v>15</v>
       </c>
       <c r="AA19">
         <v>23</v>
       </c>
       <c r="AB19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC19">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AE19">
         <v>17</v>
       </c>
       <c r="AF19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH19">
         <v>15</v>
@@ -5324,7 +5324,7 @@
         <v>75</v>
       </c>
       <c r="AK19">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL19">
         <v>42</v>
@@ -5333,34 +5333,34 @@
         <v>60</v>
       </c>
       <c r="AN19">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP19">
         <v>22</v>
       </c>
       <c r="AQ19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR19">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT19">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU19">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV19">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW19">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX19">
         <v>32</v>
@@ -5369,7 +5369,7 @@
         <v>15</v>
       </c>
       <c r="AZ19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA19">
         <v>24</v>
@@ -5378,34 +5378,34 @@
         <v>60</v>
       </c>
       <c r="BC19">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BD19">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE19">
         <v>50</v>
       </c>
       <c r="BF19">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BG19">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH19">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI19">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK19">
         <v>7.8</v>
       </c>
       <c r="BL19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM19">
         <v>10</v>
@@ -5420,13 +5420,13 @@
         <v>34</v>
       </c>
       <c r="BQ19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR19">
         <v>38</v>
       </c>
       <c r="BS19">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT19">
         <v>5.1</v>
@@ -5438,19 +5438,19 @@
         <v>12.5</v>
       </c>
       <c r="BW19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX19">
         <v>26</v>
       </c>
       <c r="BY19">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BZ19">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA19">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="CB19" t="s">
         <v>169</v>
@@ -5473,16 +5473,16 @@
         <v>157</v>
       </c>
       <c r="F20">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G20">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H20">
+        <v>2.76</v>
+      </c>
+      <c r="I20">
         <v>2.78</v>
-      </c>
-      <c r="I20">
-        <v>2.8</v>
       </c>
       <c r="J20">
         <v>3.1</v>
@@ -5491,13 +5491,13 @@
         <v>3.15</v>
       </c>
       <c r="L20">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M20">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N20">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O20">
         <v>1.54</v>
@@ -5506,7 +5506,7 @@
         <v>1.58</v>
       </c>
       <c r="Q20">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R20">
         <v>1.2</v>
@@ -5518,16 +5518,16 @@
         <v>2.14</v>
       </c>
       <c r="U20">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V20">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W20">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X20">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y20">
         <v>8.199999999999999</v>
@@ -5539,7 +5539,7 @@
         <v>46</v>
       </c>
       <c r="AB20">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -5551,7 +5551,7 @@
         <v>40</v>
       </c>
       <c r="AF20">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG20">
         <v>14</v>
@@ -5560,28 +5560,28 @@
         <v>23</v>
       </c>
       <c r="AI20">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ20">
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL20">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM20">
         <v>170</v>
       </c>
       <c r="AN20">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO20">
         <v>46</v>
       </c>
       <c r="AP20">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ20">
         <v>7.8</v>
@@ -5593,7 +5593,7 @@
         <v>40</v>
       </c>
       <c r="AT20">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU20">
         <v>6.8</v>
@@ -5608,7 +5608,7 @@
         <v>17.5</v>
       </c>
       <c r="AY20">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ20">
         <v>21</v>
@@ -5620,7 +5620,7 @@
         <v>50</v>
       </c>
       <c r="BC20">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BD20">
         <v>60</v>
@@ -5635,64 +5635,64 @@
         <v>42</v>
       </c>
       <c r="BH20">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="BI20">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="BJ20">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL20">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>16</v>
+        <v>3.9</v>
       </c>
       <c r="BN20">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BO20">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP20">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>10.5</v>
+        <v>3.65</v>
       </c>
       <c r="BR20">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="BT20">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BU20">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BV20">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>10.5</v>
+        <v>3.55</v>
       </c>
       <c r="BX20">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>13</v>
+        <v>3.9</v>
       </c>
       <c r="BZ20">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>13</v>
+        <v>3.9</v>
       </c>
       <c r="CB20" t="s">
         <v>169</v>
@@ -5715,73 +5715,73 @@
         <v>158</v>
       </c>
       <c r="F21">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="G21">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H21">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I21">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K21">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L21">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M21">
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O21">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P21">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q21">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R21">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S21">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T21">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="U21">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W21">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y21">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Z21">
         <v>26</v>
       </c>
       <c r="AA21">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB21">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC21">
         <v>8.4</v>
@@ -5793,40 +5793,40 @@
         <v>36</v>
       </c>
       <c r="AF21">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG21">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI21">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ21">
         <v>28</v>
       </c>
       <c r="AK21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL21">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM21">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN21">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO21">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP21">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AQ21">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR21">
         <v>24</v>
@@ -5835,46 +5835,46 @@
         <v>55</v>
       </c>
       <c r="AT21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU21">
         <v>8</v>
       </c>
       <c r="AV21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW21">
         <v>32</v>
       </c>
       <c r="AX21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY21">
         <v>10</v>
       </c>
       <c r="AZ21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA21">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BB21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC21">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD21">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE21">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG21">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH21">
         <v>3.95</v>
@@ -5883,7 +5883,7 @@
         <v>3.65</v>
       </c>
       <c r="BJ21">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK21">
         <v>7.8</v>
@@ -5892,46 +5892,46 @@
         <v>100</v>
       </c>
       <c r="BM21">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BN21">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO21">
         <v>4.8</v>
       </c>
       <c r="BP21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ21">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BR21">
         <v>25</v>
       </c>
       <c r="BS21">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT21">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU21">
         <v>6.2</v>
       </c>
       <c r="BV21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW21">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX21">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BY21">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ21">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="CA21">
         <v>9</v>
@@ -5957,22 +5957,22 @@
         <v>159</v>
       </c>
       <c r="F22">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="G22">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I22">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J22">
         <v>3.45</v>
       </c>
       <c r="K22">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L22">
         <v>1.42</v>
@@ -5990,139 +5990,139 @@
         <v>1.89</v>
       </c>
       <c r="Q22">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R22">
         <v>1.33</v>
       </c>
       <c r="S22">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T22">
         <v>1.81</v>
       </c>
       <c r="U22">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V22">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="X22">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y22">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z22">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA22">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB22">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>8.4</v>
       </c>
       <c r="AD22">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE22">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF22">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH22">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI22">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ22">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AK22">
         <v>24</v>
       </c>
       <c r="AL22">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AM22">
         <v>120</v>
       </c>
       <c r="AN22">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AO22">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP22">
         <v>11.5</v>
       </c>
       <c r="AQ22">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR22">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AS22">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AT22">
         <v>8</v>
       </c>
       <c r="AU22">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV22">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW22">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX22">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY22">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22">
         <v>16.5</v>
       </c>
       <c r="BA22">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BB22">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD22">
         <v>32</v>
       </c>
       <c r="BE22">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BF22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG22">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BH22">
         <v>3.75</v>
       </c>
       <c r="BI22">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ22">
         <v>11.5</v>
@@ -6137,40 +6137,40 @@
         <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BO22">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BP22">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BQ22">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS22">
         <v>22</v>
       </c>
       <c r="BT22">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU22">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BV22">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BW22">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BX22">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY22">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BZ22">
         <v>0</v>
@@ -6199,22 +6199,22 @@
         <v>160</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G23">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H23">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I23">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J23">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K23">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L23">
         <v>1.4</v>
@@ -6223,16 +6223,16 @@
         <v>1.07</v>
       </c>
       <c r="N23">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O23">
         <v>1.32</v>
       </c>
       <c r="P23">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q23">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R23">
         <v>1.37</v>
@@ -6241,25 +6241,25 @@
         <v>3.45</v>
       </c>
       <c r="T23">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="U23">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V23">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W23">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X23">
         <v>15</v>
       </c>
       <c r="Y23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z23">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA23">
         <v>38</v>
@@ -6268,10 +6268,10 @@
         <v>13</v>
       </c>
       <c r="AC23">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD23">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE23">
         <v>32</v>
@@ -6301,10 +6301,10 @@
         <v>110</v>
       </c>
       <c r="AN23">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AO23">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP23">
         <v>12.5</v>
@@ -6316,10 +6316,10 @@
         <v>14</v>
       </c>
       <c r="AS23">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU23">
         <v>7</v>
@@ -6331,7 +6331,7 @@
         <v>20</v>
       </c>
       <c r="AX23">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY23">
         <v>11.5</v>
@@ -6340,85 +6340,85 @@
         <v>14.5</v>
       </c>
       <c r="BA23">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB23">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC23">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD23">
         <v>36</v>
       </c>
       <c r="BE23">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BG23">
         <v>18</v>
       </c>
       <c r="BH23">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>3.05</v>
+        <v>1.24</v>
       </c>
       <c r="BJ23">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>6.8</v>
+        <v>1.24</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>11</v>
+        <v>1.74</v>
       </c>
       <c r="BN23">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>5.4</v>
+        <v>1.47</v>
       </c>
       <c r="BP23">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>8</v>
+        <v>1.18</v>
       </c>
       <c r="BR23">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="BT23">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>4.8</v>
+        <v>1.43</v>
       </c>
       <c r="BV23">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>7.4</v>
+        <v>1.64</v>
       </c>
       <c r="BX23">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>8.800000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="BZ23">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>8.199999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="CB23" t="s">
         <v>169</v>
@@ -6465,13 +6465,13 @@
         <v>1.12</v>
       </c>
       <c r="N24">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O24">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P24">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q24">
         <v>2.58</v>
@@ -6483,7 +6483,7 @@
         <v>5.2</v>
       </c>
       <c r="T24">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U24">
         <v>1.8</v>
@@ -6495,7 +6495,7 @@
         <v>1.78</v>
       </c>
       <c r="X24">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y24">
         <v>13.5</v>
@@ -6504,10 +6504,10 @@
         <v>28</v>
       </c>
       <c r="AA24">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB24">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC24">
         <v>7.4</v>
@@ -6516,7 +6516,7 @@
         <v>21</v>
       </c>
       <c r="AE24">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AF24">
         <v>12</v>
@@ -6525,10 +6525,10 @@
         <v>13.5</v>
       </c>
       <c r="AH24">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AI24">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AJ24">
         <v>34</v>
@@ -6537,16 +6537,16 @@
         <v>28</v>
       </c>
       <c r="AL24">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM24">
         <v>190</v>
       </c>
       <c r="AN24">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AO24">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP24">
         <v>8.199999999999999</v>
@@ -6558,7 +6558,7 @@
         <v>24</v>
       </c>
       <c r="AS24">
-        <v>8.199999999999999</v>
+        <v>65</v>
       </c>
       <c r="AT24">
         <v>6.8</v>
@@ -6570,7 +6570,7 @@
         <v>15.5</v>
       </c>
       <c r="AW24">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="AX24">
         <v>10</v>
@@ -6582,43 +6582,43 @@
         <v>19.5</v>
       </c>
       <c r="BA24">
-        <v>8.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BB24">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BC24">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BD24">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BE24">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF24">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BG24">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BH24">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI24">
         <v>2.36</v>
       </c>
       <c r="BJ24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK24">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL24">
         <v>220</v>
       </c>
       <c r="BM24">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="BN24">
         <v>4.8</v>
@@ -6630,37 +6630,37 @@
         <v>21</v>
       </c>
       <c r="BQ24">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR24">
         <v>46</v>
       </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT24">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU24">
         <v>5.6</v>
       </c>
       <c r="BV24">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX24">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ24">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB24" t="s">
         <v>169</v>
@@ -6683,16 +6683,16 @@
         <v>162</v>
       </c>
       <c r="F25">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="G25">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="H25">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I25">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="J25">
         <v>3.5</v>
@@ -6704,22 +6704,22 @@
         <v>1.44</v>
       </c>
       <c r="M25">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N25">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O25">
         <v>1.36</v>
       </c>
       <c r="P25">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q25">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S25">
         <v>3.85</v>
@@ -6728,13 +6728,13 @@
         <v>1.01</v>
       </c>
       <c r="U25">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W25">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6743,163 +6743,163 @@
         <v>1000</v>
       </c>
       <c r="Z25">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA25">
         <v>1000</v>
       </c>
       <c r="AB25">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AD25">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
         <v>1000</v>
       </c>
       <c r="AF25">
+        <v>1000</v>
+      </c>
+      <c r="AG25">
+        <v>13</v>
+      </c>
+      <c r="AH25">
+        <v>1000</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1000</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>1.26</v>
+      </c>
+      <c r="AQ25">
         <v>12</v>
       </c>
-      <c r="AG25">
-        <v>11</v>
-      </c>
-      <c r="AH25">
-        <v>22</v>
-      </c>
-      <c r="AI25">
-        <v>1000</v>
-      </c>
-      <c r="AJ25">
-        <v>1000</v>
-      </c>
-      <c r="AK25">
-        <v>1000</v>
-      </c>
-      <c r="AL25">
-        <v>1000</v>
-      </c>
-      <c r="AM25">
-        <v>1000</v>
-      </c>
-      <c r="AN25">
-        <v>1000</v>
-      </c>
-      <c r="AO25">
-        <v>1000</v>
-      </c>
-      <c r="AP25">
-        <v>1.01</v>
-      </c>
-      <c r="AQ25">
-        <v>1.01</v>
-      </c>
       <c r="AR25">
-        <v>19.5</v>
+        <v>1.23</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY25">
-        <v>8.800000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="AZ25">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BC25">
-        <v>16</v>
+        <v>1.27</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BH25">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
         <v>1.01</v>
       </c>
       <c r="BL25">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
         <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
         <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
         <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
         <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
         <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
         <v>1.01</v>
@@ -6925,16 +6925,16 @@
         <v>163</v>
       </c>
       <c r="F26">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G26">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H26">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I26">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>4</v>
@@ -6949,7 +6949,7 @@
         <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O26">
         <v>1.36</v>
@@ -6967,16 +6967,16 @@
         <v>3.8</v>
       </c>
       <c r="T26">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U26">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V26">
         <v>1.16</v>
       </c>
       <c r="W26">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X26">
         <v>16</v>
@@ -7018,7 +7018,7 @@
         <v>16.5</v>
       </c>
       <c r="AK26">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL26">
         <v>50</v>
@@ -7036,13 +7036,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ26">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT26">
         <v>6.6</v>
@@ -7051,10 +7051,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW26">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX26">
         <v>8</v>
@@ -7066,7 +7066,7 @@
         <v>21</v>
       </c>
       <c r="BA26">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB26">
         <v>13</v>
@@ -7075,76 +7075,76 @@
         <v>16</v>
       </c>
       <c r="BD26">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="BE26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF26">
         <v>9.4</v>
       </c>
       <c r="BG26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH26">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ26">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
         <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
         <v>169</v>
@@ -7338,55 +7338,55 @@
         <v>11.5</v>
       </c>
       <c r="BK27">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BN27">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BO27">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP27">
         <v>29</v>
       </c>
       <c r="BQ27">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BR27">
         <v>44</v>
       </c>
       <c r="BS27">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BT27">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BU27">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV27">
         <v>24</v>
       </c>
       <c r="BW27">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BX27">
         <v>40</v>
       </c>
       <c r="BY27">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BZ27">
         <v>34</v>
       </c>
       <c r="CA27">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="CB27" t="s">
         <v>169</v>
@@ -7409,19 +7409,19 @@
         <v>165</v>
       </c>
       <c r="F28">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="G28">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="H28">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I28">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J28">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K28">
         <v>3.5</v>
@@ -7436,7 +7436,7 @@
         <v>3.1</v>
       </c>
       <c r="O28">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P28">
         <v>1.68</v>
@@ -7451,16 +7451,16 @@
         <v>4.3</v>
       </c>
       <c r="T28">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U28">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V28">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W28">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="X28">
         <v>12.5</v>
@@ -7472,10 +7472,10 @@
         <v>25</v>
       </c>
       <c r="AA28">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB28">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC28">
         <v>8.4</v>
@@ -7487,10 +7487,10 @@
         <v>55</v>
       </c>
       <c r="AF28">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG28">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH28">
         <v>23</v>
@@ -7499,7 +7499,7 @@
         <v>70</v>
       </c>
       <c r="AJ28">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK28">
         <v>36</v>
@@ -7511,118 +7511,118 @@
         <v>150</v>
       </c>
       <c r="AN28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO28">
         <v>60</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT28">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="AU28">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="AV28">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE28">
-        <v>95</v>
+        <v>5.5</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH28">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
         <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
         <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
         <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
         <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
         <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
         <v>0</v>
@@ -7651,22 +7651,22 @@
         <v>166</v>
       </c>
       <c r="F29">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="G29">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="H29">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="I29">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="J29">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K29">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L29">
         <v>1.5</v>
@@ -7675,151 +7675,151 @@
         <v>1.1</v>
       </c>
       <c r="N29">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O29">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P29">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q29">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R29">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S29">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T29">
         <v>2</v>
       </c>
       <c r="U29">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V29">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="W29">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X29">
+        <v>13.5</v>
+      </c>
+      <c r="Y29">
+        <v>7.6</v>
+      </c>
+      <c r="Z29">
+        <v>14</v>
+      </c>
+      <c r="AA29">
+        <v>25</v>
+      </c>
+      <c r="AB29">
+        <v>16</v>
+      </c>
+      <c r="AC29">
+        <v>8</v>
+      </c>
+      <c r="AD29">
         <v>11</v>
       </c>
-      <c r="Y29">
-        <v>8</v>
-      </c>
-      <c r="Z29">
-        <v>15</v>
-      </c>
-      <c r="AA29">
-        <v>29</v>
-      </c>
-      <c r="AB29">
-        <v>12.5</v>
-      </c>
-      <c r="AC29">
-        <v>7.8</v>
-      </c>
-      <c r="AD29">
-        <v>11.5</v>
-      </c>
       <c r="AE29">
+        <v>25</v>
+      </c>
+      <c r="AF29">
+        <v>42</v>
+      </c>
+      <c r="AG29">
+        <v>23</v>
+      </c>
+      <c r="AH29">
         <v>27</v>
       </c>
-      <c r="AF29">
+      <c r="AI29">
+        <v>55</v>
+      </c>
+      <c r="AJ29">
+        <v>140</v>
+      </c>
+      <c r="AK29">
+        <v>90</v>
+      </c>
+      <c r="AL29">
+        <v>100</v>
+      </c>
+      <c r="AM29">
+        <v>190</v>
+      </c>
+      <c r="AN29">
+        <v>120</v>
+      </c>
+      <c r="AO29">
+        <v>20</v>
+      </c>
+      <c r="AP29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ29">
+        <v>6.6</v>
+      </c>
+      <c r="AR29">
+        <v>10</v>
+      </c>
+      <c r="AS29">
+        <v>21</v>
+      </c>
+      <c r="AT29">
+        <v>12</v>
+      </c>
+      <c r="AU29">
+        <v>7</v>
+      </c>
+      <c r="AV29">
+        <v>9.4</v>
+      </c>
+      <c r="AW29">
+        <v>21</v>
+      </c>
+      <c r="AX29">
+        <v>6</v>
+      </c>
+      <c r="AY29">
+        <v>17</v>
+      </c>
+      <c r="AZ29">
+        <v>19.5</v>
+      </c>
+      <c r="BA29">
         <v>30</v>
       </c>
-      <c r="AG29">
-        <v>17.5</v>
-      </c>
-      <c r="AH29">
-        <v>22</v>
-      </c>
-      <c r="AI29">
-        <v>60</v>
-      </c>
-      <c r="AJ29">
-        <v>120</v>
-      </c>
-      <c r="AK29">
-        <v>75</v>
-      </c>
-      <c r="AL29">
-        <v>90</v>
-      </c>
-      <c r="AM29">
-        <v>170</v>
-      </c>
-      <c r="AN29">
-        <v>100</v>
-      </c>
-      <c r="AO29">
-        <v>23</v>
-      </c>
-      <c r="AP29">
-        <v>9.6</v>
-      </c>
-      <c r="AQ29">
-        <v>7</v>
-      </c>
-      <c r="AR29">
-        <v>11</v>
-      </c>
-      <c r="AS29">
-        <v>8</v>
-      </c>
-      <c r="AT29">
-        <v>11</v>
-      </c>
-      <c r="AU29">
-        <v>6.8</v>
-      </c>
-      <c r="AV29">
-        <v>9.6</v>
-      </c>
-      <c r="AW29">
-        <v>22</v>
-      </c>
-      <c r="AX29">
-        <v>23</v>
-      </c>
-      <c r="AY29">
-        <v>15</v>
-      </c>
-      <c r="AZ29">
-        <v>18.5</v>
-      </c>
-      <c r="BA29">
-        <v>38</v>
-      </c>
       <c r="BB29">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BC29">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD29">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BE29">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BF29">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BG29">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH29">
         <v>3.45</v>
       </c>
       <c r="BI29">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ29">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BK29">
         <v>4.1</v>
@@ -7828,49 +7828,49 @@
         <v>1000</v>
       </c>
       <c r="BM29">
+        <v>5.8</v>
+      </c>
+      <c r="BN29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO29">
         <v>6.4</v>
       </c>
-      <c r="BN29">
-        <v>7.4</v>
-      </c>
-      <c r="BO29">
-        <v>6.2</v>
-      </c>
       <c r="BP29">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BQ29">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BR29">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BS29">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BT29">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BU29">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV29">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BW29">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BX29">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BY29">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BZ29">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA29">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="CB29" t="s">
         <v>169</v>
@@ -7893,37 +7893,37 @@
         <v>167</v>
       </c>
       <c r="F30">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G30">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="H30">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I30">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J30">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K30">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L30">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M30">
         <v>1.11</v>
       </c>
       <c r="N30">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O30">
         <v>1.48</v>
       </c>
       <c r="P30">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q30">
         <v>2.46</v>
@@ -7932,19 +7932,19 @@
         <v>1.23</v>
       </c>
       <c r="S30">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T30">
+        <v>2.16</v>
+      </c>
+      <c r="U30">
+        <v>1.77</v>
+      </c>
+      <c r="V30">
+        <v>1.21</v>
+      </c>
+      <c r="W30">
         <v>2.12</v>
-      </c>
-      <c r="U30">
-        <v>1.78</v>
-      </c>
-      <c r="V30">
-        <v>1.22</v>
-      </c>
-      <c r="W30">
-        <v>2.04</v>
       </c>
       <c r="X30">
         <v>11.5</v>
@@ -7953,37 +7953,37 @@
         <v>16</v>
       </c>
       <c r="Z30">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA30">
         <v>180</v>
       </c>
       <c r="AB30">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC30">
         <v>9</v>
       </c>
       <c r="AD30">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE30">
         <v>110</v>
       </c>
       <c r="AF30">
+        <v>11.5</v>
+      </c>
+      <c r="AG30">
         <v>12</v>
       </c>
-      <c r="AG30">
-        <v>12.5</v>
-      </c>
       <c r="AH30">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AI30">
         <v>120</v>
       </c>
       <c r="AJ30">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK30">
         <v>28</v>
@@ -7995,115 +7995,115 @@
         <v>210</v>
       </c>
       <c r="AN30">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO30">
         <v>170</v>
       </c>
       <c r="AP30">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ30">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR30">
         <v>26</v>
       </c>
       <c r="AS30">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT30">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AU30">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV30">
         <v>18.5</v>
       </c>
       <c r="AW30">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX30">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY30">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ30">
         <v>21</v>
       </c>
       <c r="BA30">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB30">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC30">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD30">
         <v>32</v>
       </c>
       <c r="BE30">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF30">
-        <v>17</v>
+        <v>4.8</v>
       </c>
       <c r="BG30">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH30">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BL30">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
         <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP30">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
         <v>1.01</v>
       </c>
       <c r="BR30">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
         <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV30">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
         <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
         <v>1.01</v>
@@ -8135,22 +8135,22 @@
         <v>168</v>
       </c>
       <c r="F31">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="G31">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="H31">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="I31">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="J31">
         <v>3.2</v>
       </c>
       <c r="K31">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L31">
         <v>1.46</v>
@@ -8159,16 +8159,16 @@
         <v>1.09</v>
       </c>
       <c r="N31">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O31">
         <v>1.39</v>
       </c>
       <c r="P31">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q31">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R31">
         <v>1.31</v>
@@ -8183,91 +8183,91 @@
         <v>2.08</v>
       </c>
       <c r="V31">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="X31">
+        <v>11.5</v>
+      </c>
+      <c r="Y31">
         <v>12</v>
       </c>
-      <c r="Y31">
-        <v>12.5</v>
-      </c>
       <c r="Z31">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA31">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB31">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC31">
         <v>7.2</v>
       </c>
       <c r="AD31">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE31">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF31">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG31">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH31">
         <v>18</v>
       </c>
       <c r="AI31">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL31">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="AM31">
         <v>120</v>
       </c>
       <c r="AN31">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO31">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP31">
         <v>10.5</v>
       </c>
       <c r="AQ31">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR31">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS31">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AT31">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU31">
         <v>6.6</v>
       </c>
       <c r="AV31">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW31">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AX31">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY31">
         <v>10.5</v>
@@ -8276,31 +8276,31 @@
         <v>15.5</v>
       </c>
       <c r="BA31">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB31">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BC31">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD31">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE31">
         <v>38</v>
       </c>
       <c r="BF31">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH31">
         <v>3.15</v>
       </c>
       <c r="BI31">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ31">
         <v>10.5</v>
@@ -8312,49 +8312,49 @@
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN31">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO31">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP31">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BQ31">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="BR31">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS31">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT31">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU31">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV31">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BW31">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX31">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY31">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ31">
         <v>34</v>
       </c>
       <c r="CA31">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB31" t="s">
         <v>169</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
@@ -523,7 +523,7 @@
     <t>Albion FC</t>
   </si>
   <si>
-    <t>2026-09-28 05:41:51</t>
+    <t>2026-09-28 07:53:38</t>
   </si>
 </sst>
 </file>
@@ -1117,79 +1117,79 @@
         <v>139</v>
       </c>
       <c r="F2">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G2">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="H2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J2">
         <v>3.6</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA2">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AB2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE2">
         <v>70</v>
@@ -1201,7 +1201,7 @@
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI2">
         <v>75</v>
@@ -1210,133 +1210,133 @@
         <v>22</v>
       </c>
       <c r="AK2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM2">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AN2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO2">
         <v>75</v>
       </c>
       <c r="AP2">
-        <v>3.65</v>
+        <v>14</v>
       </c>
       <c r="AQ2">
-        <v>3.6</v>
+        <v>15</v>
       </c>
       <c r="AR2">
+        <v>28</v>
+      </c>
+      <c r="AS2">
+        <v>65</v>
+      </c>
+      <c r="AT2">
+        <v>8</v>
+      </c>
+      <c r="AU2">
+        <v>7.6</v>
+      </c>
+      <c r="AV2">
+        <v>15.5</v>
+      </c>
+      <c r="AW2">
+        <v>32</v>
+      </c>
+      <c r="AX2">
+        <v>8.6</v>
+      </c>
+      <c r="AY2">
+        <v>8.6</v>
+      </c>
+      <c r="AZ2">
+        <v>15.5</v>
+      </c>
+      <c r="BA2">
+        <v>32</v>
+      </c>
+      <c r="BB2">
+        <v>18</v>
+      </c>
+      <c r="BC2">
+        <v>16</v>
+      </c>
+      <c r="BD2">
+        <v>22</v>
+      </c>
+      <c r="BE2">
+        <v>75</v>
+      </c>
+      <c r="BF2">
+        <v>9.4</v>
+      </c>
+      <c r="BG2">
+        <v>30</v>
+      </c>
+      <c r="BH2">
+        <v>4.2</v>
+      </c>
+      <c r="BI2">
+        <v>2.86</v>
+      </c>
+      <c r="BJ2">
+        <v>12</v>
+      </c>
+      <c r="BK2">
+        <v>3.5</v>
+      </c>
+      <c r="BL2">
+        <v>150</v>
+      </c>
+      <c r="BM2">
+        <v>90</v>
+      </c>
+      <c r="BN2">
+        <v>5.2</v>
+      </c>
+      <c r="BO2">
+        <v>3.55</v>
+      </c>
+      <c r="BP2">
+        <v>14.5</v>
+      </c>
+      <c r="BQ2">
+        <v>3.7</v>
+      </c>
+      <c r="BR2">
+        <v>32</v>
+      </c>
+      <c r="BS2">
+        <v>4.3</v>
+      </c>
+      <c r="BT2">
+        <v>9.6</v>
+      </c>
+      <c r="BU2">
+        <v>6.2</v>
+      </c>
+      <c r="BV2">
+        <v>48</v>
+      </c>
+      <c r="BW2">
         <v>4.5</v>
       </c>
-      <c r="AS2">
-        <v>4.3</v>
-      </c>
-      <c r="AT2">
-        <v>3.55</v>
-      </c>
-      <c r="AU2">
-        <v>3.3</v>
-      </c>
-      <c r="AV2">
-        <v>3.7</v>
-      </c>
-      <c r="AW2">
+      <c r="BX2">
+        <v>60</v>
+      </c>
+      <c r="BY2">
+        <v>4.6</v>
+      </c>
+      <c r="BZ2">
+        <v>26</v>
+      </c>
+      <c r="CA2">
         <v>4.2</v>
-      </c>
-      <c r="AX2">
-        <v>3.65</v>
-      </c>
-      <c r="AY2">
-        <v>3.5</v>
-      </c>
-      <c r="AZ2">
-        <v>4.4</v>
-      </c>
-      <c r="BA2">
-        <v>4.2</v>
-      </c>
-      <c r="BB2">
-        <v>3.7</v>
-      </c>
-      <c r="BC2">
-        <v>3.7</v>
-      </c>
-      <c r="BD2">
-        <v>4</v>
-      </c>
-      <c r="BE2">
-        <v>4.3</v>
-      </c>
-      <c r="BF2">
-        <v>3.65</v>
-      </c>
-      <c r="BG2">
-        <v>4.2</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.01</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>1.01</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.01</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>1.01</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>1.01</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.01</v>
-      </c>
-      <c r="BT2">
-        <v>1000</v>
-      </c>
-      <c r="BU2">
-        <v>1.01</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>1.01</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>1.01</v>
-      </c>
-      <c r="BZ2">
-        <v>1000</v>
-      </c>
-      <c r="CA2">
-        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>169</v>
@@ -1359,157 +1359,157 @@
         <v>140</v>
       </c>
       <c r="F3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G3">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H3">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
         <v>4.5</v>
       </c>
-      <c r="J3">
-        <v>4.2</v>
-      </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q3">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="R3">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S3">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="T3">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="U3">
         <v>2.42</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X3">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="Y3">
         <v>21</v>
       </c>
       <c r="Z3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA3">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AB3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AF3">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AI3">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL3">
+        <v>30</v>
+      </c>
+      <c r="AM3">
+        <v>100</v>
+      </c>
+      <c r="AN3">
+        <v>11.5</v>
+      </c>
+      <c r="AO3">
         <v>34</v>
       </c>
-      <c r="AM3">
-        <v>85</v>
-      </c>
-      <c r="AN3">
-        <v>12</v>
-      </c>
-      <c r="AO3">
-        <v>42</v>
-      </c>
       <c r="AP3">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AQ3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AS3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AT3">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV3">
         <v>13</v>
       </c>
       <c r="AW3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AX3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BB3">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC3">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BD3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE3">
         <v>55</v>
@@ -1518,67 +1518,67 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BH3">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BI3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
         <v>14.5</v>
       </c>
       <c r="BQ3">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="BR3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS3">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BT3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BU3">
         <v>6</v>
       </c>
       <c r="BV3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW3">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA3">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="CB3" t="s">
         <v>169</v>
@@ -1601,25 +1601,25 @@
         <v>141</v>
       </c>
       <c r="F4">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="G4">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
-        <v>110</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1628,19 +1628,19 @@
         <v>3.05</v>
       </c>
       <c r="O4">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
         <v>1.24</v>
       </c>
       <c r="S4">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1649,10 +1649,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W4">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1709,7 +1709,7 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
         <v>1.01</v>
@@ -1730,7 +1730,7 @@
         <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
         <v>1.01</v>
@@ -1843,43 +1843,43 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>2.32</v>
+        <v>2.82</v>
       </c>
       <c r="G5">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="H5">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="I5">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K5">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
         <v>3.6</v>
@@ -1888,121 +1888,121 @@
         <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="W5">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF5">
         <v>1000</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ5">
         <v>1000</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2085,226 +2085,226 @@
         <v>143</v>
       </c>
       <c r="F6">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="G6">
-        <v>110</v>
+        <v>5.3</v>
       </c>
       <c r="H6">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="J6">
-        <v>1.12</v>
+        <v>3.6</v>
       </c>
       <c r="K6">
-        <v>930</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
+        <v>3.95</v>
+      </c>
+      <c r="O6">
+        <v>1.27</v>
+      </c>
+      <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6">
+        <v>1.83</v>
+      </c>
+      <c r="R6">
+        <v>1.39</v>
+      </c>
+      <c r="S6">
+        <v>3.1</v>
+      </c>
+      <c r="T6">
+        <v>1.74</v>
+      </c>
+      <c r="U6">
+        <v>1.95</v>
+      </c>
+      <c r="V6">
+        <v>2.08</v>
+      </c>
+      <c r="W6">
+        <v>1.23</v>
+      </c>
+      <c r="X6">
+        <v>21</v>
+      </c>
+      <c r="Y6">
+        <v>11.5</v>
+      </c>
+      <c r="Z6">
+        <v>14.5</v>
+      </c>
+      <c r="AA6">
+        <v>25</v>
+      </c>
+      <c r="AB6">
+        <v>22</v>
+      </c>
+      <c r="AC6">
+        <v>11</v>
+      </c>
+      <c r="AD6">
+        <v>12.5</v>
+      </c>
+      <c r="AE6">
+        <v>23</v>
+      </c>
+      <c r="AF6">
+        <v>44</v>
+      </c>
+      <c r="AG6">
+        <v>23</v>
+      </c>
+      <c r="AH6">
+        <v>22</v>
+      </c>
+      <c r="AI6">
+        <v>40</v>
+      </c>
+      <c r="AJ6">
+        <v>130</v>
+      </c>
+      <c r="AK6">
+        <v>70</v>
+      </c>
+      <c r="AL6">
+        <v>75</v>
+      </c>
+      <c r="AM6">
+        <v>110</v>
+      </c>
+      <c r="AN6">
+        <v>70</v>
+      </c>
+      <c r="AO6">
+        <v>13.5</v>
+      </c>
+      <c r="AP6">
+        <v>3.6</v>
+      </c>
+      <c r="AQ6">
+        <v>3.15</v>
+      </c>
+      <c r="AR6">
+        <v>3.35</v>
+      </c>
+      <c r="AS6">
+        <v>3.7</v>
+      </c>
+      <c r="AT6">
+        <v>3.65</v>
+      </c>
+      <c r="AU6">
+        <v>3.1</v>
+      </c>
+      <c r="AV6">
+        <v>3.25</v>
+      </c>
+      <c r="AW6">
+        <v>3.65</v>
+      </c>
+      <c r="AX6">
+        <v>4</v>
+      </c>
+      <c r="AY6">
+        <v>3.65</v>
+      </c>
+      <c r="AZ6">
+        <v>3.65</v>
+      </c>
+      <c r="BA6">
+        <v>3.95</v>
+      </c>
+      <c r="BB6">
+        <v>4.2</v>
+      </c>
+      <c r="BC6">
         <v>4.1</v>
       </c>
-      <c r="O6">
-        <v>1.24</v>
-      </c>
-      <c r="P6">
-        <v>2.12</v>
-      </c>
-      <c r="Q6">
-        <v>1.66</v>
-      </c>
-      <c r="R6">
-        <v>1.43</v>
-      </c>
-      <c r="S6">
-        <v>2.64</v>
-      </c>
-      <c r="T6">
-        <v>1.01</v>
-      </c>
-      <c r="U6">
-        <v>1.01</v>
-      </c>
-      <c r="V6">
-        <v>2</v>
-      </c>
-      <c r="W6">
-        <v>1.01</v>
-      </c>
-      <c r="X6">
-        <v>1000</v>
-      </c>
-      <c r="Y6">
-        <v>1000</v>
-      </c>
-      <c r="Z6">
-        <v>1000</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>1000</v>
-      </c>
-      <c r="AC6">
-        <v>1000</v>
-      </c>
-      <c r="AD6">
-        <v>1000</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>1000</v>
-      </c>
-      <c r="AG6">
-        <v>1000</v>
-      </c>
-      <c r="AH6">
-        <v>1000</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>1000</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6">
-        <v>1.01</v>
-      </c>
-      <c r="AR6">
-        <v>1.01</v>
-      </c>
-      <c r="AS6">
-        <v>1.01</v>
-      </c>
-      <c r="AT6">
-        <v>1.01</v>
-      </c>
-      <c r="AU6">
-        <v>1.01</v>
-      </c>
-      <c r="AV6">
-        <v>1.01</v>
-      </c>
-      <c r="AW6">
-        <v>1.01</v>
-      </c>
-      <c r="AX6">
-        <v>1.01</v>
-      </c>
-      <c r="AY6">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6">
-        <v>1.01</v>
-      </c>
-      <c r="BA6">
-        <v>1.01</v>
-      </c>
-      <c r="BB6">
-        <v>1.01</v>
-      </c>
-      <c r="BC6">
-        <v>1.01</v>
-      </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM6">
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB6" t="s">
         <v>169</v>
@@ -2327,73 +2327,73 @@
         <v>144</v>
       </c>
       <c r="F7">
+        <v>2.92</v>
+      </c>
+      <c r="G7">
+        <v>2.96</v>
+      </c>
+      <c r="H7">
+        <v>2.8</v>
+      </c>
+      <c r="I7">
         <v>2.84</v>
       </c>
-      <c r="G7">
-        <v>2.86</v>
-      </c>
-      <c r="H7">
-        <v>2.86</v>
-      </c>
-      <c r="I7">
-        <v>2.9</v>
-      </c>
       <c r="J7">
+        <v>3.25</v>
+      </c>
+      <c r="K7">
         <v>3.3</v>
       </c>
-      <c r="K7">
-        <v>3.35</v>
-      </c>
       <c r="L7">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M7">
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="Q7">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R7">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T7">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W7">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y7">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>7.2</v>
@@ -2402,7 +2402,7 @@
         <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF7">
         <v>18</v>
@@ -2411,25 +2411,25 @@
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI7">
+        <v>50</v>
+      </c>
+      <c r="AJ7">
         <v>48</v>
       </c>
-      <c r="AJ7">
-        <v>44</v>
-      </c>
       <c r="AK7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO7">
         <v>34</v>
@@ -2438,10 +2438,10 @@
         <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS7">
         <v>40</v>
@@ -2450,7 +2450,7 @@
         <v>9.6</v>
       </c>
       <c r="AU7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
         <v>11.5</v>
@@ -2462,91 +2462,91 @@
         <v>16.5</v>
       </c>
       <c r="AY7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA7">
+        <v>44</v>
+      </c>
+      <c r="BB7">
         <v>42</v>
-      </c>
-      <c r="BB7">
-        <v>40</v>
       </c>
       <c r="BC7">
         <v>30</v>
       </c>
       <c r="BD7">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BE7">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BF7">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BG7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH7">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BI7">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM7">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BN7">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BO7">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ7">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS7">
-        <v>2.9</v>
+        <v>11.5</v>
       </c>
       <c r="BT7">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BU7">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW7">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY7">
-        <v>2.9</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA7">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="CB7" t="s">
         <v>169</v>
@@ -2569,31 +2569,31 @@
         <v>145</v>
       </c>
       <c r="F8">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H8">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="I8">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="J8">
         <v>3.3</v>
       </c>
       <c r="K8">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L8">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O8">
         <v>1.4</v>
@@ -2608,34 +2608,34 @@
         <v>1.3</v>
       </c>
       <c r="S8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T8">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U8">
         <v>2.08</v>
       </c>
       <c r="V8">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="W8">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X8">
         <v>12</v>
       </c>
       <c r="Y8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC8">
         <v>7.2</v>
@@ -2647,46 +2647,46 @@
         <v>32</v>
       </c>
       <c r="AF8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK8">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL8">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM8">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AP8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR8">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT8">
         <v>10</v>
@@ -2698,97 +2698,97 @@
         <v>11</v>
       </c>
       <c r="AW8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ8">
         <v>16</v>
       </c>
       <c r="BA8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB8">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BC8">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BD8">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF8">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BG8">
         <v>25</v>
       </c>
       <c r="BH8">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BI8">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM8">
-        <v>2.82</v>
+        <v>11</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO8">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ8">
-        <v>2.82</v>
+        <v>8.6</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS8">
-        <v>2.82</v>
+        <v>9.6</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU8">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW8">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY8">
-        <v>2.82</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA8">
-        <v>2.82</v>
+        <v>9.4</v>
       </c>
       <c r="CB8" t="s">
         <v>169</v>
@@ -2817,16 +2817,16 @@
         <v>2.82</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I9">
         <v>3.05</v>
       </c>
       <c r="J9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L9">
         <v>1.56</v>
@@ -2835,7 +2835,7 @@
         <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O9">
         <v>1.5</v>
@@ -2844,16 +2844,16 @@
         <v>1.63</v>
       </c>
       <c r="Q9">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R9">
         <v>1.22</v>
       </c>
       <c r="S9">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T9">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U9">
         <v>1.88</v>
@@ -2865,7 +2865,7 @@
         <v>1.55</v>
       </c>
       <c r="X9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y9">
         <v>9.199999999999999</v>
@@ -2895,7 +2895,7 @@
         <v>13</v>
       </c>
       <c r="AH9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI9">
         <v>65</v>
@@ -2913,13 +2913,13 @@
         <v>150</v>
       </c>
       <c r="AN9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP9">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ9">
         <v>8.6</v>
@@ -2964,7 +2964,7 @@
         <v>48</v>
       </c>
       <c r="BE9">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BF9">
         <v>36</v>
@@ -2973,64 +2973,64 @@
         <v>42</v>
       </c>
       <c r="BH9">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BI9">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>15</v>
+        <v>2.96</v>
       </c>
       <c r="BN9">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BP9">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>10</v>
+        <v>3.15</v>
       </c>
       <c r="BR9">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>12</v>
+        <v>3.15</v>
       </c>
       <c r="BT9">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV9">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>10.5</v>
+        <v>3.15</v>
       </c>
       <c r="BX9">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>12</v>
+        <v>3.15</v>
       </c>
       <c r="BZ9">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>12</v>
+        <v>3.15</v>
       </c>
       <c r="CB9" t="s">
         <v>169</v>
@@ -3053,22 +3053,22 @@
         <v>147</v>
       </c>
       <c r="F10">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="G10">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="H10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I10">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K10">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L10">
         <v>1.3</v>
@@ -3077,199 +3077,199 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O10">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q10">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="R10">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S10">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="T10">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V10">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W10">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X10">
         <v>26</v>
       </c>
       <c r="Y10">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF10">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG10">
         <v>12</v>
       </c>
       <c r="AH10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ10">
+        <v>25</v>
+      </c>
+      <c r="AK10">
         <v>21</v>
-      </c>
-      <c r="AK10">
-        <v>18.5</v>
       </c>
       <c r="AL10">
         <v>32</v>
       </c>
       <c r="AM10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN10">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>4.2</v>
+        <v>2.34</v>
       </c>
       <c r="AQ10">
-        <v>4.2</v>
+        <v>2.58</v>
       </c>
       <c r="AR10">
-        <v>4.6</v>
+        <v>2.58</v>
       </c>
       <c r="AS10">
+        <v>2.58</v>
+      </c>
+      <c r="AT10">
+        <v>2.16</v>
+      </c>
+      <c r="AU10">
+        <v>2.58</v>
+      </c>
+      <c r="AV10">
+        <v>2.3</v>
+      </c>
+      <c r="AW10">
+        <v>2.46</v>
+      </c>
+      <c r="AX10">
+        <v>2.22</v>
+      </c>
+      <c r="AY10">
+        <v>2.12</v>
+      </c>
+      <c r="AZ10">
+        <v>2.28</v>
+      </c>
+      <c r="BA10">
+        <v>2.46</v>
+      </c>
+      <c r="BB10">
+        <v>2.34</v>
+      </c>
+      <c r="BC10">
+        <v>2.3</v>
+      </c>
+      <c r="BD10">
+        <v>2.38</v>
+      </c>
+      <c r="BE10">
+        <v>2.5</v>
+      </c>
+      <c r="BF10">
+        <v>2.1</v>
+      </c>
+      <c r="BG10">
+        <v>2.58</v>
+      </c>
+      <c r="BH10">
         <v>4.9</v>
       </c>
-      <c r="AT10">
-        <v>3.65</v>
-      </c>
-      <c r="AU10">
-        <v>3.55</v>
-      </c>
-      <c r="AV10">
-        <v>4.1</v>
-      </c>
-      <c r="AW10">
-        <v>4.7</v>
-      </c>
-      <c r="AX10">
-        <v>3.75</v>
-      </c>
-      <c r="AY10">
-        <v>3.55</v>
-      </c>
-      <c r="AZ10">
-        <v>4</v>
-      </c>
-      <c r="BA10">
-        <v>4.7</v>
-      </c>
-      <c r="BB10">
-        <v>4.1</v>
-      </c>
-      <c r="BC10">
-        <v>4</v>
-      </c>
-      <c r="BD10">
-        <v>4.4</v>
-      </c>
-      <c r="BE10">
-        <v>4.8</v>
-      </c>
-      <c r="BF10">
-        <v>3.2</v>
-      </c>
-      <c r="BG10">
-        <v>5.1</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK10">
         <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM10">
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS10">
         <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU10">
         <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY10">
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA10">
         <v>1.01</v>
@@ -3295,64 +3295,64 @@
         <v>148</v>
       </c>
       <c r="F11">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G11">
         <v>2.46</v>
       </c>
       <c r="H11">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="I11">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J11">
         <v>2.9</v>
       </c>
       <c r="K11">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L11">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M11">
         <v>1.12</v>
       </c>
       <c r="N11">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="O11">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P11">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="Q11">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="R11">
         <v>1.18</v>
       </c>
       <c r="S11">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T11">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U11">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V11">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X11">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z11">
         <v>28</v>
@@ -3370,49 +3370,49 @@
         <v>18.5</v>
       </c>
       <c r="AE11">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG11">
         <v>13</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI11">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL11">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM11">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO11">
         <v>120</v>
       </c>
       <c r="AP11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ11">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR11">
         <v>21</v>
       </c>
       <c r="AS11">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AT11">
         <v>6</v>
@@ -3421,79 +3421,79 @@
         <v>6</v>
       </c>
       <c r="AV11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW11">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AX11">
         <v>11</v>
       </c>
       <c r="AY11">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="BB11">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BC11">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BD11">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BE11">
-        <v>150</v>
+        <v>7.6</v>
       </c>
       <c r="BF11">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BG11">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="BH11">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI11">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ11">
         <v>13</v>
       </c>
       <c r="BK11">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BL11">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="BM11">
         <v>21</v>
       </c>
       <c r="BN11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO11">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BR11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS11">
         <v>32</v>
       </c>
       <c r="BT11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU11">
         <v>5.4</v>
@@ -3537,13 +3537,13 @@
         <v>149</v>
       </c>
       <c r="F12">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="G12">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I12">
         <v>5.6</v>
@@ -3552,166 +3552,166 @@
         <v>3.15</v>
       </c>
       <c r="K12">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="L12">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="M12">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N12">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="O12">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="P12">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Q12">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S12">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="T12">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="U12">
         <v>1.59</v>
       </c>
       <c r="V12">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W12">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z12">
         <v>50</v>
       </c>
       <c r="AA12">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AB12">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC12">
         <v>8.4</v>
       </c>
       <c r="AD12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE12">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF12">
         <v>13</v>
       </c>
       <c r="AG12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AI12">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AJ12">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK12">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL12">
         <v>100</v>
       </c>
       <c r="AM12">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="AN12">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO12">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="AP12">
+        <v>4.2</v>
+      </c>
+      <c r="AQ12">
+        <v>4.5</v>
+      </c>
+      <c r="AR12">
+        <v>5.1</v>
+      </c>
+      <c r="AS12">
+        <v>5.6</v>
+      </c>
+      <c r="AT12">
+        <v>3.55</v>
+      </c>
+      <c r="AU12">
+        <v>3.85</v>
+      </c>
+      <c r="AV12">
+        <v>4.7</v>
+      </c>
+      <c r="AW12">
+        <v>5.6</v>
+      </c>
+      <c r="AX12">
+        <v>4.4</v>
+      </c>
+      <c r="AY12">
+        <v>4.5</v>
+      </c>
+      <c r="AZ12">
+        <v>4.8</v>
+      </c>
+      <c r="BA12">
+        <v>5.6</v>
+      </c>
+      <c r="BB12">
+        <v>4.8</v>
+      </c>
+      <c r="BC12">
+        <v>4.9</v>
+      </c>
+      <c r="BD12">
+        <v>5.4</v>
+      </c>
+      <c r="BE12">
         <v>5.7</v>
       </c>
-      <c r="AQ12">
-        <v>8.6</v>
-      </c>
-      <c r="AR12">
+      <c r="BF12">
+        <v>5.3</v>
+      </c>
+      <c r="BG12">
+        <v>5.6</v>
+      </c>
+      <c r="BH12">
+        <v>3.1</v>
+      </c>
+      <c r="BI12">
+        <v>2.24</v>
+      </c>
+      <c r="BJ12">
+        <v>13</v>
+      </c>
+      <c r="BK12">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT12">
-        <v>4.4</v>
-      </c>
-      <c r="AU12">
-        <v>5.3</v>
-      </c>
-      <c r="AV12">
-        <v>17</v>
-      </c>
-      <c r="AW12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX12">
-        <v>5.8</v>
-      </c>
-      <c r="AY12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB12">
-        <v>19</v>
-      </c>
-      <c r="BC12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF12">
-        <v>21</v>
-      </c>
-      <c r="BG12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH12">
-        <v>2.86</v>
-      </c>
-      <c r="BI12">
-        <v>2.08</v>
-      </c>
-      <c r="BJ12">
-        <v>15.5</v>
-      </c>
-      <c r="BK12">
-        <v>9.4</v>
-      </c>
       <c r="BL12">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="BM12">
         <v>6.2</v>
@@ -3723,31 +3723,31 @@
         <v>3.65</v>
       </c>
       <c r="BP12">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BQ12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BS12">
         <v>5.7</v>
       </c>
       <c r="BT12">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV12">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BW12">
         <v>5.8</v>
       </c>
       <c r="BX12">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="BY12">
         <v>6</v>
@@ -3779,22 +3779,22 @@
         <v>150</v>
       </c>
       <c r="F13">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G13">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H13">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I13">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J13">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="K13">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="L13">
         <v>1.66</v>
@@ -3803,7 +3803,7 @@
         <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="O13">
         <v>1.67</v>
@@ -3812,13 +3812,13 @@
         <v>1.35</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="R13">
         <v>1.13</v>
       </c>
       <c r="S13">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="T13">
         <v>2.26</v>
@@ -3830,7 +3830,7 @@
         <v>1.45</v>
       </c>
       <c r="W13">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X13">
         <v>8.199999999999999</v>
@@ -3839,10 +3839,10 @@
         <v>8</v>
       </c>
       <c r="Z13">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA13">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB13">
         <v>8.4</v>
@@ -3860,7 +3860,7 @@
         <v>21</v>
       </c>
       <c r="AG13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH13">
         <v>40</v>
@@ -3950,34 +3950,34 @@
         <v>13</v>
       </c>
       <c r="BK13">
-        <v>9.199999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="BL13">
         <v>340</v>
       </c>
       <c r="BM13">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO13">
         <v>4.5</v>
       </c>
       <c r="BP13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ13">
-        <v>8.800000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="BR13">
         <v>75</v>
       </c>
       <c r="BS13">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU13">
         <v>4.4</v>
@@ -3986,13 +3986,13 @@
         <v>38</v>
       </c>
       <c r="BW13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
         <v>75</v>
       </c>
       <c r="BY13">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -4027,10 +4027,10 @@
         <v>2.44</v>
       </c>
       <c r="H14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I14">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J14">
         <v>2.58</v>
@@ -4048,13 +4048,13 @@
         <v>1.95</v>
       </c>
       <c r="O14">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="P14">
         <v>1.34</v>
       </c>
       <c r="Q14">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="R14">
         <v>1.12</v>
@@ -4063,13 +4063,13 @@
         <v>1.01</v>
       </c>
       <c r="T14">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="U14">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V14">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W14">
         <v>1.69</v>
@@ -4078,7 +4078,7 @@
         <v>6.6</v>
       </c>
       <c r="Y14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z14">
         <v>34</v>
@@ -4087,7 +4087,7 @@
         <v>160</v>
       </c>
       <c r="AB14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC14">
         <v>7.6</v>
@@ -4129,58 +4129,58 @@
         <v>230</v>
       </c>
       <c r="AP14">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AQ14">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AR14">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AS14">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AT14">
         <v>5.1</v>
       </c>
       <c r="AU14">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AV14">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AW14">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AX14">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AY14">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AZ14">
+        <v>6.6</v>
+      </c>
+      <c r="BA14">
+        <v>7.8</v>
+      </c>
+      <c r="BB14">
+        <v>6.6</v>
+      </c>
+      <c r="BC14">
+        <v>6.8</v>
+      </c>
+      <c r="BD14">
+        <v>7.4</v>
+      </c>
+      <c r="BE14">
+        <v>8</v>
+      </c>
+      <c r="BF14">
         <v>7</v>
       </c>
-      <c r="BA14">
-        <v>8.4</v>
-      </c>
-      <c r="BB14">
-        <v>7</v>
-      </c>
-      <c r="BC14">
-        <v>7.2</v>
-      </c>
-      <c r="BD14">
-        <v>8</v>
-      </c>
-      <c r="BE14">
-        <v>8.6</v>
-      </c>
-      <c r="BF14">
-        <v>7.4</v>
-      </c>
       <c r="BG14">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH14">
         <v>2.58</v>
@@ -4263,22 +4263,22 @@
         <v>152</v>
       </c>
       <c r="F15">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="G15">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="H15">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="I15">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="J15">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K15">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
         <v>1.42</v>
@@ -4293,193 +4293,193 @@
         <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="Q15">
+        <v>1.98</v>
+      </c>
+      <c r="R15">
+        <v>1.28</v>
+      </c>
+      <c r="S15">
         <v>2</v>
       </c>
-      <c r="R15">
-        <v>1.27</v>
-      </c>
-      <c r="S15">
-        <v>1.01</v>
-      </c>
       <c r="T15">
         <v>1.01</v>
       </c>
       <c r="U15">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X15">
         <v>970</v>
       </c>
       <c r="Y15">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="Z15">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AA15">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AB15">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC15">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD15">
         <v>970</v>
       </c>
       <c r="AE15">
+        <v>70</v>
+      </c>
+      <c r="AF15">
+        <v>970</v>
+      </c>
+      <c r="AG15">
+        <v>21</v>
+      </c>
+      <c r="AH15">
+        <v>970</v>
+      </c>
+      <c r="AI15">
+        <v>110</v>
+      </c>
+      <c r="AJ15">
+        <v>65</v>
+      </c>
+      <c r="AK15">
+        <v>65</v>
+      </c>
+      <c r="AL15">
+        <v>95</v>
+      </c>
+      <c r="AM15">
+        <v>120</v>
+      </c>
+      <c r="AN15">
+        <v>46</v>
+      </c>
+      <c r="AO15">
         <v>55</v>
       </c>
-      <c r="AF15">
+      <c r="AP15">
+        <v>5.4</v>
+      </c>
+      <c r="AQ15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15">
+        <v>15.5</v>
+      </c>
+      <c r="AS15">
         <v>23</v>
       </c>
-      <c r="AG15">
-        <v>15</v>
-      </c>
-      <c r="AH15">
-        <v>23</v>
-      </c>
-      <c r="AI15">
-        <v>80</v>
-      </c>
-      <c r="AJ15">
-        <v>50</v>
-      </c>
-      <c r="AK15">
-        <v>50</v>
-      </c>
-      <c r="AL15">
-        <v>75</v>
-      </c>
-      <c r="AM15">
-        <v>130</v>
-      </c>
-      <c r="AN15">
-        <v>40</v>
-      </c>
-      <c r="AO15">
-        <v>42</v>
-      </c>
-      <c r="AP15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR15">
-        <v>13.5</v>
-      </c>
-      <c r="AS15">
-        <v>21</v>
-      </c>
       <c r="AT15">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="AU15">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="AV15">
         <v>9.6</v>
       </c>
       <c r="AW15">
+        <v>19.5</v>
+      </c>
+      <c r="AX15">
+        <v>7.8</v>
+      </c>
+      <c r="AY15">
+        <v>5.4</v>
+      </c>
+      <c r="AZ15">
+        <v>7.8</v>
+      </c>
+      <c r="BA15">
+        <v>22</v>
+      </c>
+      <c r="BB15">
         <v>15</v>
       </c>
-      <c r="AX15">
-        <v>12.5</v>
-      </c>
-      <c r="AY15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ15">
-        <v>13</v>
-      </c>
-      <c r="BA15">
-        <v>21</v>
-      </c>
-      <c r="BB15">
+      <c r="BC15">
+        <v>14</v>
+      </c>
+      <c r="BD15">
         <v>18</v>
-      </c>
-      <c r="BC15">
-        <v>13.5</v>
-      </c>
-      <c r="BD15">
-        <v>19</v>
       </c>
       <c r="BE15">
         <v>44</v>
       </c>
       <c r="BF15">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BG15">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BH15">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
         <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
         <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
         <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
         <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
         <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
         <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
         <v>1.01</v>
@@ -4508,7 +4508,7 @@
         <v>3.35</v>
       </c>
       <c r="G16">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H16">
         <v>2.34</v>
@@ -4517,7 +4517,7 @@
         <v>2.38</v>
       </c>
       <c r="J16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K16">
         <v>3.55</v>
@@ -4535,31 +4535,31 @@
         <v>1.31</v>
       </c>
       <c r="P16">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q16">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R16">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S16">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T16">
         <v>1.75</v>
       </c>
       <c r="U16">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V16">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W16">
         <v>1.4</v>
       </c>
       <c r="X16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y16">
         <v>11</v>
@@ -4571,13 +4571,13 @@
         <v>32</v>
       </c>
       <c r="AB16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC16">
         <v>7.8</v>
       </c>
       <c r="AD16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE16">
         <v>25</v>
@@ -4610,7 +4610,7 @@
         <v>36</v>
       </c>
       <c r="AO16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP16">
         <v>13</v>
@@ -4655,76 +4655,76 @@
         <v>32</v>
       </c>
       <c r="BD16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE16">
         <v>38</v>
       </c>
       <c r="BF16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH16">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BI16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ16">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK16">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BL16">
         <v>130</v>
       </c>
       <c r="BM16">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="BN16">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO16">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BP16">
+        <v>27</v>
+      </c>
+      <c r="BQ16">
+        <v>20</v>
+      </c>
+      <c r="BR16">
+        <v>38</v>
+      </c>
+      <c r="BS16">
+        <v>10.5</v>
+      </c>
+      <c r="BT16">
+        <v>5.2</v>
+      </c>
+      <c r="BU16">
+        <v>4.7</v>
+      </c>
+      <c r="BV16">
+        <v>17.5</v>
+      </c>
+      <c r="BW16">
+        <v>12.5</v>
+      </c>
+      <c r="BX16">
         <v>30</v>
       </c>
-      <c r="BQ16">
-        <v>6.4</v>
-      </c>
-      <c r="BR16">
-        <v>42</v>
-      </c>
-      <c r="BS16">
-        <v>6.2</v>
-      </c>
-      <c r="BT16">
-        <v>5.5</v>
-      </c>
-      <c r="BU16">
-        <v>4.5</v>
-      </c>
-      <c r="BV16">
-        <v>19.5</v>
-      </c>
-      <c r="BW16">
-        <v>12</v>
-      </c>
-      <c r="BX16">
-        <v>34</v>
-      </c>
       <c r="BY16">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="BZ16">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="CA16">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="CB16" t="s">
         <v>169</v>
@@ -4753,214 +4753,214 @@
         <v>2.84</v>
       </c>
       <c r="H17">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="I17">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="J17">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K17">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L17">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M17">
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="O17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P17">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q17">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="R17">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S17">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="T17">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="U17">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="V17">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W17">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X17">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y17">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z17">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD17">
         <v>12</v>
       </c>
       <c r="AE17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG17">
         <v>12.5</v>
       </c>
       <c r="AH17">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AI17">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AJ17">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK17">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM17">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO17">
+        <v>16</v>
+      </c>
+      <c r="AP17">
+        <v>18.5</v>
+      </c>
+      <c r="AQ17">
+        <v>13.5</v>
+      </c>
+      <c r="AR17">
         <v>18</v>
       </c>
-      <c r="AP17">
-        <v>17</v>
-      </c>
-      <c r="AQ17">
-        <v>12.5</v>
-      </c>
-      <c r="AR17">
-        <v>17</v>
-      </c>
       <c r="AS17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT17">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU17">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV17">
         <v>11</v>
       </c>
       <c r="AW17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX17">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY17">
         <v>11.5</v>
       </c>
       <c r="AZ17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA17">
+        <v>29</v>
+      </c>
+      <c r="BB17">
+        <v>40</v>
+      </c>
+      <c r="BC17">
+        <v>25</v>
+      </c>
+      <c r="BD17">
         <v>30</v>
-      </c>
-      <c r="BB17">
-        <v>38</v>
-      </c>
-      <c r="BC17">
-        <v>26</v>
-      </c>
-      <c r="BD17">
-        <v>32</v>
       </c>
       <c r="BE17">
         <v>50</v>
       </c>
       <c r="BF17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG17">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BH17">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BI17">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="BJ17">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
+        <v>6.6</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>2.3</v>
+      </c>
+      <c r="BN17">
         <v>7.8</v>
       </c>
-      <c r="BL17">
-        <v>90</v>
-      </c>
-      <c r="BM17">
-        <v>13</v>
-      </c>
-      <c r="BN17">
-        <v>6.2</v>
-      </c>
       <c r="BO17">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP17">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="BR17">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BT17">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU17">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV17">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>16</v>
+        <v>2.38</v>
       </c>
       <c r="BX17">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>10</v>
+        <v>2.4</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -4989,37 +4989,37 @@
         <v>155</v>
       </c>
       <c r="F18">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G18">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="H18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I18">
+        <v>3.35</v>
+      </c>
+      <c r="J18">
         <v>3.4</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>3.45</v>
       </c>
-      <c r="K18">
-        <v>3.5</v>
-      </c>
       <c r="L18">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M18">
         <v>1.08</v>
       </c>
       <c r="N18">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O18">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P18">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q18">
         <v>2.14</v>
@@ -5028,28 +5028,28 @@
         <v>1.32</v>
       </c>
       <c r="S18">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T18">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U18">
         <v>2.12</v>
       </c>
       <c r="V18">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W18">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="X18">
         <v>12.5</v>
       </c>
       <c r="Y18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA18">
         <v>65</v>
@@ -5058,19 +5058,19 @@
         <v>9.4</v>
       </c>
       <c r="AC18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE18">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF18">
         <v>15</v>
       </c>
       <c r="AG18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH18">
         <v>18</v>
@@ -5091,10 +5091,10 @@
         <v>110</v>
       </c>
       <c r="AN18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO18">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP18">
         <v>11.5</v>
@@ -5103,25 +5103,25 @@
         <v>11</v>
       </c>
       <c r="AR18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS18">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT18">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV18">
         <v>13</v>
       </c>
       <c r="AW18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY18">
         <v>10.5</v>
@@ -5130,85 +5130,85 @@
         <v>16.5</v>
       </c>
       <c r="BA18">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB18">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC18">
+        <v>25</v>
+      </c>
+      <c r="BD18">
+        <v>38</v>
+      </c>
+      <c r="BE18">
+        <v>90</v>
+      </c>
+      <c r="BF18">
         <v>22</v>
-      </c>
-      <c r="BD18">
-        <v>36</v>
-      </c>
-      <c r="BE18">
-        <v>80</v>
-      </c>
-      <c r="BF18">
-        <v>20</v>
       </c>
       <c r="BG18">
         <v>38</v>
       </c>
       <c r="BH18">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BI18">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ18">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL18">
         <v>140</v>
       </c>
       <c r="BM18">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN18">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BO18">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP18">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ18">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BR18">
         <v>34</v>
       </c>
       <c r="BS18">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BT18">
         <v>6.4</v>
       </c>
       <c r="BU18">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BV18">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW18">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX18">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY18">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ18">
         <v>32</v>
       </c>
       <c r="CA18">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB18" t="s">
         <v>169</v>
@@ -5231,22 +5231,22 @@
         <v>156</v>
       </c>
       <c r="F19">
+        <v>4.1</v>
+      </c>
+      <c r="G19">
+        <v>4.2</v>
+      </c>
+      <c r="H19">
+        <v>1.94</v>
+      </c>
+      <c r="I19">
+        <v>1.95</v>
+      </c>
+      <c r="J19">
         <v>4</v>
       </c>
-      <c r="G19">
+      <c r="K19">
         <v>4.1</v>
-      </c>
-      <c r="H19">
-        <v>1.95</v>
-      </c>
-      <c r="I19">
-        <v>1.96</v>
-      </c>
-      <c r="J19">
-        <v>4.1</v>
-      </c>
-      <c r="K19">
-        <v>4.2</v>
       </c>
       <c r="L19">
         <v>1.3</v>
@@ -5255,34 +5255,34 @@
         <v>1.04</v>
       </c>
       <c r="N19">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O19">
         <v>1.2</v>
       </c>
       <c r="P19">
+        <v>2.54</v>
+      </c>
+      <c r="Q19">
+        <v>1.63</v>
+      </c>
+      <c r="R19">
+        <v>1.61</v>
+      </c>
+      <c r="S19">
         <v>2.58</v>
       </c>
-      <c r="Q19">
-        <v>1.61</v>
-      </c>
-      <c r="R19">
-        <v>1.64</v>
-      </c>
-      <c r="S19">
-        <v>2.52</v>
-      </c>
       <c r="T19">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U19">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V19">
         <v>2.04</v>
       </c>
       <c r="W19">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X19">
         <v>24</v>
@@ -5294,22 +5294,22 @@
         <v>14</v>
       </c>
       <c r="AA19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB19">
         <v>21</v>
       </c>
       <c r="AC19">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE19">
         <v>17</v>
       </c>
       <c r="AF19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG19">
         <v>16</v>
@@ -5321,13 +5321,13 @@
         <v>26</v>
       </c>
       <c r="AJ19">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK19">
+        <v>42</v>
+      </c>
+      <c r="AL19">
         <v>40</v>
-      </c>
-      <c r="AL19">
-        <v>42</v>
       </c>
       <c r="AM19">
         <v>60</v>
@@ -5336,7 +5336,7 @@
         <v>34</v>
       </c>
       <c r="AO19">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP19">
         <v>22</v>
@@ -5348,7 +5348,7 @@
         <v>13.5</v>
       </c>
       <c r="AS19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT19">
         <v>19.5</v>
@@ -5357,13 +5357,13 @@
         <v>9</v>
       </c>
       <c r="AV19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AY19">
         <v>15</v>
@@ -5372,10 +5372,10 @@
         <v>14</v>
       </c>
       <c r="BA19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB19">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BC19">
         <v>38</v>
@@ -5384,19 +5384,19 @@
         <v>38</v>
       </c>
       <c r="BE19">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BG19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH19">
         <v>4.3</v>
       </c>
       <c r="BI19">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BJ19">
         <v>8.800000000000001</v>
@@ -5408,31 +5408,31 @@
         <v>95</v>
       </c>
       <c r="BM19">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO19">
         <v>6.8</v>
       </c>
       <c r="BP19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ19">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BR19">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT19">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BU19">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV19">
         <v>12.5</v>
@@ -5441,13 +5441,13 @@
         <v>11</v>
       </c>
       <c r="BX19">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BY19">
         <v>17.5</v>
       </c>
       <c r="BZ19">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA19">
         <v>13.5</v>
@@ -5473,76 +5473,76 @@
         <v>157</v>
       </c>
       <c r="F20">
+        <v>3.05</v>
+      </c>
+      <c r="G20">
         <v>3.1</v>
       </c>
-      <c r="G20">
-        <v>3.15</v>
-      </c>
       <c r="H20">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="I20">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="J20">
+        <v>3.05</v>
+      </c>
+      <c r="K20">
         <v>3.1</v>
-      </c>
-      <c r="K20">
-        <v>3.15</v>
       </c>
       <c r="L20">
         <v>1.61</v>
       </c>
       <c r="M20">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N20">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O20">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P20">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q20">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="R20">
         <v>1.2</v>
       </c>
       <c r="S20">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T20">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U20">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V20">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W20">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X20">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y20">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z20">
         <v>16.5</v>
       </c>
       <c r="AA20">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD20">
         <v>13</v>
@@ -5551,16 +5551,16 @@
         <v>40</v>
       </c>
       <c r="AF20">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG20">
         <v>14</v>
       </c>
       <c r="AH20">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI20">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ20">
         <v>60</v>
@@ -5575,46 +5575,46 @@
         <v>170</v>
       </c>
       <c r="AN20">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO20">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP20">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ20">
         <v>7.8</v>
       </c>
       <c r="AR20">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS20">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AT20">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU20">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV20">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW20">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX20">
         <v>17.5</v>
       </c>
       <c r="AY20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ20">
         <v>21</v>
       </c>
       <c r="BA20">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB20">
         <v>50</v>
@@ -5629,70 +5629,70 @@
         <v>140</v>
       </c>
       <c r="BF20">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BG20">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH20">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="BI20">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK20">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL20">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BM20">
-        <v>3.9</v>
+        <v>12.5</v>
       </c>
       <c r="BN20">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BO20">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ20">
-        <v>3.65</v>
+        <v>9.6</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS20">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="BT20">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BU20">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW20">
-        <v>3.55</v>
+        <v>9.4</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY20">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA20">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="CB20" t="s">
         <v>169</v>
@@ -5715,25 +5715,25 @@
         <v>158</v>
       </c>
       <c r="F21">
+        <v>2.16</v>
+      </c>
+      <c r="G21">
         <v>2.18</v>
       </c>
-      <c r="G21">
-        <v>2.22</v>
-      </c>
       <c r="H21">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I21">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="J21">
+        <v>3.75</v>
+      </c>
+      <c r="K21">
         <v>3.8</v>
       </c>
-      <c r="K21">
-        <v>3.85</v>
-      </c>
       <c r="L21">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M21">
         <v>1.05</v>
@@ -5751,7 +5751,7 @@
         <v>1.72</v>
       </c>
       <c r="R21">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S21">
         <v>2.78</v>
@@ -5763,10 +5763,10 @@
         <v>2.62</v>
       </c>
       <c r="V21">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W21">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X21">
         <v>21</v>
@@ -5775,7 +5775,7 @@
         <v>17.5</v>
       </c>
       <c r="Z21">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA21">
         <v>75</v>
@@ -5793,7 +5793,7 @@
         <v>36</v>
       </c>
       <c r="AF21">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG21">
         <v>10.5</v>
@@ -5802,25 +5802,25 @@
         <v>14.5</v>
       </c>
       <c r="AI21">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ21">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL21">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM21">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN21">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO21">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AP21">
         <v>19</v>
@@ -5829,13 +5829,13 @@
         <v>16.5</v>
       </c>
       <c r="AR21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS21">
         <v>55</v>
       </c>
       <c r="AT21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU21">
         <v>8</v>
@@ -5847,7 +5847,7 @@
         <v>32</v>
       </c>
       <c r="AX21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY21">
         <v>10</v>
@@ -5856,34 +5856,34 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB21">
         <v>25</v>
       </c>
       <c r="BC21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD21">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE21">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF21">
         <v>11</v>
       </c>
       <c r="BG21">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BH21">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI21">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ21">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK21">
         <v>7.8</v>
@@ -5892,49 +5892,49 @@
         <v>100</v>
       </c>
       <c r="BM21">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BN21">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO21">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BQ21">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BR21">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BS21">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT21">
         <v>7</v>
       </c>
       <c r="BU21">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV21">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BW21">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX21">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY21">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA21">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB21" t="s">
         <v>169</v>
@@ -5957,25 +5957,25 @@
         <v>159</v>
       </c>
       <c r="F22">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="G22">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="H22">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="I22">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J22">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K22">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M22">
         <v>1.08</v>
@@ -5990,67 +5990,67 @@
         <v>1.89</v>
       </c>
       <c r="Q22">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R22">
         <v>1.33</v>
       </c>
       <c r="S22">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T22">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="U22">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="X22">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y22">
         <v>13.5</v>
       </c>
       <c r="Z22">
+        <v>24</v>
+      </c>
+      <c r="AA22">
+        <v>65</v>
+      </c>
+      <c r="AB22">
+        <v>10.5</v>
+      </c>
+      <c r="AC22">
+        <v>7.8</v>
+      </c>
+      <c r="AD22">
+        <v>14.5</v>
+      </c>
+      <c r="AE22">
+        <v>42</v>
+      </c>
+      <c r="AF22">
+        <v>16.5</v>
+      </c>
+      <c r="AG22">
+        <v>12</v>
+      </c>
+      <c r="AH22">
+        <v>18</v>
+      </c>
+      <c r="AI22">
+        <v>55</v>
+      </c>
+      <c r="AJ22">
+        <v>34</v>
+      </c>
+      <c r="AK22">
         <v>27</v>
-      </c>
-      <c r="AA22">
-        <v>80</v>
-      </c>
-      <c r="AB22">
-        <v>10</v>
-      </c>
-      <c r="AC22">
-        <v>8.4</v>
-      </c>
-      <c r="AD22">
-        <v>16</v>
-      </c>
-      <c r="AE22">
-        <v>48</v>
-      </c>
-      <c r="AF22">
-        <v>14.5</v>
-      </c>
-      <c r="AG22">
-        <v>11</v>
-      </c>
-      <c r="AH22">
-        <v>19.5</v>
-      </c>
-      <c r="AI22">
-        <v>60</v>
-      </c>
-      <c r="AJ22">
-        <v>30</v>
-      </c>
-      <c r="AK22">
-        <v>24</v>
       </c>
       <c r="AL22">
         <v>55</v>
@@ -6059,118 +6059,118 @@
         <v>120</v>
       </c>
       <c r="AN22">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AO22">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AP22">
+        <v>11</v>
+      </c>
+      <c r="AQ22">
         <v>11.5</v>
       </c>
-      <c r="AQ22">
+      <c r="AR22">
+        <v>20</v>
+      </c>
+      <c r="AS22">
+        <v>50</v>
+      </c>
+      <c r="AT22">
+        <v>8.6</v>
+      </c>
+      <c r="AU22">
+        <v>7</v>
+      </c>
+      <c r="AV22">
         <v>12.5</v>
       </c>
-      <c r="AR22">
-        <v>23</v>
-      </c>
-      <c r="AS22">
-        <v>55</v>
-      </c>
-      <c r="AT22">
-        <v>8</v>
-      </c>
-      <c r="AU22">
-        <v>7.2</v>
-      </c>
-      <c r="AV22">
-        <v>14</v>
-      </c>
       <c r="AW22">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AX22">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY22">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ22">
         <v>16.5</v>
       </c>
       <c r="BA22">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB22">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BC22">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD22">
         <v>32</v>
       </c>
       <c r="BE22">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF22">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BG22">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH22">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI22">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK22">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL22">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="BM22">
         <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BO22">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BP22">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BQ22">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BR22">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS22">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BT22">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BU22">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV22">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BW22">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BX22">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BY22">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BZ22">
         <v>0</v>
@@ -6199,16 +6199,16 @@
         <v>160</v>
       </c>
       <c r="F23">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G23">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H23">
         <v>2.42</v>
       </c>
       <c r="I23">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J23">
         <v>3.4</v>
@@ -6229,25 +6229,25 @@
         <v>1.32</v>
       </c>
       <c r="P23">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q23">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R23">
         <v>1.37</v>
       </c>
       <c r="S23">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T23">
         <v>1.74</v>
       </c>
       <c r="U23">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V23">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W23">
         <v>1.44</v>
@@ -6328,7 +6328,7 @@
         <v>10</v>
       </c>
       <c r="AW23">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX23">
         <v>19</v>
@@ -6361,64 +6361,64 @@
         <v>18</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI23">
-        <v>1.24</v>
+        <v>2.86</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK23">
-        <v>1.24</v>
+        <v>5.6</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.74</v>
+        <v>12.5</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO23">
-        <v>1.47</v>
+        <v>5.5</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ23">
-        <v>1.18</v>
+        <v>9</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS23">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU23">
-        <v>1.43</v>
+        <v>4.8</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW23">
-        <v>1.64</v>
+        <v>8</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY23">
-        <v>1.19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA23">
-        <v>1.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB23" t="s">
         <v>169</v>
@@ -6441,178 +6441,178 @@
         <v>161</v>
       </c>
       <c r="F24">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="H24">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I24">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="J24">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K24">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="L24">
         <v>1.55</v>
       </c>
       <c r="M24">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N24">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="O24">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P24">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="Q24">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="R24">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S24">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="T24">
         <v>2.1</v>
       </c>
       <c r="U24">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W24">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="X24">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z24">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AA24">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AB24">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC24">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD24">
         <v>21</v>
       </c>
       <c r="AE24">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF24">
+        <v>11</v>
+      </c>
+      <c r="AG24">
         <v>12</v>
       </c>
-      <c r="AG24">
-        <v>13.5</v>
-      </c>
       <c r="AH24">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI24">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ24">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AK24">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL24">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AM24">
         <v>190</v>
       </c>
       <c r="AN24">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AO24">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP24">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS24">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AT24">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU24">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV24">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW24">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AX24">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AY24">
         <v>10.5</v>
       </c>
       <c r="AZ24">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA24">
         <v>55</v>
       </c>
       <c r="BB24">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC24">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE24">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF24">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BG24">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BH24">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI24">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BJ24">
         <v>13</v>
       </c>
       <c r="BK24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL24">
         <v>220</v>
@@ -6621,43 +6621,43 @@
         <v>7.2</v>
       </c>
       <c r="BN24">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BO24">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BP24">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BQ24">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BR24">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BS24">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT24">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU24">
         <v>5.6</v>
       </c>
       <c r="BV24">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BW24">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX24">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BY24">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ24">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CA24">
         <v>6.4</v>
@@ -6686,22 +6686,22 @@
         <v>1.79</v>
       </c>
       <c r="G25">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="H25">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I25">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J25">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K25">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L25">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M25">
         <v>1.08</v>
@@ -6710,31 +6710,31 @@
         <v>3.35</v>
       </c>
       <c r="O25">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P25">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="Q25">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R25">
         <v>1.29</v>
       </c>
       <c r="S25">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V25">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W25">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6743,7 +6743,7 @@
         <v>1000</v>
       </c>
       <c r="Z25">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
         <v>1000</v>
@@ -6752,7 +6752,7 @@
         <v>1000</v>
       </c>
       <c r="AC25">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
         <v>1000</v>
@@ -6764,7 +6764,7 @@
         <v>1000</v>
       </c>
       <c r="AG25">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
         <v>1000</v>
@@ -6791,58 +6791,58 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AS25">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6928,13 +6928,13 @@
         <v>1.62</v>
       </c>
       <c r="G26">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I26">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J26">
         <v>4</v>
@@ -6946,7 +6946,7 @@
         <v>1.43</v>
       </c>
       <c r="M26">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
         <v>3.6</v>
@@ -6979,7 +6979,7 @@
         <v>2.5</v>
       </c>
       <c r="X26">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y26">
         <v>24</v>
@@ -7015,7 +7015,7 @@
         <v>130</v>
       </c>
       <c r="AJ26">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK26">
         <v>19</v>
@@ -7039,10 +7039,10 @@
         <v>16.5</v>
       </c>
       <c r="AR26">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AS26">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT26">
         <v>6.6</v>
@@ -7051,10 +7051,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV26">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AW26">
-        <v>7.6</v>
+        <v>55</v>
       </c>
       <c r="AX26">
         <v>8</v>
@@ -7066,7 +7066,7 @@
         <v>21</v>
       </c>
       <c r="BA26">
-        <v>7.6</v>
+        <v>55</v>
       </c>
       <c r="BB26">
         <v>13</v>
@@ -7075,16 +7075,16 @@
         <v>16</v>
       </c>
       <c r="BD26">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BE26">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF26">
         <v>9.4</v>
       </c>
       <c r="BG26">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7167,88 +7167,88 @@
         <v>164</v>
       </c>
       <c r="F27">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="G27">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="H27">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="I27">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="J27">
         <v>3.35</v>
       </c>
       <c r="K27">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L27">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M27">
         <v>1.07</v>
       </c>
       <c r="N27">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O27">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P27">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q27">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S27">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T27">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U27">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V27">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W27">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="X27">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y27">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Z27">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AA27">
         <v>46</v>
       </c>
       <c r="AB27">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD27">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE27">
         <v>36</v>
       </c>
       <c r="AF27">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AG27">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH27">
         <v>21</v>
@@ -7257,76 +7257,76 @@
         <v>46</v>
       </c>
       <c r="AJ27">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AK27">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AL27">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM27">
         <v>120</v>
       </c>
       <c r="AN27">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AO27">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AP27">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR27">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS27">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AT27">
+        <v>10</v>
+      </c>
+      <c r="AU27">
+        <v>6.8</v>
+      </c>
+      <c r="AV27">
+        <v>11</v>
+      </c>
+      <c r="AW27">
+        <v>8</v>
+      </c>
+      <c r="AX27">
+        <v>15</v>
+      </c>
+      <c r="AY27">
         <v>10.5</v>
-      </c>
-      <c r="AU27">
-        <v>7</v>
-      </c>
-      <c r="AV27">
-        <v>10.5</v>
-      </c>
-      <c r="AW27">
-        <v>20</v>
-      </c>
-      <c r="AX27">
-        <v>17.5</v>
-      </c>
-      <c r="AY27">
-        <v>11.5</v>
       </c>
       <c r="AZ27">
         <v>15</v>
       </c>
       <c r="BA27">
-        <v>5.2</v>
+        <v>15.5</v>
       </c>
       <c r="BB27">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC27">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BD27">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="BE27">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF27">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="BG27">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH27">
         <v>3.9</v>
@@ -7338,7 +7338,7 @@
         <v>11.5</v>
       </c>
       <c r="BK27">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="BL27">
         <v>1000</v>
@@ -7347,37 +7347,37 @@
         <v>4.6</v>
       </c>
       <c r="BN27">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BO27">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BP27">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BQ27">
         <v>4</v>
       </c>
       <c r="BR27">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BS27">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BT27">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU27">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV27">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BW27">
         <v>4</v>
       </c>
       <c r="BX27">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY27">
         <v>4.2</v>
@@ -7409,22 +7409,22 @@
         <v>165</v>
       </c>
       <c r="F28">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G28">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H28">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I28">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J28">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K28">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L28">
         <v>1.49</v>
@@ -7439,187 +7439,187 @@
         <v>1.43</v>
       </c>
       <c r="P28">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R28">
         <v>1.25</v>
       </c>
       <c r="S28">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T28">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U28">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V28">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
         <v>1.67</v>
       </c>
       <c r="X28">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z28">
         <v>25</v>
       </c>
       <c r="AA28">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB28">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC28">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD28">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE28">
         <v>55</v>
       </c>
       <c r="AF28">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG28">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH28">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI28">
         <v>70</v>
       </c>
       <c r="AJ28">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK28">
+        <v>32</v>
+      </c>
+      <c r="AL28">
+        <v>55</v>
+      </c>
+      <c r="AM28">
+        <v>160</v>
+      </c>
+      <c r="AN28">
+        <v>29</v>
+      </c>
+      <c r="AO28">
+        <v>70</v>
+      </c>
+      <c r="AP28">
+        <v>9.4</v>
+      </c>
+      <c r="AQ28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR28">
+        <v>20</v>
+      </c>
+      <c r="AS28">
+        <v>46</v>
+      </c>
+      <c r="AT28">
+        <v>7.4</v>
+      </c>
+      <c r="AU28">
+        <v>6.6</v>
+      </c>
+      <c r="AV28">
+        <v>13</v>
+      </c>
+      <c r="AW28">
+        <v>30</v>
+      </c>
+      <c r="AX28">
+        <v>12</v>
+      </c>
+      <c r="AY28">
+        <v>10</v>
+      </c>
+      <c r="AZ28">
+        <v>17</v>
+      </c>
+      <c r="BA28">
+        <v>44</v>
+      </c>
+      <c r="BB28">
+        <v>24</v>
+      </c>
+      <c r="BC28">
+        <v>23</v>
+      </c>
+      <c r="BD28">
         <v>36</v>
       </c>
-      <c r="AL28">
-        <v>60</v>
-      </c>
-      <c r="AM28">
-        <v>150</v>
-      </c>
-      <c r="AN28">
-        <v>32</v>
-      </c>
-      <c r="AO28">
-        <v>60</v>
-      </c>
-      <c r="AP28">
-        <v>3.95</v>
-      </c>
-      <c r="AQ28">
-        <v>3.95</v>
-      </c>
-      <c r="AR28">
-        <v>4.6</v>
-      </c>
-      <c r="AS28">
-        <v>5.3</v>
-      </c>
-      <c r="AT28">
-        <v>3.6</v>
-      </c>
-      <c r="AU28">
-        <v>3.4</v>
-      </c>
-      <c r="AV28">
-        <v>4.2</v>
-      </c>
-      <c r="AW28">
-        <v>5.2</v>
-      </c>
-      <c r="AX28">
-        <v>4.3</v>
-      </c>
-      <c r="AY28">
+      <c r="BE28">
+        <v>90</v>
+      </c>
+      <c r="BF28">
+        <v>21</v>
+      </c>
+      <c r="BG28">
+        <v>34</v>
+      </c>
+      <c r="BH28">
+        <v>3.3</v>
+      </c>
+      <c r="BI28">
+        <v>2.5</v>
+      </c>
+      <c r="BJ28">
+        <v>12</v>
+      </c>
+      <c r="BK28">
+        <v>1.01</v>
+      </c>
+      <c r="BL28">
+        <v>190</v>
+      </c>
+      <c r="BM28">
+        <v>1.01</v>
+      </c>
+      <c r="BN28">
+        <v>5.8</v>
+      </c>
+      <c r="BO28">
         <v>4</v>
       </c>
-      <c r="AZ28">
-        <v>4.6</v>
-      </c>
-      <c r="BA28">
-        <v>5.3</v>
-      </c>
-      <c r="BB28">
-        <v>5</v>
-      </c>
-      <c r="BC28">
-        <v>4.9</v>
-      </c>
-      <c r="BD28">
-        <v>5.2</v>
-      </c>
-      <c r="BE28">
-        <v>5.5</v>
-      </c>
-      <c r="BF28">
-        <v>4.8</v>
-      </c>
-      <c r="BG28">
-        <v>5.2</v>
-      </c>
-      <c r="BH28">
-        <v>1000</v>
-      </c>
-      <c r="BI28">
-        <v>1.01</v>
-      </c>
-      <c r="BJ28">
-        <v>1000</v>
-      </c>
-      <c r="BK28">
-        <v>1.01</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>1.01</v>
-      </c>
-      <c r="BN28">
-        <v>1000</v>
-      </c>
-      <c r="BO28">
-        <v>1.01</v>
-      </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ28">
         <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS28">
         <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY28">
         <v>1.01</v>
@@ -7651,22 +7651,22 @@
         <v>166</v>
       </c>
       <c r="F29">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G29">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H29">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="I29">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K29">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L29">
         <v>1.5</v>
@@ -7693,31 +7693,31 @@
         <v>4.4</v>
       </c>
       <c r="T29">
+        <v>2.04</v>
+      </c>
+      <c r="U29">
+        <v>1.91</v>
+      </c>
+      <c r="V29">
         <v>2</v>
       </c>
-      <c r="U29">
-        <v>1.93</v>
-      </c>
-      <c r="V29">
-        <v>1.94</v>
-      </c>
       <c r="W29">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X29">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y29">
         <v>7.6</v>
       </c>
       <c r="Z29">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AA29">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB29">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AC29">
         <v>8</v>
@@ -7729,13 +7729,13 @@
         <v>25</v>
       </c>
       <c r="AF29">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AG29">
+        <v>20</v>
+      </c>
+      <c r="AH29">
         <v>23</v>
-      </c>
-      <c r="AH29">
-        <v>27</v>
       </c>
       <c r="AI29">
         <v>55</v>
@@ -7744,46 +7744,46 @@
         <v>140</v>
       </c>
       <c r="AK29">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL29">
         <v>100</v>
       </c>
       <c r="AM29">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN29">
         <v>120</v>
       </c>
       <c r="AO29">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AP29">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ29">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR29">
         <v>10</v>
       </c>
       <c r="AS29">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AT29">
         <v>12</v>
       </c>
       <c r="AU29">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV29">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX29">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AY29">
         <v>17</v>
@@ -7792,85 +7792,85 @@
         <v>19.5</v>
       </c>
       <c r="BA29">
-        <v>30</v>
+        <v>9.6</v>
       </c>
       <c r="BB29">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC29">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BD29">
-        <v>6.6</v>
+        <v>42</v>
       </c>
       <c r="BE29">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BF29">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG29">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH29">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>2.76</v>
+        <v>1.25</v>
       </c>
       <c r="BJ29">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>4.1</v>
+        <v>1.42</v>
       </c>
       <c r="BV29">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
         <v>169</v>
@@ -7893,10 +7893,10 @@
         <v>167</v>
       </c>
       <c r="F30">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G30">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H30">
         <v>5.3</v>
@@ -7905,10 +7905,10 @@
         <v>5.6</v>
       </c>
       <c r="J30">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K30">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L30">
         <v>1.53</v>
@@ -7938,13 +7938,13 @@
         <v>2.16</v>
       </c>
       <c r="U30">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V30">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W30">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X30">
         <v>11.5</v>
@@ -8010,7 +8010,7 @@
         <v>26</v>
       </c>
       <c r="AS30">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT30">
         <v>5.6</v>
@@ -8028,7 +8028,7 @@
         <v>8.6</v>
       </c>
       <c r="AY30">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ30">
         <v>21</v>
@@ -8049,64 +8049,64 @@
         <v>6.2</v>
       </c>
       <c r="BF30">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="BG30">
         <v>6</v>
       </c>
       <c r="BH30">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI30">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL30">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM30">
         <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO30">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ30">
         <v>1.01</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS30">
         <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU30">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW30">
         <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ30">
         <v>0</v>
@@ -8135,139 +8135,139 @@
         <v>168</v>
       </c>
       <c r="F31">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="G31">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="H31">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I31">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="J31">
         <v>3.2</v>
       </c>
       <c r="K31">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L31">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M31">
         <v>1.09</v>
       </c>
       <c r="N31">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O31">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P31">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q31">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R31">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S31">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T31">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U31">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V31">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W31">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="X31">
         <v>11.5</v>
       </c>
       <c r="Y31">
+        <v>13</v>
+      </c>
+      <c r="Z31">
+        <v>24</v>
+      </c>
+      <c r="AA31">
+        <v>70</v>
+      </c>
+      <c r="AB31">
+        <v>9.6</v>
+      </c>
+      <c r="AC31">
+        <v>7.4</v>
+      </c>
+      <c r="AD31">
+        <v>15.5</v>
+      </c>
+      <c r="AE31">
+        <v>46</v>
+      </c>
+      <c r="AF31">
+        <v>14.5</v>
+      </c>
+      <c r="AG31">
         <v>12</v>
-      </c>
-      <c r="Z31">
-        <v>22</v>
-      </c>
-      <c r="AA31">
-        <v>60</v>
-      </c>
-      <c r="AB31">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC31">
-        <v>7.2</v>
-      </c>
-      <c r="AD31">
-        <v>14</v>
-      </c>
-      <c r="AE31">
-        <v>40</v>
-      </c>
-      <c r="AF31">
-        <v>15.5</v>
-      </c>
-      <c r="AG31">
-        <v>12.5</v>
       </c>
       <c r="AH31">
         <v>18</v>
       </c>
       <c r="AI31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ31">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK31">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL31">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="AM31">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AO31">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AP31">
         <v>10.5</v>
       </c>
       <c r="AQ31">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR31">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS31">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AT31">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU31">
         <v>6.6</v>
       </c>
       <c r="AV31">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW31">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX31">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AY31">
         <v>10.5</v>
@@ -8276,85 +8276,85 @@
         <v>15.5</v>
       </c>
       <c r="BA31">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB31">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BC31">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BD31">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE31">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BF31">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BG31">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH31">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI31">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BJ31">
         <v>10.5</v>
       </c>
       <c r="BK31">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
+        <v>13.5</v>
+      </c>
+      <c r="BN31">
+        <v>5.1</v>
+      </c>
+      <c r="BO31">
+        <v>4.5</v>
+      </c>
+      <c r="BP31">
+        <v>18.5</v>
+      </c>
+      <c r="BQ31">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR31">
+        <v>34</v>
+      </c>
+      <c r="BS31">
+        <v>10</v>
+      </c>
+      <c r="BT31">
+        <v>6.6</v>
+      </c>
+      <c r="BU31">
+        <v>5.4</v>
+      </c>
+      <c r="BV31">
+        <v>30</v>
+      </c>
+      <c r="BW31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX31">
+        <v>44</v>
+      </c>
+      <c r="BY31">
         <v>11</v>
       </c>
-      <c r="BN31">
-        <v>5.6</v>
-      </c>
-      <c r="BO31">
-        <v>4.7</v>
-      </c>
-      <c r="BP31">
-        <v>22</v>
-      </c>
-      <c r="BQ31">
-        <v>7.6</v>
-      </c>
-      <c r="BR31">
-        <v>38</v>
-      </c>
-      <c r="BS31">
-        <v>9</v>
-      </c>
-      <c r="BT31">
-        <v>6.4</v>
-      </c>
-      <c r="BU31">
-        <v>5.2</v>
-      </c>
-      <c r="BV31">
-        <v>27</v>
-      </c>
-      <c r="BW31">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX31">
-        <v>42</v>
-      </c>
-      <c r="BY31">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BZ31">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA31">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB31" t="s">
         <v>169</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="172">
   <si>
     <t>League</t>
   </si>
@@ -325,7 +325,7 @@
     <t>19:00:00</t>
   </si>
   <si>
-    <t>19:30:00</t>
+    <t>20:00:00</t>
   </si>
   <si>
     <t>20:30:00</t>
@@ -388,6 +388,12 @@
     <t>Leganes</t>
   </si>
   <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Northern Ireland</t>
+  </si>
+  <si>
     <t>Türkiye</t>
   </si>
   <si>
@@ -397,12 +403,6 @@
     <t>Belgium</t>
   </si>
   <si>
-    <t>Northern Ireland</t>
-  </si>
-  <si>
-    <t>Sweden</t>
-  </si>
-  <si>
     <t>Guadeloupe</t>
   </si>
   <si>
@@ -412,6 +412,9 @@
     <t>Independiente Yumbo</t>
   </si>
   <si>
+    <t>Cuba</t>
+  </si>
+  <si>
     <t>Internacional de Palmira</t>
   </si>
   <si>
@@ -478,6 +481,12 @@
     <t>CD Castellon</t>
   </si>
   <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
     <t>Italy</t>
   </si>
   <si>
@@ -487,12 +496,6 @@
     <t>France</t>
   </si>
   <si>
-    <t>Hungary</t>
-  </si>
-  <si>
-    <t>Poland</t>
-  </si>
-  <si>
     <t>Barbados</t>
   </si>
   <si>
@@ -502,6 +505,9 @@
     <t>Orsomarso</t>
   </si>
   <si>
+    <t>Bonaire</t>
+  </si>
+  <si>
     <t>Leones FC</t>
   </si>
   <si>
@@ -523,7 +529,7 @@
     <t>Albion FC</t>
   </si>
   <si>
-    <t>2026-09-28 07:53:38</t>
+    <t>2026-09-28 10:05:42</t>
   </si>
 </sst>
 </file>
@@ -855,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB31"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1114,232 +1120,232 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G2">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J2">
         <v>3.6</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O2">
+        <v>1.37</v>
+      </c>
+      <c r="P2">
+        <v>1.89</v>
+      </c>
+      <c r="Q2">
+        <v>2.08</v>
+      </c>
+      <c r="R2">
         <v>1.28</v>
       </c>
-      <c r="P2">
-        <v>2.04</v>
-      </c>
-      <c r="Q2">
-        <v>1.83</v>
-      </c>
-      <c r="R2">
-        <v>1.4</v>
-      </c>
       <c r="S2">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="T2">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="U2">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
         <v>1.23</v>
       </c>
       <c r="W2">
+        <v>2.1</v>
+      </c>
+      <c r="X2">
+        <v>13</v>
+      </c>
+      <c r="Y2">
+        <v>17.5</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>8.4</v>
+      </c>
+      <c r="AC2">
+        <v>990</v>
+      </c>
+      <c r="AD2">
+        <v>990</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>13</v>
+      </c>
+      <c r="AG2">
+        <v>990</v>
+      </c>
+      <c r="AH2">
+        <v>990</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>18.5</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>9</v>
+      </c>
+      <c r="AQ2">
+        <v>2.36</v>
+      </c>
+      <c r="AR2">
+        <v>2.7</v>
+      </c>
+      <c r="AS2">
+        <v>2.7</v>
+      </c>
+      <c r="AT2">
         <v>2.06</v>
       </c>
-      <c r="X2">
-        <v>20</v>
-      </c>
-      <c r="Y2">
-        <v>18.5</v>
-      </c>
-      <c r="Z2">
-        <v>42</v>
-      </c>
-      <c r="AA2">
-        <v>150</v>
-      </c>
-      <c r="AB2">
+      <c r="AU2">
+        <v>7</v>
+      </c>
+      <c r="AV2">
+        <v>2.44</v>
+      </c>
+      <c r="AW2">
+        <v>2.7</v>
+      </c>
+      <c r="AX2">
+        <v>2.26</v>
+      </c>
+      <c r="AY2">
+        <v>2.22</v>
+      </c>
+      <c r="AZ2">
+        <v>2.74</v>
+      </c>
+      <c r="BA2">
+        <v>2.7</v>
+      </c>
+      <c r="BB2">
+        <v>2.7</v>
+      </c>
+      <c r="BC2">
+        <v>2.7</v>
+      </c>
+      <c r="BD2">
+        <v>2.7</v>
+      </c>
+      <c r="BE2">
+        <v>2.76</v>
+      </c>
+      <c r="BF2">
+        <v>2.36</v>
+      </c>
+      <c r="BG2">
+        <v>2.7</v>
+      </c>
+      <c r="BH2">
+        <v>3.05</v>
+      </c>
+      <c r="BI2">
+        <v>2.76</v>
+      </c>
+      <c r="BJ2">
+        <v>14</v>
+      </c>
+      <c r="BK2">
         <v>10.5</v>
       </c>
-      <c r="AC2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>19</v>
-      </c>
-      <c r="AE2">
-        <v>70</v>
-      </c>
-      <c r="AF2">
+      <c r="BL2">
+        <v>960</v>
+      </c>
+      <c r="BM2">
+        <v>5.9</v>
+      </c>
+      <c r="BN2">
+        <v>4.9</v>
+      </c>
+      <c r="BO2">
+        <v>3.75</v>
+      </c>
+      <c r="BP2">
+        <v>16</v>
+      </c>
+      <c r="BQ2">
         <v>12.5</v>
       </c>
-      <c r="AG2">
-        <v>11</v>
-      </c>
-      <c r="AH2">
-        <v>19</v>
-      </c>
-      <c r="AI2">
-        <v>75</v>
-      </c>
-      <c r="AJ2">
-        <v>22</v>
-      </c>
-      <c r="AK2">
-        <v>19.5</v>
-      </c>
-      <c r="AL2">
+      <c r="BR2">
+        <v>36</v>
+      </c>
+      <c r="BS2">
+        <v>30</v>
+      </c>
+      <c r="BT2">
+        <v>10.5</v>
+      </c>
+      <c r="BU2">
+        <v>7.6</v>
+      </c>
+      <c r="BV2">
+        <v>65</v>
+      </c>
+      <c r="BW2">
         <v>38</v>
       </c>
-      <c r="AM2">
-        <v>160</v>
-      </c>
-      <c r="AN2">
-        <v>12</v>
-      </c>
-      <c r="AO2">
-        <v>75</v>
-      </c>
-      <c r="AP2">
-        <v>14</v>
-      </c>
-      <c r="AQ2">
-        <v>15</v>
-      </c>
-      <c r="AR2">
-        <v>28</v>
-      </c>
-      <c r="AS2">
-        <v>65</v>
-      </c>
-      <c r="AT2">
-        <v>8</v>
-      </c>
-      <c r="AU2">
-        <v>7.6</v>
-      </c>
-      <c r="AV2">
-        <v>15.5</v>
-      </c>
-      <c r="AW2">
-        <v>32</v>
-      </c>
-      <c r="AX2">
-        <v>8.6</v>
-      </c>
-      <c r="AY2">
-        <v>8.6</v>
-      </c>
-      <c r="AZ2">
-        <v>15.5</v>
-      </c>
-      <c r="BA2">
-        <v>32</v>
-      </c>
-      <c r="BB2">
-        <v>18</v>
-      </c>
-      <c r="BC2">
-        <v>16</v>
-      </c>
-      <c r="BD2">
-        <v>22</v>
-      </c>
-      <c r="BE2">
-        <v>75</v>
-      </c>
-      <c r="BF2">
-        <v>9.4</v>
-      </c>
-      <c r="BG2">
-        <v>30</v>
-      </c>
-      <c r="BH2">
-        <v>4.2</v>
-      </c>
-      <c r="BI2">
-        <v>2.86</v>
-      </c>
-      <c r="BJ2">
-        <v>12</v>
-      </c>
-      <c r="BK2">
-        <v>3.5</v>
-      </c>
-      <c r="BL2">
-        <v>150</v>
-      </c>
-      <c r="BM2">
-        <v>90</v>
-      </c>
-      <c r="BN2">
-        <v>5.2</v>
-      </c>
-      <c r="BO2">
-        <v>3.55</v>
-      </c>
-      <c r="BP2">
-        <v>14.5</v>
-      </c>
-      <c r="BQ2">
-        <v>3.7</v>
-      </c>
-      <c r="BR2">
-        <v>32</v>
-      </c>
-      <c r="BS2">
-        <v>4.3</v>
-      </c>
-      <c r="BT2">
-        <v>9.6</v>
-      </c>
-      <c r="BU2">
-        <v>6.2</v>
-      </c>
-      <c r="BV2">
-        <v>48</v>
-      </c>
-      <c r="BW2">
-        <v>4.5</v>
-      </c>
       <c r="BX2">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="BY2">
-        <v>4.6</v>
+        <v>55</v>
       </c>
       <c r="BZ2">
-        <v>26</v>
+        <v>960</v>
       </c>
       <c r="CA2">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="CB2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1356,67 +1362,67 @@
         <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F3">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G3">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="H3">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
         <v>1.31</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q3">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R3">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S3">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T3">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="U3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V3">
         <v>1.33</v>
       </c>
       <c r="W3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X3">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="Y3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z3">
         <v>34</v>
@@ -1425,88 +1431,88 @@
         <v>85</v>
       </c>
       <c r="AB3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
+        <v>16</v>
+      </c>
+      <c r="AE3">
+        <v>42</v>
+      </c>
+      <c r="AF3">
+        <v>15</v>
+      </c>
+      <c r="AG3">
+        <v>10.5</v>
+      </c>
+      <c r="AH3">
         <v>17</v>
-      </c>
-      <c r="AE3">
-        <v>44</v>
-      </c>
-      <c r="AF3">
-        <v>14.5</v>
-      </c>
-      <c r="AG3">
-        <v>11.5</v>
-      </c>
-      <c r="AH3">
-        <v>24</v>
       </c>
       <c r="AI3">
         <v>46</v>
       </c>
       <c r="AJ3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL3">
         <v>30</v>
       </c>
       <c r="AM3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO3">
         <v>34</v>
       </c>
       <c r="AP3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR3">
         <v>23</v>
       </c>
       <c r="AS3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
         <v>29</v>
       </c>
       <c r="AX3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA3">
         <v>29</v>
       </c>
       <c r="BB3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC3">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BD3">
         <v>24</v>
@@ -1515,73 +1521,73 @@
         <v>55</v>
       </c>
       <c r="BF3">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH3">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BI3">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BN3">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BO3">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BP3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ3">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="BR3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BS3">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BU3">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BV3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BX3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CA3">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="CB3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1598,79 +1604,79 @@
         <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F4">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="G4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H4">
+        <v>4.1</v>
+      </c>
+      <c r="I4">
+        <v>4.6</v>
+      </c>
+      <c r="J4">
+        <v>3.35</v>
+      </c>
+      <c r="K4">
         <v>3.7</v>
       </c>
-      <c r="I4">
-        <v>6.8</v>
-      </c>
-      <c r="J4">
-        <v>3.25</v>
-      </c>
-      <c r="K4">
-        <v>4.5</v>
-      </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4">
         <v>1000</v>
@@ -1679,139 +1685,139 @@
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI4">
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY4">
         <v>1.01</v>
@@ -1823,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1840,28 +1846,28 @@
         <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F5">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="G5">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H5">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I5">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J5">
         <v>3.35</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M5">
         <v>1.07</v>
@@ -1870,7 +1876,7 @@
         <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
         <v>1.81</v>
@@ -1882,190 +1888,190 @@
         <v>1.3</v>
       </c>
       <c r="S5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T5">
         <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W5">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="X5">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Y5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AA5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB5">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD5">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE5">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG5">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI5">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK5">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AL5">
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AN5">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AO5">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AP5">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>3.05</v>
+        <v>9</v>
       </c>
       <c r="AR5">
-        <v>3.55</v>
+        <v>11.5</v>
       </c>
       <c r="AS5">
-        <v>3.85</v>
+        <v>25</v>
       </c>
       <c r="AT5">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AU5">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV5">
-        <v>3.25</v>
+        <v>9</v>
       </c>
       <c r="AW5">
-        <v>3.85</v>
+        <v>19</v>
       </c>
       <c r="AX5">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AY5">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA5">
-        <v>3.85</v>
+        <v>30</v>
       </c>
       <c r="BB5">
-        <v>4.4</v>
+        <v>36</v>
       </c>
       <c r="BC5">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE5">
-        <v>3.2</v>
+        <v>50</v>
       </c>
       <c r="BF5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BG5">
-        <v>3.65</v>
+        <v>15</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
         <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM5">
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ5">
         <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS5">
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW5">
         <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2082,25 +2088,25 @@
         <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F6">
         <v>4.3</v>
       </c>
       <c r="G6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H6">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="I6">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J6">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
         <v>1.37</v>
@@ -2112,37 +2118,37 @@
         <v>3.95</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P6">
         <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R6">
         <v>1.39</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T6">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="U6">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="V6">
         <v>2.08</v>
       </c>
       <c r="W6">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X6">
         <v>21</v>
       </c>
       <c r="Y6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z6">
         <v>14.5</v>
@@ -2151,13 +2157,13 @@
         <v>25</v>
       </c>
       <c r="AB6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC6">
+        <v>10.5</v>
+      </c>
+      <c r="AD6">
         <v>11</v>
-      </c>
-      <c r="AD6">
-        <v>12.5</v>
       </c>
       <c r="AE6">
         <v>23</v>
@@ -2172,7 +2178,7 @@
         <v>22</v>
       </c>
       <c r="AI6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ6">
         <v>130</v>
@@ -2193,121 +2199,121 @@
         <v>13.5</v>
       </c>
       <c r="AP6">
+        <v>4</v>
+      </c>
+      <c r="AQ6">
+        <v>3.55</v>
+      </c>
+      <c r="AR6">
+        <v>3.7</v>
+      </c>
+      <c r="AS6">
+        <v>4.1</v>
+      </c>
+      <c r="AT6">
+        <v>3.95</v>
+      </c>
+      <c r="AU6">
+        <v>3.35</v>
+      </c>
+      <c r="AV6">
+        <v>3.4</v>
+      </c>
+      <c r="AW6">
+        <v>4</v>
+      </c>
+      <c r="AX6">
+        <v>4.4</v>
+      </c>
+      <c r="AY6">
+        <v>4</v>
+      </c>
+      <c r="AZ6">
+        <v>4</v>
+      </c>
+      <c r="BA6">
+        <v>4.3</v>
+      </c>
+      <c r="BB6">
+        <v>4.7</v>
+      </c>
+      <c r="BC6">
+        <v>4.6</v>
+      </c>
+      <c r="BD6">
+        <v>4.6</v>
+      </c>
+      <c r="BE6">
+        <v>4.7</v>
+      </c>
+      <c r="BF6">
+        <v>4.6</v>
+      </c>
+      <c r="BG6">
         <v>3.6</v>
       </c>
-      <c r="AQ6">
-        <v>3.15</v>
-      </c>
-      <c r="AR6">
-        <v>3.35</v>
-      </c>
-      <c r="AS6">
-        <v>3.7</v>
-      </c>
-      <c r="AT6">
-        <v>3.65</v>
-      </c>
-      <c r="AU6">
-        <v>3.1</v>
-      </c>
-      <c r="AV6">
-        <v>3.25</v>
-      </c>
-      <c r="AW6">
-        <v>3.65</v>
-      </c>
-      <c r="AX6">
-        <v>4</v>
-      </c>
-      <c r="AY6">
-        <v>3.65</v>
-      </c>
-      <c r="AZ6">
-        <v>3.65</v>
-      </c>
-      <c r="BA6">
-        <v>3.95</v>
-      </c>
-      <c r="BB6">
-        <v>4.2</v>
-      </c>
-      <c r="BC6">
-        <v>4.1</v>
-      </c>
-      <c r="BD6">
-        <v>4.1</v>
-      </c>
-      <c r="BE6">
-        <v>4.2</v>
-      </c>
-      <c r="BF6">
-        <v>4.1</v>
-      </c>
-      <c r="BG6">
-        <v>3.3</v>
-      </c>
       <c r="BH6">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2324,19 +2330,19 @@
         <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F7">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="G7">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H7">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="I7">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="J7">
         <v>3.25</v>
@@ -2351,49 +2357,49 @@
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P7">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
         <v>1.28</v>
       </c>
       <c r="S7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T7">
         <v>1.89</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V7">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X7">
         <v>11</v>
       </c>
       <c r="Y7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7">
         <v>17</v>
       </c>
       <c r="AA7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC7">
         <v>7.2</v>
@@ -2405,22 +2411,22 @@
         <v>36</v>
       </c>
       <c r="AF7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
         <v>50</v>
       </c>
       <c r="AJ7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL7">
         <v>50</v>
@@ -2429,10 +2435,10 @@
         <v>120</v>
       </c>
       <c r="AN7">
+        <v>34</v>
+      </c>
+      <c r="AO7">
         <v>36</v>
-      </c>
-      <c r="AO7">
-        <v>34</v>
       </c>
       <c r="AP7">
         <v>10.5</v>
@@ -2441,10 +2447,10 @@
         <v>9.4</v>
       </c>
       <c r="AR7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AT7">
         <v>9.6</v>
@@ -2456,7 +2462,7 @@
         <v>11.5</v>
       </c>
       <c r="AW7">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX7">
         <v>16.5</v>
@@ -2480,76 +2486,76 @@
         <v>46</v>
       </c>
       <c r="BE7">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF7">
         <v>30</v>
       </c>
       <c r="BG7">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BH7">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BK7">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BL7">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13.5</v>
+        <v>130</v>
       </c>
       <c r="BN7">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>9.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="BR7">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>11.5</v>
+        <v>1.1</v>
       </c>
       <c r="BT7">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BV7">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9</v>
+        <v>1.1</v>
       </c>
       <c r="BX7">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>11.5</v>
+        <v>1.1</v>
       </c>
       <c r="BZ7">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="CA7">
-        <v>11</v>
+        <v>1.08</v>
       </c>
       <c r="CB7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2566,7 +2572,7 @@
         <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -2575,88 +2581,88 @@
         <v>3.05</v>
       </c>
       <c r="H8">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I8">
         <v>2.7</v>
       </c>
       <c r="J8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K8">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L8">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P8">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="Q8">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T8">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U8">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V8">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W8">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z8">
         <v>16.5</v>
       </c>
       <c r="AA8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB8">
         <v>11</v>
       </c>
       <c r="AC8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF8">
         <v>20</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ8">
         <v>50</v>
@@ -2668,19 +2674,19 @@
         <v>48</v>
       </c>
       <c r="AM8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN8">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR8">
         <v>15.5</v>
@@ -2692,25 +2698,25 @@
         <v>10</v>
       </c>
       <c r="AU8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV8">
         <v>11</v>
       </c>
       <c r="AW8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX8">
         <v>18.5</v>
       </c>
       <c r="AY8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8">
         <v>16</v>
       </c>
       <c r="BA8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB8">
         <v>44</v>
@@ -2719,25 +2725,25 @@
         <v>32</v>
       </c>
       <c r="BD8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE8">
         <v>85</v>
       </c>
       <c r="BF8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI8">
         <v>2.9</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK8">
         <v>8.800000000000001</v>
@@ -2746,25 +2752,25 @@
         <v>160</v>
       </c>
       <c r="BM8">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="BN8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO8">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP8">
         <v>29</v>
       </c>
       <c r="BQ8">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BR8">
         <v>46</v>
       </c>
       <c r="BS8">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT8">
         <v>5.5</v>
@@ -2776,22 +2782,22 @@
         <v>24</v>
       </c>
       <c r="BW8">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BX8">
         <v>42</v>
       </c>
       <c r="BY8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2808,67 +2814,67 @@
         <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F9">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="G9">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="H9">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I9">
         <v>3.05</v>
       </c>
       <c r="J9">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K9">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L9">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="M9">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="O9">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="P9">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="Q9">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="R9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S9">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="T9">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="U9">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="V9">
         <v>1.48</v>
       </c>
       <c r="W9">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X9">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z9">
         <v>18</v>
@@ -2877,52 +2883,52 @@
         <v>55</v>
       </c>
       <c r="AB9">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>16</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI9">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ9">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK9">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL9">
+        <v>70</v>
+      </c>
+      <c r="AM9">
+        <v>190</v>
+      </c>
+      <c r="AN9">
+        <v>50</v>
+      </c>
+      <c r="AO9">
         <v>60</v>
       </c>
-      <c r="AM9">
-        <v>150</v>
-      </c>
-      <c r="AN9">
-        <v>44</v>
-      </c>
-      <c r="AO9">
-        <v>50</v>
-      </c>
       <c r="AP9">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AQ9">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AR9">
         <v>17</v>
@@ -2931,7 +2937,7 @@
         <v>46</v>
       </c>
       <c r="AT9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU9">
         <v>6.8</v>
@@ -2940,100 +2946,100 @@
         <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AX9">
         <v>15</v>
       </c>
       <c r="AY9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA9">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB9">
         <v>40</v>
       </c>
       <c r="BC9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BD9">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BE9">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BF9">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BG9">
         <v>42</v>
       </c>
       <c r="BH9">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="BI9">
         <v>2.5</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK9">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>2.96</v>
+        <v>170</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO9">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ9">
-        <v>3.15</v>
+        <v>10</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS9">
-        <v>3.15</v>
+        <v>12.5</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU9">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW9">
-        <v>3.15</v>
+        <v>10.5</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY9">
-        <v>3.15</v>
+        <v>13</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA9">
-        <v>3.15</v>
+        <v>13</v>
       </c>
       <c r="CB9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3050,49 +3056,49 @@
         <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F10">
+        <v>1.68</v>
+      </c>
+      <c r="G10">
         <v>1.78</v>
       </c>
-      <c r="G10">
-        <v>1.89</v>
-      </c>
       <c r="H10">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I10">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K10">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L10">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O10">
         <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q10">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R10">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S10">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="T10">
         <v>1.66</v>
@@ -3101,124 +3107,124 @@
         <v>2.18</v>
       </c>
       <c r="V10">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W10">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="X10">
+        <v>27</v>
+      </c>
+      <c r="Y10">
         <v>26</v>
       </c>
-      <c r="Y10">
-        <v>1000</v>
-      </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD10">
+        <v>23</v>
+      </c>
+      <c r="AE10">
+        <v>65</v>
+      </c>
+      <c r="AF10">
+        <v>14</v>
+      </c>
+      <c r="AG10">
+        <v>11.5</v>
+      </c>
+      <c r="AH10">
         <v>21</v>
       </c>
-      <c r="AE10">
+      <c r="AI10">
+        <v>60</v>
+      </c>
+      <c r="AJ10">
+        <v>20</v>
+      </c>
+      <c r="AK10">
+        <v>18</v>
+      </c>
+      <c r="AL10">
+        <v>30</v>
+      </c>
+      <c r="AM10">
+        <v>80</v>
+      </c>
+      <c r="AN10">
+        <v>8.4</v>
+      </c>
+      <c r="AO10">
         <v>55</v>
       </c>
-      <c r="AF10">
-        <v>16</v>
-      </c>
-      <c r="AG10">
-        <v>12</v>
-      </c>
-      <c r="AH10">
-        <v>19.5</v>
-      </c>
-      <c r="AI10">
-        <v>55</v>
-      </c>
-      <c r="AJ10">
-        <v>25</v>
-      </c>
-      <c r="AK10">
-        <v>21</v>
-      </c>
-      <c r="AL10">
-        <v>32</v>
-      </c>
-      <c r="AM10">
-        <v>85</v>
-      </c>
-      <c r="AN10">
-        <v>11.5</v>
-      </c>
-      <c r="AO10">
-        <v>1000</v>
-      </c>
       <c r="AP10">
-        <v>2.34</v>
+        <v>4.9</v>
       </c>
       <c r="AQ10">
-        <v>2.58</v>
+        <v>4.9</v>
       </c>
       <c r="AR10">
-        <v>2.58</v>
+        <v>5.4</v>
       </c>
       <c r="AS10">
-        <v>2.58</v>
+        <v>5.8</v>
       </c>
       <c r="AT10">
-        <v>2.16</v>
+        <v>4.1</v>
       </c>
       <c r="AU10">
-        <v>2.58</v>
+        <v>8.4</v>
       </c>
       <c r="AV10">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="AW10">
-        <v>2.46</v>
+        <v>5.5</v>
       </c>
       <c r="AX10">
-        <v>2.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY10">
-        <v>2.12</v>
+        <v>7.8</v>
       </c>
       <c r="AZ10">
-        <v>2.28</v>
+        <v>4.7</v>
       </c>
       <c r="BA10">
-        <v>2.46</v>
+        <v>5.5</v>
       </c>
       <c r="BB10">
-        <v>2.34</v>
+        <v>4.6</v>
       </c>
       <c r="BC10">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="BD10">
-        <v>2.38</v>
+        <v>20</v>
       </c>
       <c r="BE10">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF10">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG10">
-        <v>2.58</v>
+        <v>5.5</v>
       </c>
       <c r="BH10">
         <v>4.9</v>
       </c>
       <c r="BI10">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
@@ -3227,25 +3233,25 @@
         <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM10">
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BO10">
         <v>3.85</v>
       </c>
       <c r="BP10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS10">
         <v>1.01</v>
@@ -3269,13 +3275,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="CA10">
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3292,40 +3298,40 @@
         <v>118</v>
       </c>
       <c r="E11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F11">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="H11">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I11">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="K11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L11">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M11">
         <v>1.12</v>
       </c>
       <c r="N11">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P11">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Q11">
         <v>2.56</v>
@@ -3334,19 +3340,19 @@
         <v>1.18</v>
       </c>
       <c r="S11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T11">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V11">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -3358,10 +3364,10 @@
         <v>28</v>
       </c>
       <c r="AA11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC11">
         <v>7.6</v>
@@ -3370,106 +3376,106 @@
         <v>18.5</v>
       </c>
       <c r="AE11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG11">
         <v>13</v>
       </c>
       <c r="AH11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI11">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AJ11">
+        <v>36</v>
+      </c>
+      <c r="AK11">
+        <v>36</v>
+      </c>
+      <c r="AL11">
+        <v>70</v>
+      </c>
+      <c r="AM11">
+        <v>220</v>
+      </c>
+      <c r="AN11">
         <v>38</v>
-      </c>
-      <c r="AK11">
-        <v>38</v>
-      </c>
-      <c r="AL11">
-        <v>75</v>
-      </c>
-      <c r="AM11">
-        <v>230</v>
-      </c>
-      <c r="AN11">
-        <v>40</v>
       </c>
       <c r="AO11">
         <v>120</v>
       </c>
       <c r="AP11">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR11">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AS11">
         <v>55</v>
       </c>
       <c r="AT11">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AU11">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AV11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW11">
         <v>32</v>
       </c>
       <c r="AX11">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AY11">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA11">
         <v>46</v>
       </c>
       <c r="BB11">
+        <v>22</v>
+      </c>
+      <c r="BC11">
+        <v>21</v>
+      </c>
+      <c r="BD11">
+        <v>34</v>
+      </c>
+      <c r="BE11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF11">
         <v>23</v>
       </c>
-      <c r="BC11">
-        <v>20</v>
-      </c>
-      <c r="BD11">
-        <v>32</v>
-      </c>
-      <c r="BE11">
-        <v>7.6</v>
-      </c>
-      <c r="BF11">
-        <v>22</v>
-      </c>
       <c r="BG11">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH11">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI11">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BJ11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL11">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="BM11">
         <v>21</v>
@@ -3478,7 +3484,7 @@
         <v>5.5</v>
       </c>
       <c r="BO11">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BP11">
         <v>23</v>
@@ -3487,7 +3493,7 @@
         <v>15</v>
       </c>
       <c r="BR11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS11">
         <v>32</v>
@@ -3496,19 +3502,19 @@
         <v>8</v>
       </c>
       <c r="BU11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV11">
+        <v>48</v>
+      </c>
+      <c r="BW11">
+        <v>30</v>
+      </c>
+      <c r="BX11">
+        <v>75</v>
+      </c>
+      <c r="BY11">
         <v>46</v>
-      </c>
-      <c r="BW11">
-        <v>29</v>
-      </c>
-      <c r="BX11">
-        <v>70</v>
-      </c>
-      <c r="BY11">
-        <v>44</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3517,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3534,10 +3540,10 @@
         <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G12">
         <v>2.14</v>
@@ -3552,13 +3558,13 @@
         <v>3.15</v>
       </c>
       <c r="K12">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
         <v>1.52</v>
       </c>
       <c r="M12">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N12">
         <v>2.68</v>
@@ -3567,13 +3573,13 @@
         <v>1.5</v>
       </c>
       <c r="P12">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="Q12">
         <v>2.52</v>
       </c>
       <c r="R12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S12">
         <v>5.1</v>
@@ -3582,7 +3588,7 @@
         <v>2.12</v>
       </c>
       <c r="U12">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="V12">
         <v>1.23</v>
@@ -3714,7 +3720,7 @@
         <v>280</v>
       </c>
       <c r="BM12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN12">
         <v>4.8</v>
@@ -3726,7 +3732,7 @@
         <v>18</v>
       </c>
       <c r="BQ12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR12">
         <v>50</v>
@@ -3744,10 +3750,10 @@
         <v>65</v>
       </c>
       <c r="BW12">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX12">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BY12">
         <v>6</v>
@@ -3759,7 +3765,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3776,10 +3782,10 @@
         <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F13">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>3.5</v>
@@ -4001,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4018,7 +4024,7 @@
         <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F14">
         <v>2.18</v>
@@ -4030,13 +4036,13 @@
         <v>4.4</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J14">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="K14">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="L14">
         <v>1.69</v>
@@ -4045,16 +4051,16 @@
         <v>1.18</v>
       </c>
       <c r="N14">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O14">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="P14">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Q14">
-        <v>1.02</v>
+        <v>2.94</v>
       </c>
       <c r="R14">
         <v>1.12</v>
@@ -4063,22 +4069,22 @@
         <v>1.01</v>
       </c>
       <c r="T14">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V14">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W14">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X14">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="Y14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z14">
         <v>34</v>
@@ -4090,7 +4096,7 @@
         <v>6.4</v>
       </c>
       <c r="AC14">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD14">
         <v>25</v>
@@ -4114,7 +4120,7 @@
         <v>38</v>
       </c>
       <c r="AK14">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL14">
         <v>100</v>
@@ -4129,58 +4135,58 @@
         <v>230</v>
       </c>
       <c r="AP14">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AQ14">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AR14">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS14">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="AU14">
         <v>4.3</v>
       </c>
       <c r="AV14">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AW14">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX14">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AY14">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AZ14">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB14">
+        <v>7</v>
+      </c>
+      <c r="BC14">
+        <v>7.2</v>
+      </c>
+      <c r="BD14">
         <v>7.8</v>
       </c>
-      <c r="BB14">
-        <v>6.6</v>
-      </c>
-      <c r="BC14">
-        <v>6.8</v>
-      </c>
-      <c r="BD14">
+      <c r="BE14">
+        <v>8.4</v>
+      </c>
+      <c r="BF14">
         <v>7.4</v>
       </c>
-      <c r="BE14">
-        <v>8</v>
-      </c>
-      <c r="BF14">
-        <v>7</v>
-      </c>
       <c r="BG14">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14">
         <v>2.58</v>
@@ -4243,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4260,169 +4266,169 @@
         <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F15">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G15">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="H15">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I15">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="J15">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K15">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L15">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M15">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="O15">
         <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="Q15">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R15">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S15">
-        <v>2</v>
+        <v>3.55</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V15">
         <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="X15">
         <v>970</v>
       </c>
       <c r="Y15">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="Z15">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AA15">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AB15">
+        <v>11</v>
+      </c>
+      <c r="AC15">
+        <v>8</v>
+      </c>
+      <c r="AD15">
+        <v>14</v>
+      </c>
+      <c r="AE15">
+        <v>48</v>
+      </c>
+      <c r="AF15">
+        <v>18</v>
+      </c>
+      <c r="AG15">
+        <v>13</v>
+      </c>
+      <c r="AH15">
         <v>18.5</v>
       </c>
-      <c r="AC15">
-        <v>10.5</v>
-      </c>
-      <c r="AD15">
-        <v>970</v>
-      </c>
-      <c r="AE15">
-        <v>70</v>
-      </c>
-      <c r="AF15">
-        <v>970</v>
-      </c>
-      <c r="AG15">
-        <v>21</v>
-      </c>
-      <c r="AH15">
-        <v>970</v>
-      </c>
       <c r="AI15">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AJ15">
+        <v>44</v>
+      </c>
+      <c r="AK15">
+        <v>42</v>
+      </c>
+      <c r="AL15">
         <v>65</v>
-      </c>
-      <c r="AK15">
-        <v>65</v>
-      </c>
-      <c r="AL15">
-        <v>95</v>
       </c>
       <c r="AM15">
         <v>120</v>
       </c>
       <c r="AN15">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AO15">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AP15">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ15">
         <v>9.199999999999999</v>
       </c>
       <c r="AR15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS15">
+        <v>34</v>
+      </c>
+      <c r="AT15">
+        <v>7.8</v>
+      </c>
+      <c r="AU15">
+        <v>5.7</v>
+      </c>
+      <c r="AV15">
+        <v>10</v>
+      </c>
+      <c r="AW15">
         <v>23</v>
       </c>
-      <c r="AT15">
-        <v>4.9</v>
-      </c>
-      <c r="AU15">
-        <v>3.45</v>
-      </c>
-      <c r="AV15">
-        <v>9.6</v>
-      </c>
-      <c r="AW15">
-        <v>19.5</v>
-      </c>
       <c r="AX15">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AY15">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BA15">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BB15">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="BC15">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BD15">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BE15">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="BF15">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BG15">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4485,7 +4491,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4502,7 +4508,7 @@
         <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F16">
         <v>3.35</v>
@@ -4511,10 +4517,10 @@
         <v>3.45</v>
       </c>
       <c r="H16">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I16">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J16">
         <v>3.5</v>
@@ -4535,16 +4541,16 @@
         <v>1.31</v>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q16">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R16">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S16">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T16">
         <v>1.75</v>
@@ -4553,13 +4559,13 @@
         <v>2.26</v>
       </c>
       <c r="V16">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W16">
         <v>1.4</v>
       </c>
       <c r="X16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y16">
         <v>11</v>
@@ -4586,7 +4592,7 @@
         <v>25</v>
       </c>
       <c r="AG16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH16">
         <v>17</v>
@@ -4640,7 +4646,7 @@
         <v>21</v>
       </c>
       <c r="AY16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ16">
         <v>15.5</v>
@@ -4655,19 +4661,19 @@
         <v>32</v>
       </c>
       <c r="BD16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE16">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BF16">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BG16">
         <v>16</v>
       </c>
       <c r="BH16">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI16">
         <v>3.2</v>
@@ -4682,7 +4688,7 @@
         <v>130</v>
       </c>
       <c r="BM16">
-        <v>13.5</v>
+        <v>90</v>
       </c>
       <c r="BN16">
         <v>6.6</v>
@@ -4700,19 +4706,19 @@
         <v>38</v>
       </c>
       <c r="BS16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT16">
         <v>5.2</v>
       </c>
       <c r="BU16">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV16">
         <v>17.5</v>
       </c>
       <c r="BW16">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BX16">
         <v>30</v>
@@ -4727,7 +4733,7 @@
         <v>16.5</v>
       </c>
       <c r="CB16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4744,232 +4750,232 @@
         <v>124</v>
       </c>
       <c r="E17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F17">
-        <v>2.82</v>
+        <v>2.08</v>
       </c>
       <c r="G17">
-        <v>2.84</v>
+        <v>2.1</v>
       </c>
       <c r="H17">
-        <v>2.64</v>
+        <v>3.8</v>
       </c>
       <c r="I17">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="J17">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K17">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L17">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M17">
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O17">
         <v>1.22</v>
       </c>
       <c r="P17">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q17">
         <v>1.7</v>
       </c>
       <c r="R17">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S17">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T17">
         <v>1.59</v>
       </c>
       <c r="U17">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V17">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="X17">
         <v>20</v>
       </c>
       <c r="Y17">
+        <v>18</v>
+      </c>
+      <c r="Z17">
+        <v>30</v>
+      </c>
+      <c r="AA17">
+        <v>75</v>
+      </c>
+      <c r="AB17">
+        <v>13</v>
+      </c>
+      <c r="AC17">
+        <v>8.6</v>
+      </c>
+      <c r="AD17">
         <v>14.5</v>
       </c>
-      <c r="Z17">
-        <v>19</v>
-      </c>
-      <c r="AA17">
+      <c r="AE17">
+        <v>40</v>
+      </c>
+      <c r="AF17">
+        <v>14.5</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+      <c r="AH17">
+        <v>14.5</v>
+      </c>
+      <c r="AI17">
+        <v>40</v>
+      </c>
+      <c r="AJ17">
+        <v>25</v>
+      </c>
+      <c r="AK17">
+        <v>18</v>
+      </c>
+      <c r="AL17">
+        <v>29</v>
+      </c>
+      <c r="AM17">
+        <v>60</v>
+      </c>
+      <c r="AN17">
+        <v>11.5</v>
+      </c>
+      <c r="AO17">
+        <v>34</v>
+      </c>
+      <c r="AP17">
+        <v>19.5</v>
+      </c>
+      <c r="AQ17">
+        <v>17</v>
+      </c>
+      <c r="AR17">
+        <v>28</v>
+      </c>
+      <c r="AS17">
+        <v>65</v>
+      </c>
+      <c r="AT17">
+        <v>11.5</v>
+      </c>
+      <c r="AU17">
+        <v>8.4</v>
+      </c>
+      <c r="AV17">
+        <v>13.5</v>
+      </c>
+      <c r="AW17">
         <v>36</v>
       </c>
-      <c r="AB17">
-        <v>15</v>
-      </c>
-      <c r="AC17">
-        <v>8.4</v>
-      </c>
-      <c r="AD17">
-        <v>12</v>
-      </c>
-      <c r="AE17">
-        <v>25</v>
-      </c>
-      <c r="AF17">
-        <v>21</v>
-      </c>
-      <c r="AG17">
-        <v>12.5</v>
-      </c>
-      <c r="AH17">
-        <v>13.5</v>
-      </c>
-      <c r="AI17">
+      <c r="AX17">
+        <v>14</v>
+      </c>
+      <c r="AY17">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17">
+        <v>14</v>
+      </c>
+      <c r="BA17">
+        <v>36</v>
+      </c>
+      <c r="BB17">
+        <v>23</v>
+      </c>
+      <c r="BC17">
+        <v>17.5</v>
+      </c>
+      <c r="BD17">
+        <v>27</v>
+      </c>
+      <c r="BE17">
+        <v>55</v>
+      </c>
+      <c r="BF17">
+        <v>10.5</v>
+      </c>
+      <c r="BG17">
         <v>30</v>
       </c>
-      <c r="AJ17">
-        <v>44</v>
-      </c>
-      <c r="AK17">
-        <v>28</v>
-      </c>
-      <c r="AL17">
-        <v>32</v>
-      </c>
-      <c r="AM17">
-        <v>55</v>
-      </c>
-      <c r="AN17">
-        <v>19</v>
-      </c>
-      <c r="AO17">
-        <v>16</v>
-      </c>
-      <c r="AP17">
-        <v>18.5</v>
-      </c>
-      <c r="AQ17">
-        <v>13.5</v>
-      </c>
-      <c r="AR17">
-        <v>18</v>
-      </c>
-      <c r="AS17">
-        <v>32</v>
-      </c>
-      <c r="AT17">
-        <v>14</v>
-      </c>
-      <c r="AU17">
+      <c r="BH17">
+        <v>4</v>
+      </c>
+      <c r="BI17">
+        <v>3.7</v>
+      </c>
+      <c r="BJ17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK17">
         <v>8</v>
-      </c>
-      <c r="AV17">
-        <v>11</v>
-      </c>
-      <c r="AW17">
-        <v>22</v>
-      </c>
-      <c r="AX17">
-        <v>19.5</v>
-      </c>
-      <c r="AY17">
-        <v>11.5</v>
-      </c>
-      <c r="AZ17">
-        <v>13</v>
-      </c>
-      <c r="BA17">
-        <v>29</v>
-      </c>
-      <c r="BB17">
-        <v>40</v>
-      </c>
-      <c r="BC17">
-        <v>25</v>
-      </c>
-      <c r="BD17">
-        <v>30</v>
-      </c>
-      <c r="BE17">
-        <v>50</v>
-      </c>
-      <c r="BF17">
-        <v>17</v>
-      </c>
-      <c r="BG17">
-        <v>15</v>
-      </c>
-      <c r="BH17">
-        <v>4.5</v>
-      </c>
-      <c r="BI17">
-        <v>3.35</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
-        <v>6.6</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.3</v>
+        <v>65</v>
       </c>
       <c r="BN17">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BO17">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS17">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BT17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU17">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW17">
-        <v>2.38</v>
+        <v>10</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CB17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4986,232 +4992,232 @@
         <v>125</v>
       </c>
       <c r="E18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F18">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="G18">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="H18">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="I18">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="J18">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="K18">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="L18">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="M18">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="N18">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="O18">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="P18">
+        <v>1.57</v>
+      </c>
+      <c r="Q18">
+        <v>2.7</v>
+      </c>
+      <c r="R18">
+        <v>1.2</v>
+      </c>
+      <c r="S18">
+        <v>5.6</v>
+      </c>
+      <c r="T18">
+        <v>2.16</v>
+      </c>
+      <c r="U18">
         <v>1.85</v>
       </c>
-      <c r="Q18">
-        <v>2.14</v>
-      </c>
-      <c r="R18">
-        <v>1.32</v>
-      </c>
-      <c r="S18">
-        <v>3.95</v>
-      </c>
-      <c r="T18">
-        <v>1.85</v>
-      </c>
-      <c r="U18">
-        <v>2.12</v>
-      </c>
       <c r="V18">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="X18">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="Y18">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z18">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AA18">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AB18">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC18">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AD18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE18">
         <v>40</v>
       </c>
       <c r="AF18">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AG18">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH18">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI18">
+        <v>65</v>
+      </c>
+      <c r="AJ18">
         <v>55</v>
       </c>
-      <c r="AJ18">
+      <c r="AK18">
+        <v>44</v>
+      </c>
+      <c r="AL18">
+        <v>70</v>
+      </c>
+      <c r="AM18">
+        <v>170</v>
+      </c>
+      <c r="AN18">
+        <v>55</v>
+      </c>
+      <c r="AO18">
+        <v>48</v>
+      </c>
+      <c r="AP18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ18">
+        <v>7.8</v>
+      </c>
+      <c r="AR18">
+        <v>15.5</v>
+      </c>
+      <c r="AS18">
+        <v>44</v>
+      </c>
+      <c r="AT18">
+        <v>8.4</v>
+      </c>
+      <c r="AU18">
+        <v>6.6</v>
+      </c>
+      <c r="AV18">
+        <v>12.5</v>
+      </c>
+      <c r="AW18">
+        <v>38</v>
+      </c>
+      <c r="AX18">
+        <v>17.5</v>
+      </c>
+      <c r="AY18">
+        <v>13</v>
+      </c>
+      <c r="AZ18">
+        <v>21</v>
+      </c>
+      <c r="BA18">
+        <v>60</v>
+      </c>
+      <c r="BB18">
+        <v>50</v>
+      </c>
+      <c r="BC18">
+        <v>42</v>
+      </c>
+      <c r="BD18">
+        <v>60</v>
+      </c>
+      <c r="BE18">
+        <v>140</v>
+      </c>
+      <c r="BF18">
+        <v>50</v>
+      </c>
+      <c r="BG18">
+        <v>44</v>
+      </c>
+      <c r="BH18">
+        <v>3</v>
+      </c>
+      <c r="BI18">
+        <v>2.5</v>
+      </c>
+      <c r="BJ18">
+        <v>12.5</v>
+      </c>
+      <c r="BK18">
+        <v>4.1</v>
+      </c>
+      <c r="BL18">
+        <v>230</v>
+      </c>
+      <c r="BM18">
+        <v>170</v>
+      </c>
+      <c r="BN18">
+        <v>6.8</v>
+      </c>
+      <c r="BO18">
+        <v>4.8</v>
+      </c>
+      <c r="BP18">
         <v>34</v>
       </c>
-      <c r="AK18">
-        <v>27</v>
-      </c>
-      <c r="AL18">
-        <v>42</v>
-      </c>
-      <c r="AM18">
-        <v>110</v>
-      </c>
-      <c r="AN18">
-        <v>24</v>
-      </c>
-      <c r="AO18">
-        <v>42</v>
-      </c>
-      <c r="AP18">
-        <v>11.5</v>
-      </c>
-      <c r="AQ18">
-        <v>11</v>
-      </c>
-      <c r="AR18">
-        <v>20</v>
-      </c>
-      <c r="AS18">
-        <v>50</v>
-      </c>
-      <c r="AT18">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU18">
-        <v>7.2</v>
-      </c>
-      <c r="AV18">
-        <v>13</v>
-      </c>
-      <c r="AW18">
-        <v>36</v>
-      </c>
-      <c r="AX18">
-        <v>14</v>
-      </c>
-      <c r="AY18">
-        <v>10.5</v>
-      </c>
-      <c r="AZ18">
-        <v>16.5</v>
-      </c>
-      <c r="BA18">
-        <v>48</v>
-      </c>
-      <c r="BB18">
-        <v>30</v>
-      </c>
-      <c r="BC18">
-        <v>25</v>
-      </c>
-      <c r="BD18">
-        <v>38</v>
-      </c>
-      <c r="BE18">
-        <v>90</v>
-      </c>
-      <c r="BF18">
-        <v>22</v>
-      </c>
-      <c r="BG18">
-        <v>38</v>
-      </c>
-      <c r="BH18">
-        <v>3.3</v>
-      </c>
-      <c r="BI18">
-        <v>2.88</v>
-      </c>
-      <c r="BJ18">
-        <v>10.5</v>
-      </c>
-      <c r="BK18">
-        <v>8.4</v>
-      </c>
-      <c r="BL18">
-        <v>140</v>
-      </c>
-      <c r="BM18">
-        <v>11.5</v>
-      </c>
-      <c r="BN18">
-        <v>5.4</v>
-      </c>
-      <c r="BO18">
-        <v>4.6</v>
-      </c>
-      <c r="BP18">
-        <v>19.5</v>
-      </c>
       <c r="BQ18">
-        <v>16</v>
+        <v>5.2</v>
       </c>
       <c r="BR18">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BS18">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT18">
         <v>6.4</v>
       </c>
       <c r="BU18">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BV18">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BW18">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="BX18">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BY18">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="BZ18">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="CA18">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="CB18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5228,232 +5234,232 @@
         <v>126</v>
       </c>
       <c r="E19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F19">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="G19">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="H19">
-        <v>1.94</v>
+        <v>2.6</v>
       </c>
       <c r="I19">
-        <v>1.95</v>
+        <v>2.64</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K19">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L19">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="O19">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P19">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="R19">
+        <v>1.57</v>
+      </c>
+      <c r="S19">
+        <v>2.72</v>
+      </c>
+      <c r="T19">
+        <v>1.58</v>
+      </c>
+      <c r="U19">
+        <v>2.66</v>
+      </c>
+      <c r="V19">
         <v>1.61</v>
       </c>
-      <c r="S19">
-        <v>2.58</v>
-      </c>
-      <c r="T19">
-        <v>1.6</v>
-      </c>
-      <c r="U19">
-        <v>2.62</v>
-      </c>
-      <c r="V19">
-        <v>2.04</v>
-      </c>
       <c r="W19">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="X19">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="Y19">
+        <v>14.5</v>
+      </c>
+      <c r="Z19">
+        <v>19</v>
+      </c>
+      <c r="AA19">
+        <v>36</v>
+      </c>
+      <c r="AB19">
+        <v>15</v>
+      </c>
+      <c r="AC19">
+        <v>8.4</v>
+      </c>
+      <c r="AD19">
+        <v>12</v>
+      </c>
+      <c r="AE19">
+        <v>25</v>
+      </c>
+      <c r="AF19">
+        <v>21</v>
+      </c>
+      <c r="AG19">
+        <v>12.5</v>
+      </c>
+      <c r="AH19">
+        <v>13.5</v>
+      </c>
+      <c r="AI19">
+        <v>30</v>
+      </c>
+      <c r="AJ19">
+        <v>46</v>
+      </c>
+      <c r="AK19">
+        <v>28</v>
+      </c>
+      <c r="AL19">
+        <v>32</v>
+      </c>
+      <c r="AM19">
+        <v>55</v>
+      </c>
+      <c r="AN19">
+        <v>19.5</v>
+      </c>
+      <c r="AO19">
+        <v>17</v>
+      </c>
+      <c r="AP19">
+        <v>18.5</v>
+      </c>
+      <c r="AQ19">
+        <v>13.5</v>
+      </c>
+      <c r="AR19">
+        <v>18</v>
+      </c>
+      <c r="AS19">
+        <v>34</v>
+      </c>
+      <c r="AT19">
+        <v>14.5</v>
+      </c>
+      <c r="AU19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV19">
+        <v>11</v>
+      </c>
+      <c r="AW19">
+        <v>22</v>
+      </c>
+      <c r="AX19">
+        <v>19.5</v>
+      </c>
+      <c r="AY19">
+        <v>11.5</v>
+      </c>
+      <c r="AZ19">
         <v>13</v>
       </c>
-      <c r="Z19">
-        <v>14</v>
-      </c>
-      <c r="AA19">
-        <v>22</v>
-      </c>
-      <c r="AB19">
-        <v>21</v>
-      </c>
-      <c r="AC19">
-        <v>9.4</v>
-      </c>
-      <c r="AD19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE19">
-        <v>17</v>
-      </c>
-      <c r="AF19">
-        <v>32</v>
-      </c>
-      <c r="AG19">
-        <v>16</v>
-      </c>
-      <c r="AH19">
+      <c r="BA19">
+        <v>28</v>
+      </c>
+      <c r="BB19">
+        <v>42</v>
+      </c>
+      <c r="BC19">
+        <v>25</v>
+      </c>
+      <c r="BD19">
+        <v>30</v>
+      </c>
+      <c r="BE19">
+        <v>50</v>
+      </c>
+      <c r="BF19">
+        <v>17.5</v>
+      </c>
+      <c r="BG19">
         <v>15</v>
-      </c>
-      <c r="AI19">
-        <v>26</v>
-      </c>
-      <c r="AJ19">
-        <v>80</v>
-      </c>
-      <c r="AK19">
-        <v>42</v>
-      </c>
-      <c r="AL19">
-        <v>40</v>
-      </c>
-      <c r="AM19">
-        <v>60</v>
-      </c>
-      <c r="AN19">
-        <v>34</v>
-      </c>
-      <c r="AO19">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AP19">
-        <v>22</v>
-      </c>
-      <c r="AQ19">
-        <v>12.5</v>
-      </c>
-      <c r="AR19">
-        <v>13.5</v>
-      </c>
-      <c r="AS19">
-        <v>20</v>
-      </c>
-      <c r="AT19">
-        <v>19.5</v>
-      </c>
-      <c r="AU19">
-        <v>9</v>
-      </c>
-      <c r="AV19">
-        <v>9.6</v>
-      </c>
-      <c r="AW19">
-        <v>16</v>
-      </c>
-      <c r="AX19">
-        <v>30</v>
-      </c>
-      <c r="AY19">
-        <v>15</v>
-      </c>
-      <c r="AZ19">
-        <v>14</v>
-      </c>
-      <c r="BA19">
-        <v>25</v>
-      </c>
-      <c r="BB19">
-        <v>65</v>
-      </c>
-      <c r="BC19">
-        <v>38</v>
-      </c>
-      <c r="BD19">
-        <v>38</v>
-      </c>
-      <c r="BE19">
-        <v>55</v>
-      </c>
-      <c r="BF19">
-        <v>30</v>
-      </c>
-      <c r="BG19">
-        <v>8.800000000000001</v>
       </c>
       <c r="BH19">
         <v>4.3</v>
       </c>
       <c r="BI19">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BJ19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK19">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL19">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BM19">
-        <v>11.5</v>
+        <v>65</v>
       </c>
       <c r="BN19">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO19">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BP19">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BQ19">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="BR19">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BS19">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BT19">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV19">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="BW19">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BX19">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BY19">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BZ19">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="CA19">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5470,232 +5476,232 @@
         <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F20">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="G20">
+        <v>2.58</v>
+      </c>
+      <c r="H20">
         <v>3.1</v>
       </c>
-      <c r="H20">
-        <v>2.84</v>
-      </c>
       <c r="I20">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="J20">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K20">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="L20">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="M20">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="N20">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="O20">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="P20">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="Q20">
-        <v>2.74</v>
+        <v>2.16</v>
       </c>
       <c r="R20">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="S20">
+        <v>3.95</v>
+      </c>
+      <c r="T20">
+        <v>1.85</v>
+      </c>
+      <c r="U20">
+        <v>2.12</v>
+      </c>
+      <c r="V20">
+        <v>1.46</v>
+      </c>
+      <c r="W20">
+        <v>1.63</v>
+      </c>
+      <c r="X20">
+        <v>12</v>
+      </c>
+      <c r="Y20">
+        <v>11.5</v>
+      </c>
+      <c r="Z20">
+        <v>20</v>
+      </c>
+      <c r="AA20">
+        <v>60</v>
+      </c>
+      <c r="AB20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC20">
+        <v>7.4</v>
+      </c>
+      <c r="AD20">
+        <v>13.5</v>
+      </c>
+      <c r="AE20">
+        <v>38</v>
+      </c>
+      <c r="AF20">
+        <v>15.5</v>
+      </c>
+      <c r="AG20">
+        <v>11.5</v>
+      </c>
+      <c r="AH20">
+        <v>17.5</v>
+      </c>
+      <c r="AI20">
+        <v>50</v>
+      </c>
+      <c r="AJ20">
+        <v>38</v>
+      </c>
+      <c r="AK20">
+        <v>28</v>
+      </c>
+      <c r="AL20">
+        <v>44</v>
+      </c>
+      <c r="AM20">
+        <v>110</v>
+      </c>
+      <c r="AN20">
+        <v>25</v>
+      </c>
+      <c r="AO20">
+        <v>38</v>
+      </c>
+      <c r="AP20">
+        <v>11.5</v>
+      </c>
+      <c r="AQ20">
+        <v>10.5</v>
+      </c>
+      <c r="AR20">
+        <v>18.5</v>
+      </c>
+      <c r="AS20">
+        <v>48</v>
+      </c>
+      <c r="AT20">
+        <v>9.4</v>
+      </c>
+      <c r="AU20">
+        <v>7.2</v>
+      </c>
+      <c r="AV20">
+        <v>13</v>
+      </c>
+      <c r="AW20">
+        <v>36</v>
+      </c>
+      <c r="AX20">
+        <v>15</v>
+      </c>
+      <c r="AY20">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20">
+        <v>16.5</v>
+      </c>
+      <c r="BA20">
+        <v>48</v>
+      </c>
+      <c r="BB20">
+        <v>34</v>
+      </c>
+      <c r="BC20">
+        <v>27</v>
+      </c>
+      <c r="BD20">
+        <v>40</v>
+      </c>
+      <c r="BE20">
+        <v>85</v>
+      </c>
+      <c r="BF20">
+        <v>23</v>
+      </c>
+      <c r="BG20">
+        <v>34</v>
+      </c>
+      <c r="BH20">
+        <v>3.2</v>
+      </c>
+      <c r="BI20">
+        <v>2.98</v>
+      </c>
+      <c r="BJ20">
+        <v>9.6</v>
+      </c>
+      <c r="BK20">
+        <v>8.6</v>
+      </c>
+      <c r="BL20">
+        <v>140</v>
+      </c>
+      <c r="BM20">
+        <v>110</v>
+      </c>
+      <c r="BN20">
+        <v>5.3</v>
+      </c>
+      <c r="BO20">
+        <v>4.9</v>
+      </c>
+      <c r="BP20">
+        <v>19.5</v>
+      </c>
+      <c r="BQ20">
+        <v>16.5</v>
+      </c>
+      <c r="BR20">
+        <v>36</v>
+      </c>
+      <c r="BS20">
+        <v>12</v>
+      </c>
+      <c r="BT20">
+        <v>6.2</v>
+      </c>
+      <c r="BU20">
         <v>5.6</v>
       </c>
-      <c r="T20">
-        <v>2.16</v>
-      </c>
-      <c r="U20">
-        <v>1.84</v>
-      </c>
-      <c r="V20">
-        <v>1.53</v>
-      </c>
-      <c r="W20">
-        <v>1.47</v>
-      </c>
-      <c r="X20">
-        <v>8.4</v>
-      </c>
-      <c r="Y20">
-        <v>8</v>
-      </c>
-      <c r="Z20">
-        <v>16.5</v>
-      </c>
-      <c r="AA20">
-        <v>50</v>
-      </c>
-      <c r="AB20">
-        <v>8.6</v>
-      </c>
-      <c r="AC20">
-        <v>6.8</v>
-      </c>
-      <c r="AD20">
-        <v>13</v>
-      </c>
-      <c r="AE20">
-        <v>40</v>
-      </c>
-      <c r="AF20">
-        <v>18.5</v>
-      </c>
-      <c r="AG20">
-        <v>14</v>
-      </c>
-      <c r="AH20">
-        <v>22</v>
-      </c>
-      <c r="AI20">
-        <v>70</v>
-      </c>
-      <c r="AJ20">
-        <v>60</v>
-      </c>
-      <c r="AK20">
-        <v>46</v>
-      </c>
-      <c r="AL20">
-        <v>70</v>
-      </c>
-      <c r="AM20">
-        <v>170</v>
-      </c>
-      <c r="AN20">
-        <v>55</v>
-      </c>
-      <c r="AO20">
-        <v>48</v>
-      </c>
-      <c r="AP20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ20">
-        <v>7.8</v>
-      </c>
-      <c r="AR20">
-        <v>15.5</v>
-      </c>
-      <c r="AS20">
-        <v>44</v>
-      </c>
-      <c r="AT20">
-        <v>8.4</v>
-      </c>
-      <c r="AU20">
-        <v>6.6</v>
-      </c>
-      <c r="AV20">
-        <v>12.5</v>
-      </c>
-      <c r="AW20">
-        <v>38</v>
-      </c>
-      <c r="AX20">
-        <v>17.5</v>
-      </c>
-      <c r="AY20">
-        <v>13</v>
-      </c>
-      <c r="AZ20">
-        <v>21</v>
-      </c>
-      <c r="BA20">
-        <v>60</v>
-      </c>
-      <c r="BB20">
-        <v>50</v>
-      </c>
-      <c r="BC20">
+      <c r="BV20">
+        <v>27</v>
+      </c>
+      <c r="BW20">
+        <v>10.5</v>
+      </c>
+      <c r="BX20">
         <v>42</v>
       </c>
-      <c r="BD20">
-        <v>60</v>
-      </c>
-      <c r="BE20">
-        <v>140</v>
-      </c>
-      <c r="BF20">
-        <v>50</v>
-      </c>
-      <c r="BG20">
-        <v>44</v>
-      </c>
-      <c r="BH20">
-        <v>2.72</v>
-      </c>
-      <c r="BI20">
-        <v>2.52</v>
-      </c>
-      <c r="BJ20">
-        <v>11</v>
-      </c>
-      <c r="BK20">
-        <v>9.6</v>
-      </c>
-      <c r="BL20">
-        <v>220</v>
-      </c>
-      <c r="BM20">
-        <v>12.5</v>
-      </c>
-      <c r="BN20">
-        <v>5.9</v>
-      </c>
-      <c r="BO20">
-        <v>5.3</v>
-      </c>
-      <c r="BP20">
-        <v>34</v>
-      </c>
-      <c r="BQ20">
-        <v>9.6</v>
-      </c>
-      <c r="BR20">
-        <v>60</v>
-      </c>
-      <c r="BS20">
-        <v>11</v>
-      </c>
-      <c r="BT20">
-        <v>5.6</v>
-      </c>
-      <c r="BU20">
-        <v>5.1</v>
-      </c>
-      <c r="BV20">
-        <v>30</v>
-      </c>
-      <c r="BW20">
-        <v>9.4</v>
-      </c>
-      <c r="BX20">
-        <v>55</v>
-      </c>
       <c r="BY20">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ20">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="CA20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5712,232 +5718,232 @@
         <v>128</v>
       </c>
       <c r="E21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F21">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="G21">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="H21">
-        <v>3.6</v>
+        <v>1.93</v>
       </c>
       <c r="I21">
-        <v>3.65</v>
+        <v>1.94</v>
       </c>
       <c r="J21">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L21">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N21">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="O21">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P21">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="Q21">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="R21">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="S21">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="T21">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U21">
         <v>2.62</v>
       </c>
       <c r="V21">
-        <v>1.37</v>
+        <v>2.06</v>
       </c>
       <c r="W21">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="X21">
+        <v>23</v>
+      </c>
+      <c r="Y21">
+        <v>12.5</v>
+      </c>
+      <c r="Z21">
+        <v>13.5</v>
+      </c>
+      <c r="AA21">
+        <v>23</v>
+      </c>
+      <c r="AB21">
         <v>21</v>
       </c>
-      <c r="Y21">
-        <v>17.5</v>
-      </c>
-      <c r="Z21">
-        <v>28</v>
-      </c>
-      <c r="AA21">
-        <v>75</v>
-      </c>
-      <c r="AB21">
-        <v>13</v>
-      </c>
       <c r="AC21">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD21">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE21">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="AF21">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="AG21">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AH21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI21">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AJ21">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="AK21">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="AL21">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AM21">
         <v>60</v>
       </c>
       <c r="AN21">
+        <v>36</v>
+      </c>
+      <c r="AO21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AP21">
+        <v>22</v>
+      </c>
+      <c r="AQ21">
         <v>12</v>
       </c>
-      <c r="AO21">
-        <v>30</v>
-      </c>
-      <c r="AP21">
-        <v>19</v>
-      </c>
-      <c r="AQ21">
-        <v>16.5</v>
-      </c>
       <c r="AR21">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AS21">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="AT21">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU21">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV21">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AW21">
+        <v>16</v>
+      </c>
+      <c r="AX21">
         <v>32</v>
       </c>
-      <c r="AX21">
-        <v>14.5</v>
-      </c>
       <c r="AY21">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ21">
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BB21">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="BC21">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="BD21">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BE21">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF21">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BG21">
-        <v>28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BI21">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BJ21">
         <v>8.800000000000001</v>
       </c>
       <c r="BK21">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL21">
         <v>100</v>
       </c>
       <c r="BM21">
-        <v>11.5</v>
+        <v>65</v>
       </c>
       <c r="BN21">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BO21">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BP21">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="BQ21">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BR21">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BS21">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT21">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BU21">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV21">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="BW21">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BX21">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="BY21">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ21">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CA21">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="CB21" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5954,25 +5960,25 @@
         <v>129</v>
       </c>
       <c r="E22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F22">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G22">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I22">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J22">
         <v>3.4</v>
       </c>
       <c r="K22">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L22">
         <v>1.43</v>
@@ -5990,7 +5996,7 @@
         <v>1.89</v>
       </c>
       <c r="Q22">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R22">
         <v>1.33</v>
@@ -5999,22 +6005,22 @@
         <v>3.75</v>
       </c>
       <c r="T22">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U22">
         <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X22">
         <v>13</v>
       </c>
       <c r="Y22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z22">
         <v>24</v>
@@ -6035,7 +6041,7 @@
         <v>42</v>
       </c>
       <c r="AF22">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG22">
         <v>12</v>
@@ -6047,19 +6053,19 @@
         <v>55</v>
       </c>
       <c r="AJ22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK22">
         <v>27</v>
       </c>
       <c r="AL22">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM22">
         <v>120</v>
       </c>
       <c r="AN22">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO22">
         <v>42</v>
@@ -6077,7 +6083,7 @@
         <v>50</v>
       </c>
       <c r="AT22">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22">
         <v>7</v>
@@ -6086,19 +6092,19 @@
         <v>12.5</v>
       </c>
       <c r="AW22">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AX22">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22">
         <v>16.5</v>
       </c>
       <c r="BA22">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB22">
         <v>28</v>
@@ -6107,19 +6113,19 @@
         <v>22</v>
       </c>
       <c r="BD22">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE22">
         <v>75</v>
       </c>
       <c r="BF22">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG22">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BH22">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI22">
         <v>2.74</v>
@@ -6140,7 +6146,7 @@
         <v>5.9</v>
       </c>
       <c r="BO22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP22">
         <v>21</v>
@@ -6152,7 +6158,7 @@
         <v>38</v>
       </c>
       <c r="BS22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BT22">
         <v>7.4</v>
@@ -6179,7 +6185,7 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6196,25 +6202,25 @@
         <v>130</v>
       </c>
       <c r="E23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F23">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G23">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H23">
         <v>2.42</v>
       </c>
       <c r="I23">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J23">
         <v>3.4</v>
       </c>
       <c r="K23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L23">
         <v>1.4</v>
@@ -6226,31 +6232,31 @@
         <v>3.9</v>
       </c>
       <c r="O23">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P23">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q23">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R23">
         <v>1.37</v>
       </c>
       <c r="S23">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T23">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U23">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V23">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W23">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X23">
         <v>15</v>
@@ -6259,7 +6265,7 @@
         <v>11</v>
       </c>
       <c r="Z23">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA23">
         <v>38</v>
@@ -6274,10 +6280,10 @@
         <v>12</v>
       </c>
       <c r="AE23">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF23">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG23">
         <v>14</v>
@@ -6286,142 +6292,142 @@
         <v>17.5</v>
       </c>
       <c r="AI23">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ23">
         <v>55</v>
       </c>
       <c r="AK23">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AL23">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM23">
         <v>110</v>
       </c>
       <c r="AN23">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO23">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP23">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ23">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AR23">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="AS23">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT23">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="AU23">
+        <v>4.9</v>
+      </c>
+      <c r="AV23">
+        <v>6</v>
+      </c>
+      <c r="AW23">
+        <v>7.6</v>
+      </c>
+      <c r="AX23">
+        <v>7.2</v>
+      </c>
+      <c r="AY23">
+        <v>6.2</v>
+      </c>
+      <c r="AZ23">
+        <v>6.6</v>
+      </c>
+      <c r="BA23">
+        <v>8.6</v>
+      </c>
+      <c r="BB23">
+        <v>9</v>
+      </c>
+      <c r="BC23">
+        <v>8.6</v>
+      </c>
+      <c r="BD23">
+        <v>8.6</v>
+      </c>
+      <c r="BE23">
+        <v>9.6</v>
+      </c>
+      <c r="BF23">
+        <v>8.4</v>
+      </c>
+      <c r="BG23">
         <v>7</v>
-      </c>
-      <c r="AV23">
-        <v>10</v>
-      </c>
-      <c r="AW23">
-        <v>23</v>
-      </c>
-      <c r="AX23">
-        <v>19</v>
-      </c>
-      <c r="AY23">
-        <v>11.5</v>
-      </c>
-      <c r="AZ23">
-        <v>14.5</v>
-      </c>
-      <c r="BA23">
-        <v>7.8</v>
-      </c>
-      <c r="BB23">
-        <v>7.8</v>
-      </c>
-      <c r="BC23">
-        <v>7.6</v>
-      </c>
-      <c r="BD23">
-        <v>36</v>
-      </c>
-      <c r="BE23">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF23">
-        <v>23</v>
-      </c>
-      <c r="BG23">
-        <v>18</v>
       </c>
       <c r="BH23">
         <v>3.5</v>
       </c>
       <c r="BI23">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="BJ23">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK23">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN23">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO23">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP23">
         <v>25</v>
       </c>
       <c r="BQ23">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BR23">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS23">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT23">
         <v>5.5</v>
       </c>
       <c r="BU23">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV23">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW23">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX23">
         <v>32</v>
       </c>
       <c r="BY23">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ23">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA23">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB23" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6438,64 +6444,64 @@
         <v>131</v>
       </c>
       <c r="E24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G24">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H24">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I24">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K24">
         <v>3.45</v>
       </c>
       <c r="L24">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M24">
         <v>1.11</v>
       </c>
       <c r="N24">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="O24">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P24">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q24">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R24">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S24">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T24">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U24">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V24">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W24">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y24">
         <v>13</v>
@@ -6507,10 +6513,10 @@
         <v>150</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC24">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD24">
         <v>21</v>
@@ -6525,19 +6531,19 @@
         <v>12</v>
       </c>
       <c r="AH24">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI24">
         <v>120</v>
       </c>
       <c r="AJ24">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AK24">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL24">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM24">
         <v>190</v>
@@ -6546,52 +6552,52 @@
         <v>24</v>
       </c>
       <c r="AO24">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AP24">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ24">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR24">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS24">
         <v>80</v>
       </c>
       <c r="AT24">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU24">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW24">
         <v>46</v>
       </c>
       <c r="AX24">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY24">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA24">
         <v>55</v>
       </c>
       <c r="BB24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC24">
         <v>20</v>
       </c>
       <c r="BD24">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BE24">
         <v>11</v>
@@ -6606,7 +6612,7 @@
         <v>3.2</v>
       </c>
       <c r="BI24">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ24">
         <v>13</v>
@@ -6618,31 +6624,31 @@
         <v>220</v>
       </c>
       <c r="BM24">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BN24">
         <v>4.5</v>
       </c>
       <c r="BO24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP24">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ24">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="BR24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS24">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT24">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BU24">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV24">
         <v>55</v>
@@ -6663,12 +6669,12 @@
         <v>6.4</v>
       </c>
       <c r="CB24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
         <v>94</v>
@@ -6680,393 +6686,393 @@
         <v>132</v>
       </c>
       <c r="E25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F25">
-        <v>1.79</v>
+        <v>1.17</v>
       </c>
       <c r="G25">
-        <v>1.83</v>
+        <v>1.19</v>
       </c>
       <c r="H25">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="I25">
-        <v>5.8</v>
+        <v>26</v>
       </c>
       <c r="J25">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="L25">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="M25">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="N25">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="O25">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="P25">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="Q25">
-        <v>2.16</v>
+        <v>1.48</v>
       </c>
       <c r="R25">
-        <v>1.29</v>
+        <v>1.74</v>
       </c>
       <c r="S25">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="T25">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="U25">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="W25">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AA25">
         <v>1000</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AE25">
         <v>1000</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="AO25">
         <v>1000</v>
       </c>
       <c r="AP25">
+        <v>25</v>
+      </c>
+      <c r="AQ25">
+        <v>46</v>
+      </c>
+      <c r="AR25">
         <v>1.01</v>
       </c>
-      <c r="AQ25">
-        <v>1.01</v>
-      </c>
-      <c r="AR25">
-        <v>1.15</v>
-      </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BG25">
         <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BL25">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM25">
         <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BQ25">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="BW25">
         <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BY25">
         <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="CB25" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s">
         <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
         <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F26">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G26">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H26">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K26">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M26">
         <v>1.08</v>
       </c>
       <c r="N26">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O26">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P26">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q26">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R26">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S26">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T26">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U26">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="V26">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W26">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X26">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y26">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z26">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA26">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AB26">
         <v>7.4</v>
       </c>
       <c r="AC26">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD26">
         <v>32</v>
       </c>
       <c r="AE26">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AF26">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG26">
         <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI26">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AJ26">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK26">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL26">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM26">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN26">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO26">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AP26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ26">
         <v>16.5</v>
       </c>
       <c r="AR26">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS26">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT26">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU26">
         <v>8.199999999999999</v>
       </c>
       <c r="AV26">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW26">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX26">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AY26">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA26">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB26">
         <v>13</v>
@@ -7075,22 +7081,22 @@
         <v>16</v>
       </c>
       <c r="BD26">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BE26">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="BF26">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG26">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="BH26">
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
@@ -7147,12 +7153,12 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B27" t="s">
         <v>94</v>
@@ -7164,237 +7170,237 @@
         <v>134</v>
       </c>
       <c r="E27" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F27">
-        <v>2.66</v>
+        <v>1.62</v>
       </c>
       <c r="G27">
-        <v>2.78</v>
+        <v>1.65</v>
       </c>
       <c r="H27">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="I27">
-        <v>2.92</v>
+        <v>7.2</v>
       </c>
       <c r="J27">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K27">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="L27">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M27">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N27">
+        <v>3.6</v>
+      </c>
+      <c r="O27">
+        <v>1.36</v>
+      </c>
+      <c r="P27">
+        <v>1.87</v>
+      </c>
+      <c r="Q27">
+        <v>2.06</v>
+      </c>
+      <c r="R27">
+        <v>1.33</v>
+      </c>
+      <c r="S27">
         <v>3.8</v>
       </c>
-      <c r="O27">
-        <v>1.33</v>
-      </c>
-      <c r="P27">
-        <v>1.92</v>
-      </c>
-      <c r="Q27">
-        <v>2</v>
-      </c>
-      <c r="R27">
-        <v>1.36</v>
-      </c>
-      <c r="S27">
-        <v>3.65</v>
-      </c>
       <c r="T27">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="U27">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="V27">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="W27">
-        <v>1.56</v>
+        <v>2.52</v>
       </c>
       <c r="X27">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y27">
+        <v>23</v>
+      </c>
+      <c r="Z27">
+        <v>70</v>
+      </c>
+      <c r="AA27">
+        <v>270</v>
+      </c>
+      <c r="AB27">
+        <v>7.4</v>
+      </c>
+      <c r="AC27">
+        <v>9.4</v>
+      </c>
+      <c r="AD27">
+        <v>32</v>
+      </c>
+      <c r="AE27">
+        <v>140</v>
+      </c>
+      <c r="AF27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG27">
+        <v>10.5</v>
+      </c>
+      <c r="AH27">
+        <v>25</v>
+      </c>
+      <c r="AI27">
+        <v>130</v>
+      </c>
+      <c r="AJ27">
+        <v>15.5</v>
+      </c>
+      <c r="AK27">
+        <v>19</v>
+      </c>
+      <c r="AL27">
+        <v>50</v>
+      </c>
+      <c r="AM27">
+        <v>190</v>
+      </c>
+      <c r="AN27">
+        <v>13</v>
+      </c>
+      <c r="AO27">
+        <v>210</v>
+      </c>
+      <c r="AP27">
+        <v>11.5</v>
+      </c>
+      <c r="AQ27">
+        <v>16.5</v>
+      </c>
+      <c r="AR27">
+        <v>40</v>
+      </c>
+      <c r="AS27">
+        <v>8.6</v>
+      </c>
+      <c r="AT27">
+        <v>6.6</v>
+      </c>
+      <c r="AU27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV27">
+        <v>22</v>
+      </c>
+      <c r="AW27">
+        <v>55</v>
+      </c>
+      <c r="AX27">
+        <v>8</v>
+      </c>
+      <c r="AY27">
+        <v>9</v>
+      </c>
+      <c r="AZ27">
+        <v>21</v>
+      </c>
+      <c r="BA27">
+        <v>55</v>
+      </c>
+      <c r="BB27">
+        <v>13</v>
+      </c>
+      <c r="BC27">
+        <v>16</v>
+      </c>
+      <c r="BD27">
+        <v>36</v>
+      </c>
+      <c r="BE27">
+        <v>9</v>
+      </c>
+      <c r="BF27">
+        <v>9.4</v>
+      </c>
+      <c r="BG27">
+        <v>9</v>
+      </c>
+      <c r="BH27">
+        <v>3.85</v>
+      </c>
+      <c r="BI27">
+        <v>2.68</v>
+      </c>
+      <c r="BJ27">
         <v>13.5</v>
       </c>
-      <c r="Z27">
-        <v>24</v>
-      </c>
-      <c r="AA27">
+      <c r="BK27">
+        <v>8.4</v>
+      </c>
+      <c r="BL27">
+        <v>210</v>
+      </c>
+      <c r="BM27">
+        <v>1.01</v>
+      </c>
+      <c r="BN27">
+        <v>4.6</v>
+      </c>
+      <c r="BO27">
+        <v>3.15</v>
+      </c>
+      <c r="BP27">
+        <v>13</v>
+      </c>
+      <c r="BQ27">
+        <v>8</v>
+      </c>
+      <c r="BR27">
+        <v>36</v>
+      </c>
+      <c r="BS27">
+        <v>20</v>
+      </c>
+      <c r="BT27">
+        <v>12.5</v>
+      </c>
+      <c r="BU27">
+        <v>7.6</v>
+      </c>
+      <c r="BV27">
+        <v>80</v>
+      </c>
+      <c r="BW27">
         <v>46</v>
       </c>
-      <c r="AB27">
-        <v>12.5</v>
-      </c>
-      <c r="AC27">
-        <v>7.8</v>
-      </c>
-      <c r="AD27">
-        <v>13</v>
-      </c>
-      <c r="AE27">
-        <v>36</v>
-      </c>
-      <c r="AF27">
-        <v>18</v>
-      </c>
-      <c r="AG27">
-        <v>12.5</v>
-      </c>
-      <c r="AH27">
-        <v>21</v>
-      </c>
-      <c r="AI27">
-        <v>46</v>
-      </c>
-      <c r="AJ27">
+      <c r="BX27">
+        <v>90</v>
+      </c>
+      <c r="BY27">
         <v>50</v>
       </c>
-      <c r="AK27">
-        <v>36</v>
-      </c>
-      <c r="AL27">
-        <v>48</v>
-      </c>
-      <c r="AM27">
-        <v>120</v>
-      </c>
-      <c r="AN27">
-        <v>26</v>
-      </c>
-      <c r="AO27">
-        <v>38</v>
-      </c>
-      <c r="AP27">
-        <v>12.5</v>
-      </c>
-      <c r="AQ27">
-        <v>10</v>
-      </c>
-      <c r="AR27">
-        <v>15</v>
-      </c>
-      <c r="AS27">
-        <v>6.8</v>
-      </c>
-      <c r="AT27">
-        <v>10</v>
-      </c>
-      <c r="AU27">
-        <v>6.8</v>
-      </c>
-      <c r="AV27">
-        <v>11</v>
-      </c>
-      <c r="AW27">
-        <v>8</v>
-      </c>
-      <c r="AX27">
-        <v>15</v>
-      </c>
-      <c r="AY27">
-        <v>10.5</v>
-      </c>
-      <c r="AZ27">
-        <v>15</v>
-      </c>
-      <c r="BA27">
-        <v>15.5</v>
-      </c>
-      <c r="BB27">
-        <v>8.4</v>
-      </c>
-      <c r="BC27">
-        <v>8</v>
-      </c>
-      <c r="BD27">
-        <v>14.5</v>
-      </c>
-      <c r="BE27">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF27">
-        <v>20</v>
-      </c>
-      <c r="BG27">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH27">
-        <v>3.9</v>
-      </c>
-      <c r="BI27">
-        <v>2.7</v>
-      </c>
-      <c r="BJ27">
-        <v>11.5</v>
-      </c>
-      <c r="BK27">
-        <v>3.5</v>
-      </c>
-      <c r="BL27">
-        <v>1000</v>
-      </c>
-      <c r="BM27">
-        <v>4.6</v>
-      </c>
-      <c r="BN27">
-        <v>6.8</v>
-      </c>
-      <c r="BO27">
-        <v>4.3</v>
-      </c>
-      <c r="BP27">
-        <v>25</v>
-      </c>
-      <c r="BQ27">
-        <v>4</v>
-      </c>
-      <c r="BR27">
-        <v>40</v>
-      </c>
-      <c r="BS27">
-        <v>4.2</v>
-      </c>
-      <c r="BT27">
-        <v>7.2</v>
-      </c>
-      <c r="BU27">
-        <v>4.5</v>
-      </c>
-      <c r="BV27">
-        <v>28</v>
-      </c>
-      <c r="BW27">
-        <v>4</v>
-      </c>
-      <c r="BX27">
-        <v>42</v>
-      </c>
-      <c r="BY27">
-        <v>4.2</v>
-      </c>
       <c r="BZ27">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="CA27">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="CB27" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
         <v>94</v>
@@ -7406,88 +7412,88 @@
         <v>135</v>
       </c>
       <c r="E28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F28">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="G28">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="H28">
+        <v>2.88</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28">
         <v>3.35</v>
       </c>
-      <c r="I28">
-        <v>3.6</v>
-      </c>
-      <c r="J28">
-        <v>3.2</v>
-      </c>
       <c r="K28">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L28">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M28">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N28">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="O28">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="P28">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="Q28">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="R28">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S28">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="T28">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="U28">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="X28">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="Y28">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA28">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AB28">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="AC28">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD28">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE28">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AF28">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AG28">
         <v>12.5</v>
@@ -7496,177 +7502,177 @@
         <v>21</v>
       </c>
       <c r="AI28">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AJ28">
+        <v>50</v>
+      </c>
+      <c r="AK28">
         <v>36</v>
       </c>
-      <c r="AK28">
-        <v>32</v>
-      </c>
       <c r="AL28">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM28">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AN28">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO28">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AP28">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ28">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR28">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="AS28">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="AT28">
+        <v>9.6</v>
+      </c>
+      <c r="AU28">
+        <v>6.8</v>
+      </c>
+      <c r="AV28">
+        <v>11</v>
+      </c>
+      <c r="AW28">
+        <v>6.8</v>
+      </c>
+      <c r="AX28">
+        <v>6.2</v>
+      </c>
+      <c r="AY28">
+        <v>5.4</v>
+      </c>
+      <c r="AZ28">
+        <v>14.5</v>
+      </c>
+      <c r="BA28">
+        <v>7</v>
+      </c>
+      <c r="BB28">
+        <v>6.8</v>
+      </c>
+      <c r="BC28">
+        <v>6.8</v>
+      </c>
+      <c r="BD28">
+        <v>7</v>
+      </c>
+      <c r="BE28">
         <v>7.4</v>
       </c>
-      <c r="AU28">
-        <v>6.6</v>
-      </c>
-      <c r="AV28">
-        <v>13</v>
-      </c>
-      <c r="AW28">
-        <v>30</v>
-      </c>
-      <c r="AX28">
-        <v>12</v>
-      </c>
-      <c r="AY28">
-        <v>10</v>
-      </c>
-      <c r="AZ28">
-        <v>17</v>
-      </c>
-      <c r="BA28">
-        <v>44</v>
-      </c>
-      <c r="BB28">
-        <v>24</v>
-      </c>
-      <c r="BC28">
-        <v>23</v>
-      </c>
-      <c r="BD28">
-        <v>36</v>
-      </c>
-      <c r="BE28">
-        <v>90</v>
-      </c>
       <c r="BF28">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BG28">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BH28">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>2.5</v>
+        <v>1.19</v>
       </c>
       <c r="BJ28">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BL28">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BN28">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>4</v>
+        <v>1.19</v>
       </c>
       <c r="BP28">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BR28">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BT28">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>5.1</v>
+        <v>1.19</v>
       </c>
       <c r="BV28">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="BX28">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="CB28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
         <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
         <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F29">
-        <v>4.6</v>
+        <v>2.36</v>
       </c>
       <c r="G29">
-        <v>4.9</v>
+        <v>2.44</v>
       </c>
       <c r="H29">
-        <v>1.97</v>
+        <v>3.4</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J29">
+        <v>3.25</v>
+      </c>
+      <c r="K29">
         <v>3.45</v>
-      </c>
-      <c r="K29">
-        <v>3.6</v>
       </c>
       <c r="L29">
         <v>1.5</v>
@@ -7675,234 +7681,234 @@
         <v>1.1</v>
       </c>
       <c r="N29">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O29">
         <v>1.43</v>
       </c>
       <c r="P29">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Q29">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R29">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S29">
         <v>4.4</v>
       </c>
       <c r="T29">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="U29">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V29">
-        <v>2</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
-        <v>1.26</v>
+        <v>1.69</v>
       </c>
       <c r="X29">
         <v>11.5</v>
       </c>
       <c r="Y29">
+        <v>12</v>
+      </c>
+      <c r="Z29">
+        <v>25</v>
+      </c>
+      <c r="AA29">
+        <v>80</v>
+      </c>
+      <c r="AB29">
+        <v>8.6</v>
+      </c>
+      <c r="AC29">
         <v>7.6</v>
       </c>
-      <c r="Z29">
-        <v>11.5</v>
-      </c>
-      <c r="AA29">
-        <v>24</v>
-      </c>
-      <c r="AB29">
-        <v>14.5</v>
-      </c>
-      <c r="AC29">
-        <v>8</v>
-      </c>
       <c r="AD29">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE29">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AF29">
+        <v>15</v>
+      </c>
+      <c r="AG29">
+        <v>12.5</v>
+      </c>
+      <c r="AH29">
+        <v>21</v>
+      </c>
+      <c r="AI29">
+        <v>75</v>
+      </c>
+      <c r="AJ29">
         <v>36</v>
       </c>
-      <c r="AG29">
+      <c r="AK29">
+        <v>32</v>
+      </c>
+      <c r="AL29">
+        <v>55</v>
+      </c>
+      <c r="AM29">
+        <v>160</v>
+      </c>
+      <c r="AN29">
+        <v>28</v>
+      </c>
+      <c r="AO29">
+        <v>60</v>
+      </c>
+      <c r="AP29">
+        <v>9.4</v>
+      </c>
+      <c r="AQ29">
+        <v>10</v>
+      </c>
+      <c r="AR29">
         <v>20</v>
       </c>
-      <c r="AH29">
+      <c r="AS29">
+        <v>27</v>
+      </c>
+      <c r="AT29">
+        <v>7.4</v>
+      </c>
+      <c r="AU29">
+        <v>6.6</v>
+      </c>
+      <c r="AV29">
+        <v>13</v>
+      </c>
+      <c r="AW29">
+        <v>30</v>
+      </c>
+      <c r="AX29">
+        <v>12</v>
+      </c>
+      <c r="AY29">
+        <v>10</v>
+      </c>
+      <c r="AZ29">
+        <v>17</v>
+      </c>
+      <c r="BA29">
+        <v>42</v>
+      </c>
+      <c r="BB29">
         <v>23</v>
       </c>
-      <c r="AI29">
-        <v>55</v>
-      </c>
-      <c r="AJ29">
-        <v>140</v>
-      </c>
-      <c r="AK29">
-        <v>85</v>
-      </c>
-      <c r="AL29">
-        <v>100</v>
-      </c>
-      <c r="AM29">
-        <v>180</v>
-      </c>
-      <c r="AN29">
-        <v>120</v>
-      </c>
-      <c r="AO29">
-        <v>18.5</v>
-      </c>
-      <c r="AP29">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ29">
-        <v>6.8</v>
-      </c>
-      <c r="AR29">
-        <v>10</v>
-      </c>
-      <c r="AS29">
-        <v>19.5</v>
-      </c>
-      <c r="AT29">
+      <c r="BC29">
+        <v>22</v>
+      </c>
+      <c r="BD29">
+        <v>34</v>
+      </c>
+      <c r="BE29">
+        <v>90</v>
+      </c>
+      <c r="BF29">
+        <v>20</v>
+      </c>
+      <c r="BG29">
+        <v>34</v>
+      </c>
+      <c r="BH29">
+        <v>3.3</v>
+      </c>
+      <c r="BI29">
+        <v>2.5</v>
+      </c>
+      <c r="BJ29">
         <v>12</v>
-      </c>
-      <c r="AU29">
-        <v>7.2</v>
-      </c>
-      <c r="AV29">
-        <v>9.6</v>
-      </c>
-      <c r="AW29">
-        <v>20</v>
-      </c>
-      <c r="AX29">
-        <v>17</v>
-      </c>
-      <c r="AY29">
-        <v>17</v>
-      </c>
-      <c r="AZ29">
-        <v>19.5</v>
-      </c>
-      <c r="BA29">
-        <v>9.6</v>
-      </c>
-      <c r="BB29">
-        <v>10.5</v>
-      </c>
-      <c r="BC29">
-        <v>28</v>
-      </c>
-      <c r="BD29">
-        <v>42</v>
-      </c>
-      <c r="BE29">
-        <v>10</v>
-      </c>
-      <c r="BF29">
-        <v>10.5</v>
-      </c>
-      <c r="BG29">
-        <v>16</v>
-      </c>
-      <c r="BH29">
-        <v>1000</v>
-      </c>
-      <c r="BI29">
-        <v>1.25</v>
-      </c>
-      <c r="BJ29">
-        <v>1000</v>
       </c>
       <c r="BK29">
         <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM29">
         <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO29">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ29">
         <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS29">
         <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU29">
-        <v>1.42</v>
+        <v>5.1</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY29">
         <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s">
         <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
         <v>137</v>
       </c>
       <c r="E30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F30">
-        <v>1.87</v>
+        <v>4.6</v>
       </c>
       <c r="G30">
-        <v>1.91</v>
+        <v>4.9</v>
       </c>
       <c r="H30">
-        <v>5.3</v>
+        <v>1.96</v>
       </c>
       <c r="I30">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J30">
         <v>3.45</v>
@@ -7911,216 +7917,216 @@
         <v>3.6</v>
       </c>
       <c r="L30">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="M30">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N30">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="O30">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="P30">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="Q30">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="R30">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S30">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="T30">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="U30">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="V30">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="W30">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="X30">
         <v>11.5</v>
       </c>
       <c r="Y30">
+        <v>7.6</v>
+      </c>
+      <c r="Z30">
+        <v>11.5</v>
+      </c>
+      <c r="AA30">
+        <v>28</v>
+      </c>
+      <c r="AB30">
+        <v>14.5</v>
+      </c>
+      <c r="AC30">
+        <v>8</v>
+      </c>
+      <c r="AD30">
+        <v>11</v>
+      </c>
+      <c r="AE30">
+        <v>25</v>
+      </c>
+      <c r="AF30">
+        <v>36</v>
+      </c>
+      <c r="AG30">
+        <v>20</v>
+      </c>
+      <c r="AH30">
+        <v>23</v>
+      </c>
+      <c r="AI30">
+        <v>55</v>
+      </c>
+      <c r="AJ30">
+        <v>140</v>
+      </c>
+      <c r="AK30">
+        <v>95</v>
+      </c>
+      <c r="AL30">
+        <v>100</v>
+      </c>
+      <c r="AM30">
+        <v>180</v>
+      </c>
+      <c r="AN30">
+        <v>120</v>
+      </c>
+      <c r="AO30">
+        <v>18.5</v>
+      </c>
+      <c r="AP30">
+        <v>10</v>
+      </c>
+      <c r="AQ30">
+        <v>6.8</v>
+      </c>
+      <c r="AR30">
+        <v>10</v>
+      </c>
+      <c r="AS30">
+        <v>19.5</v>
+      </c>
+      <c r="AT30">
+        <v>12</v>
+      </c>
+      <c r="AU30">
+        <v>7.2</v>
+      </c>
+      <c r="AV30">
+        <v>9.6</v>
+      </c>
+      <c r="AW30">
+        <v>20</v>
+      </c>
+      <c r="AX30">
+        <v>17</v>
+      </c>
+      <c r="AY30">
+        <v>17.5</v>
+      </c>
+      <c r="AZ30">
+        <v>19.5</v>
+      </c>
+      <c r="BA30">
+        <v>9.6</v>
+      </c>
+      <c r="BB30">
+        <v>10.5</v>
+      </c>
+      <c r="BC30">
+        <v>28</v>
+      </c>
+      <c r="BD30">
+        <v>42</v>
+      </c>
+      <c r="BE30">
+        <v>10</v>
+      </c>
+      <c r="BF30">
+        <v>10.5</v>
+      </c>
+      <c r="BG30">
         <v>16</v>
       </c>
-      <c r="Z30">
-        <v>44</v>
-      </c>
-      <c r="AA30">
-        <v>180</v>
-      </c>
-      <c r="AB30">
-        <v>7.2</v>
-      </c>
-      <c r="AC30">
-        <v>9</v>
-      </c>
-      <c r="AD30">
-        <v>26</v>
-      </c>
-      <c r="AE30">
-        <v>110</v>
-      </c>
-      <c r="AF30">
-        <v>11.5</v>
-      </c>
-      <c r="AG30">
-        <v>12</v>
-      </c>
-      <c r="AH30">
-        <v>32</v>
-      </c>
-      <c r="AI30">
-        <v>120</v>
-      </c>
-      <c r="AJ30">
-        <v>25</v>
-      </c>
-      <c r="AK30">
-        <v>28</v>
-      </c>
-      <c r="AL30">
-        <v>60</v>
-      </c>
-      <c r="AM30">
-        <v>210</v>
-      </c>
-      <c r="AN30">
-        <v>20</v>
-      </c>
-      <c r="AO30">
-        <v>170</v>
-      </c>
-      <c r="AP30">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ30">
-        <v>12</v>
-      </c>
-      <c r="AR30">
-        <v>26</v>
-      </c>
-      <c r="AS30">
-        <v>6.2</v>
-      </c>
-      <c r="AT30">
-        <v>5.6</v>
-      </c>
-      <c r="AU30">
-        <v>7.4</v>
-      </c>
-      <c r="AV30">
-        <v>18.5</v>
-      </c>
-      <c r="AW30">
-        <v>6</v>
-      </c>
-      <c r="AX30">
-        <v>8.6</v>
-      </c>
-      <c r="AY30">
-        <v>9</v>
-      </c>
-      <c r="AZ30">
-        <v>21</v>
-      </c>
-      <c r="BA30">
-        <v>6</v>
-      </c>
-      <c r="BB30">
-        <v>18.5</v>
-      </c>
-      <c r="BC30">
-        <v>20</v>
-      </c>
-      <c r="BD30">
-        <v>32</v>
-      </c>
-      <c r="BE30">
-        <v>6.2</v>
-      </c>
-      <c r="BF30">
-        <v>17</v>
-      </c>
-      <c r="BG30">
-        <v>6</v>
-      </c>
       <c r="BH30">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BI30">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="BJ30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BK30">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BL30">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BN30">
+        <v>8.4</v>
+      </c>
+      <c r="BO30">
+        <v>6.8</v>
+      </c>
+      <c r="BP30">
+        <v>48</v>
+      </c>
+      <c r="BQ30">
+        <v>5.2</v>
+      </c>
+      <c r="BR30">
+        <v>75</v>
+      </c>
+      <c r="BS30">
+        <v>5.4</v>
+      </c>
+      <c r="BT30">
+        <v>5.2</v>
+      </c>
+      <c r="BU30">
+        <v>4</v>
+      </c>
+      <c r="BV30">
+        <v>18</v>
+      </c>
+      <c r="BW30">
         <v>4.4</v>
       </c>
-      <c r="BO30">
-        <v>3.85</v>
-      </c>
-      <c r="BP30">
-        <v>16.5</v>
-      </c>
-      <c r="BQ30">
-        <v>1.01</v>
-      </c>
-      <c r="BR30">
-        <v>44</v>
-      </c>
-      <c r="BS30">
-        <v>1.01</v>
-      </c>
-      <c r="BT30">
-        <v>8.4</v>
-      </c>
-      <c r="BU30">
-        <v>6.4</v>
-      </c>
-      <c r="BV30">
-        <v>65</v>
-      </c>
-      <c r="BW30">
-        <v>1.01</v>
-      </c>
       <c r="BX30">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="BY30">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="BZ30">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CB30" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
         <v>94</v>
@@ -8132,232 +8138,474 @@
         <v>138</v>
       </c>
       <c r="E31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F31">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="G31">
-        <v>2.44</v>
+        <v>1.96</v>
       </c>
       <c r="H31">
+        <v>4.9</v>
+      </c>
+      <c r="I31">
+        <v>5.3</v>
+      </c>
+      <c r="J31">
         <v>3.45</v>
       </c>
-      <c r="I31">
-        <v>3.65</v>
-      </c>
-      <c r="J31">
-        <v>3.2</v>
-      </c>
       <c r="K31">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="L31">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M31">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N31">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="O31">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="P31">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="Q31">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="R31">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="S31">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="T31">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="U31">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="V31">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="W31">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="X31">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y31">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z31">
+        <v>42</v>
+      </c>
+      <c r="AA31">
+        <v>170</v>
+      </c>
+      <c r="AB31">
+        <v>6.6</v>
+      </c>
+      <c r="AC31">
+        <v>9</v>
+      </c>
+      <c r="AD31">
+        <v>21</v>
+      </c>
+      <c r="AE31">
+        <v>100</v>
+      </c>
+      <c r="AF31">
+        <v>10.5</v>
+      </c>
+      <c r="AG31">
+        <v>10.5</v>
+      </c>
+      <c r="AH31">
+        <v>32</v>
+      </c>
+      <c r="AI31">
+        <v>120</v>
+      </c>
+      <c r="AJ31">
+        <v>23</v>
+      </c>
+      <c r="AK31">
+        <v>29</v>
+      </c>
+      <c r="AL31">
+        <v>55</v>
+      </c>
+      <c r="AM31">
+        <v>230</v>
+      </c>
+      <c r="AN31">
         <v>24</v>
       </c>
-      <c r="AA31">
-        <v>70</v>
-      </c>
-      <c r="AB31">
-        <v>9.6</v>
-      </c>
-      <c r="AC31">
-        <v>7.4</v>
-      </c>
-      <c r="AD31">
-        <v>15.5</v>
-      </c>
-      <c r="AE31">
-        <v>46</v>
-      </c>
-      <c r="AF31">
-        <v>14.5</v>
-      </c>
-      <c r="AG31">
-        <v>12</v>
-      </c>
-      <c r="AH31">
-        <v>18</v>
-      </c>
-      <c r="AI31">
-        <v>60</v>
-      </c>
-      <c r="AJ31">
-        <v>34</v>
-      </c>
-      <c r="AK31">
-        <v>28</v>
-      </c>
-      <c r="AL31">
-        <v>46</v>
-      </c>
-      <c r="AM31">
-        <v>1000</v>
-      </c>
-      <c r="AN31">
-        <v>23</v>
-      </c>
       <c r="AO31">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="AP31">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ31">
         <v>11.5</v>
       </c>
       <c r="AR31">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AS31">
+        <v>10</v>
+      </c>
+      <c r="AT31">
+        <v>5.9</v>
+      </c>
+      <c r="AU31">
+        <v>5.8</v>
+      </c>
+      <c r="AV31">
+        <v>16</v>
+      </c>
+      <c r="AW31">
         <v>55</v>
       </c>
-      <c r="AT31">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU31">
-        <v>6.6</v>
-      </c>
-      <c r="AV31">
-        <v>13</v>
-      </c>
-      <c r="AW31">
-        <v>36</v>
-      </c>
       <c r="AX31">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AY31">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ31">
+        <v>20</v>
+      </c>
+      <c r="BA31">
+        <v>60</v>
+      </c>
+      <c r="BB31">
+        <v>17</v>
+      </c>
+      <c r="BC31">
+        <v>18</v>
+      </c>
+      <c r="BD31">
+        <v>34</v>
+      </c>
+      <c r="BE31">
+        <v>42</v>
+      </c>
+      <c r="BF31">
         <v>15.5</v>
       </c>
-      <c r="BA31">
-        <v>48</v>
-      </c>
-      <c r="BB31">
-        <v>28</v>
-      </c>
-      <c r="BC31">
-        <v>23</v>
-      </c>
-      <c r="BD31">
-        <v>38</v>
-      </c>
-      <c r="BE31">
-        <v>55</v>
-      </c>
-      <c r="BF31">
-        <v>19</v>
-      </c>
       <c r="BG31">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="BH31">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI31">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
+        <v>1.01</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.01</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>1.01</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>1.01</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.01</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>1.01</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.01</v>
+      </c>
+      <c r="BZ31">
+        <v>0</v>
+      </c>
+      <c r="CA31">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" t="s">
+        <v>170</v>
+      </c>
+      <c r="F32">
+        <v>2.52</v>
+      </c>
+      <c r="G32">
+        <v>2.56</v>
+      </c>
+      <c r="H32">
+        <v>3.25</v>
+      </c>
+      <c r="I32">
+        <v>3.35</v>
+      </c>
+      <c r="J32">
+        <v>3.25</v>
+      </c>
+      <c r="K32">
+        <v>3.3</v>
+      </c>
+      <c r="L32">
+        <v>1.46</v>
+      </c>
+      <c r="M32">
+        <v>1.09</v>
+      </c>
+      <c r="N32">
+        <v>3.5</v>
+      </c>
+      <c r="O32">
+        <v>1.37</v>
+      </c>
+      <c r="P32">
+        <v>1.83</v>
+      </c>
+      <c r="Q32">
+        <v>2.14</v>
+      </c>
+      <c r="R32">
+        <v>1.32</v>
+      </c>
+      <c r="S32">
+        <v>3.9</v>
+      </c>
+      <c r="T32">
+        <v>1.84</v>
+      </c>
+      <c r="U32">
+        <v>2.12</v>
+      </c>
+      <c r="V32">
+        <v>1.43</v>
+      </c>
+      <c r="W32">
+        <v>1.64</v>
+      </c>
+      <c r="X32">
+        <v>12</v>
+      </c>
+      <c r="Y32">
+        <v>12</v>
+      </c>
+      <c r="Z32">
+        <v>23</v>
+      </c>
+      <c r="AA32">
+        <v>65</v>
+      </c>
+      <c r="AB32">
+        <v>10.5</v>
+      </c>
+      <c r="AC32">
+        <v>7.2</v>
+      </c>
+      <c r="AD32">
+        <v>14.5</v>
+      </c>
+      <c r="AE32">
+        <v>42</v>
+      </c>
+      <c r="AF32">
+        <v>16</v>
+      </c>
+      <c r="AG32">
+        <v>12</v>
+      </c>
+      <c r="AH32">
+        <v>18</v>
+      </c>
+      <c r="AI32">
+        <v>380</v>
+      </c>
+      <c r="AJ32">
+        <v>38</v>
+      </c>
+      <c r="AK32">
+        <v>29</v>
+      </c>
+      <c r="AL32">
+        <v>46</v>
+      </c>
+      <c r="AM32">
+        <v>110</v>
+      </c>
+      <c r="AN32">
+        <v>25</v>
+      </c>
+      <c r="AO32">
+        <v>48</v>
+      </c>
+      <c r="AP32">
+        <v>10.5</v>
+      </c>
+      <c r="AQ32">
+        <v>11</v>
+      </c>
+      <c r="AR32">
+        <v>18.5</v>
+      </c>
+      <c r="AS32">
+        <v>48</v>
+      </c>
+      <c r="AT32">
+        <v>9</v>
+      </c>
+      <c r="AU32">
+        <v>6.4</v>
+      </c>
+      <c r="AV32">
+        <v>11.5</v>
+      </c>
+      <c r="AW32">
+        <v>34</v>
+      </c>
+      <c r="AX32">
         <v>13.5</v>
       </c>
-      <c r="BN31">
-        <v>5.1</v>
-      </c>
-      <c r="BO31">
-        <v>4.5</v>
-      </c>
-      <c r="BP31">
-        <v>18.5</v>
-      </c>
-      <c r="BQ31">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR31">
+      <c r="AY32">
+        <v>10.5</v>
+      </c>
+      <c r="AZ32">
+        <v>15.5</v>
+      </c>
+      <c r="BA32">
+        <v>36</v>
+      </c>
+      <c r="BB32">
+        <v>30</v>
+      </c>
+      <c r="BC32">
+        <v>25</v>
+      </c>
+      <c r="BD32">
+        <v>38</v>
+      </c>
+      <c r="BE32">
+        <v>55</v>
+      </c>
+      <c r="BF32">
+        <v>21</v>
+      </c>
+      <c r="BG32">
         <v>34</v>
       </c>
-      <c r="BS31">
+      <c r="BH32">
+        <v>3.15</v>
+      </c>
+      <c r="BI32">
+        <v>2.94</v>
+      </c>
+      <c r="BJ32">
+        <v>9.6</v>
+      </c>
+      <c r="BK32">
+        <v>5.9</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>13</v>
+      </c>
+      <c r="BN32">
+        <v>5.4</v>
+      </c>
+      <c r="BO32">
+        <v>4.7</v>
+      </c>
+      <c r="BP32">
+        <v>21</v>
+      </c>
+      <c r="BQ32">
+        <v>8.6</v>
+      </c>
+      <c r="BR32">
+        <v>34</v>
+      </c>
+      <c r="BS32">
         <v>10</v>
       </c>
-      <c r="BT31">
+      <c r="BT32">
         <v>6.6</v>
       </c>
-      <c r="BU31">
-        <v>5.4</v>
-      </c>
-      <c r="BV31">
-        <v>30</v>
-      </c>
-      <c r="BW31">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX31">
-        <v>44</v>
-      </c>
-      <c r="BY31">
-        <v>11</v>
-      </c>
-      <c r="BZ31">
-        <v>32</v>
-      </c>
-      <c r="CA31">
+      <c r="BU32">
+        <v>5.7</v>
+      </c>
+      <c r="BV32">
+        <v>28</v>
+      </c>
+      <c r="BW32">
+        <v>9.6</v>
+      </c>
+      <c r="BX32">
+        <v>42</v>
+      </c>
+      <c r="BY32">
+        <v>10.5</v>
+      </c>
+      <c r="BZ32">
+        <v>34</v>
+      </c>
+      <c r="CA32">
         <v>10</v>
       </c>
-      <c r="CB31" t="s">
-        <v>169</v>
+      <c r="CB32" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
